--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1909,6 +1909,43 @@
       <c r="G19" s="27" t="inlineStr">
         <is>
           <t>나이 제한: 가입은 허용하고 범위 밖은 위험 예측만 제외, 챌린지 참여 가능(REQ-ELIG-001 그대로). 응급 시 진행 여부(ELIG-003 vs NFR-SAFE-004)는 보류 / 음주 빈도 필수 결정: 비흡연·비음주는 나트륨 미션으로 대체하는 판정이 W04 입력에 기대므로 / 응급 진행 여부와 혈압 측정 포함 여부 확정(9/28 팀 결정) / 고혈압 진단자도 예측 대상(입력으로 사용). 심혈관질환 진단자 제외 범위·서비스 대상 질환 표현은 팀 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>v1.9</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>NFR-ML-007 "모델 B는 사용하지 않는다", REQ-PRED-009·NFR-ML-008 삭제, 결과 카드 2개(모델 A만) / 건강정보 입력에 허리둘레·한 번 음주량 없음 / 생활습관 설문은 챌린지 추천 전용</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>모델 B 복원: NFR-ML-007 모델 A·B 이원화 복원, REQ-PRED-009·NFR-ML-008 복원, REQ-PRED-001 모델 B 결과 추가(판정이 아니라 요인 설명·챌린지 근거), REQ-PRED-006 카드 3개(세 번째 = 모델 B 현재 위험 프로필), REQ-ELIG-002 모델 B는 고혈압 진단·치료 중이면 예측 안 함 / REQ-HEALTH-002 필수 항목에 허리둘레·한 번 음주량 추가 / REQ-HEALTH-005 설문 중 외식·배달·아침·신체활동을 모델 B 입력으로도 사용</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>1차 멘토링(9/28) — 쉬운 모델(모델 B) 먼저, 모델 A도 보정 없이 빠르게 만들어 데모에 연결</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>v1.8의 "팀 결정 — 모델 B 제외"(9/28 17:22)는 1차 멘토링(9/28 19:31) 전 결정. 한 번 음주량 선택지는 학습 데이터(BD2_1) 구간 그대로(1–2 / 3–4 / 5–6 / 7–9 / 10잔 이상)</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.00500011" customWidth="1" min="1" max="1"/>
@@ -5045,6 +5082,222 @@
       <c r="E100" s="27" t="inlineStr">
         <is>
           <t>팀 결정 — 흡연·음주를 건강정보에서 수집</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B101" s="27" t="inlineStr">
+        <is>
+          <t>NFR-ML-007</t>
+        </is>
+      </c>
+      <c r="C101" s="27" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D101" s="27" t="inlineStr">
+        <is>
+          <t>모델 A 단독 → 모델 A·B 이원화(v1.7 문장 복원)</t>
+        </is>
+      </c>
+      <c r="E101" s="27" t="inlineStr">
+        <is>
+          <t>1차 멘토링(9/28) — 모델 B 먼저 개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="27" t="inlineStr">
+        <is>
+          <t>복원</t>
+        </is>
+      </c>
+      <c r="B102" s="27" t="inlineStr">
+        <is>
+          <t>NFR-ML-008</t>
+        </is>
+      </c>
+      <c r="C102" s="27" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D102" s="27" t="inlineStr">
+        <is>
+          <t>모델 B 학습 모집단(고혈압군 제외) 정의 복원</t>
+        </is>
+      </c>
+      <c r="E102" s="27" t="inlineStr">
+        <is>
+          <t>1차 멘토링(9/28) — 모델 B 먼저 개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="27" t="inlineStr">
+        <is>
+          <t>복원</t>
+        </is>
+      </c>
+      <c r="B103" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-009</t>
+        </is>
+      </c>
+      <c r="C103" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D103" s="27" t="inlineStr">
+        <is>
+          <t>모델 B 라벨(정상 vs 경계군) 정의 복원. 모집단 참조를 NFR-ML-008로 정정</t>
+        </is>
+      </c>
+      <c r="E103" s="27" t="inlineStr">
+        <is>
+          <t>1차 멘토링(9/28) — 모델 B 먼저 개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B104" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-001</t>
+        </is>
+      </c>
+      <c r="C104" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D104" s="27" t="inlineStr">
+        <is>
+          <t>모델 B 결과(경계군과 닮은 정도·기여 요인) 추가. 3단계 판정은 모델 A에만 적용</t>
+        </is>
+      </c>
+      <c r="E104" s="27" t="inlineStr">
+        <is>
+          <t>1차 멘토링(9/28) — 모델 B 먼저 개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-006</t>
+        </is>
+      </c>
+      <c r="C105" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D105" s="27" t="inlineStr">
+        <is>
+          <t>카드 2개 → 3개(세 번째 = 모델 B 현재 위험 프로필·개선 가능 1위 요인)</t>
+        </is>
+      </c>
+      <c r="E105" s="27" t="inlineStr">
+        <is>
+          <t>1차 멘토링(9/28) — 모델 B 먼저 개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B106" s="27" t="inlineStr">
+        <is>
+          <t>REQ-ELIG-002</t>
+        </is>
+      </c>
+      <c r="C106" s="27" t="inlineStr">
+        <is>
+          <t>이용 적합성</t>
+        </is>
+      </c>
+      <c r="D106" s="27" t="inlineStr">
+        <is>
+          <t>모델 B는 고혈압 진단·치료 중인 사용자에게 예측하지 않음</t>
+        </is>
+      </c>
+      <c r="E106" s="27" t="inlineStr">
+        <is>
+          <t>1차 멘토링(9/28) — 모델 B 먼저 개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B107" s="27" t="inlineStr">
+        <is>
+          <t>REQ-HEALTH-002</t>
+        </is>
+      </c>
+      <c r="C107" s="27" t="inlineStr">
+        <is>
+          <t>건강정보</t>
+        </is>
+      </c>
+      <c r="D107" s="27" t="inlineStr">
+        <is>
+          <t>필수 항목에 허리둘레·한 번 음주량(마시는 사람만) 추가</t>
+        </is>
+      </c>
+      <c r="E107" s="27" t="inlineStr">
+        <is>
+          <t>1차 멘토링(9/28) — 모델 B 먼저 개발 / 허리둘레는 모델 B 주요 입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B108" s="27" t="inlineStr">
+        <is>
+          <t>REQ-HEALTH-005</t>
+        </is>
+      </c>
+      <c r="C108" s="27" t="inlineStr">
+        <is>
+          <t>건강정보</t>
+        </is>
+      </c>
+      <c r="D108" s="27" t="inlineStr">
+        <is>
+          <t>설문 중 외식·배달·아침 식사·신체활동을 모델 B 입력으로도 사용</t>
+        </is>
+      </c>
+      <c r="E108" s="27" t="inlineStr">
+        <is>
+          <t>1차 멘토링(9/28) — 모델 B 먼저 개발</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.00500011" customWidth="1" min="1" max="1"/>
@@ -5618,7 +5871,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>대상 질환(관상동맥질환)을 이미 진단받은 사용자는 신규 위험 예측 대상에서 제외하고 생활습관 기능과 의료기관 안내로 연결해야 한다. 고혈압 진단·치료 상태는 제외 조건이 아니라 예측 입력으로 사용한다.</t>
+          <t>대상 질환(관상동맥질환)을 이미 진단받은 사용자는 신규 위험 예측 대상에서 제외하고 생활습관 기능과 의료기관 안내로 연결해야 한다. 고혈압 진단·치료 상태는 제외 조건이 아니라 예측 입력으로 사용한다. 단, 모델 B는 고혈압 진단·치료 중인 사용자에게 예측하지 않는다(학습 모집단에서 고혈압 제외, NFR-ML-008).</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -5633,7 +5886,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>기진단자에게 위험 확률을 생성·표시하지 않는다. 챌린지·대시보드는 계속 이용 가능. 고혈압 진단자와 혈압약 복용자는 예측 대상이며 고혈압 진단·치료 상태는 모델 입력으로 수집한다. (심혈관질환 진단자 제외 범위는 모델 문서의 적용 대상 정의 확인 후 확정)</t>
+          <t>기진단자에게 위험 확률을 생성·표시하지 않는다. 챌린지·대시보드는 계속 이용 가능. 고혈압 진단자와 혈압약 복용자는 모델 A 예측 대상이며(모델 B 결과는 생성하지 않음) 고혈압 진단·치료 상태는 모델 입력으로 수집한다. (심혈관질환 진단자 제외 범위는 모델 문서의 적용 대상 정의 확인 후 확정)</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -5846,7 +6099,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>사용자는 위험 예측 모델에 필요한 건강정보를 입력할 수 있어야 한다. 필수 항목은 수축기혈압·이완기혈압·신장·체중·흡연 여부·음주 빈도·당뇨병 여부·고혈압 진단·치료 상태(진단 없음 / 진단받았지만 약은 안 먹음 / 진단받았고 약을 먹는 중)·총콜레스테롤·HDL콜레스테롤·부모 고혈압 가족력이며, 선택 항목은 공복혈당·운동 빈도이다. 나이·성별은 REQ-HEALTH-001의 프로필 정보를 그대로 참조한다.</t>
+          <t>사용자는 위험 예측 모델에 필요한 건강정보를 입력할 수 있어야 한다. 필수 항목은 수축기혈압·이완기혈압·신장·체중·허리둘레·흡연 여부·음주 빈도·한 번 음주량(마시는 사람만)·당뇨병 여부·고혈압 진단·치료 상태(진단 없음 / 진단받았지만 약은 안 먹음 / 진단받았고 약을 먹는 중)·총콜레스테롤·HDL콜레스테롤·부모 고혈압 가족력이며, 선택 항목은 공복혈당·운동 빈도이다. 나이·성별은 REQ-HEALTH-001의 프로필 정보를 그대로 참조한다.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -5861,7 +6114,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>필수·선택 항목과 단위를 구분(혈압 mmHg, 신장 cm, 체중 kg, 콜레스테롤 mg/dL). BMI는 신장·체중에서 서버가 계산하며 사용자가 직접 입력하지 않는다. 선택 항목이 비어도 예측은 수행하되 결과에 정확도 한계를 표시. 입력 계약을 스키마 버전으로 추적. 성별·나이는 REQ-HEALTH-001에서 1회만 수집하며, 검진 입력 시 다시 요청하지 않는다.</t>
+          <t>필수·선택 항목과 단위를 구분(혈압 mmHg, 신장 cm, 체중 kg, 허리둘레 cm, 콜레스테롤 mg/dL). BMI는 신장·체중에서 서버가 계산하며 사용자가 직접 입력하지 않는다. 선택 항목이 비어도 예측은 수행하되 결과에 정확도 한계를 표시. 입력 계약을 스키마 버전으로 추적. 성별·나이는 REQ-HEALTH-001에서 1회만 수집하며, 검진 입력 시 다시 요청하지 않는다. 음주 빈도·한 번 음주량·흡연 여부의 선택지는 모델 문서의 입력 변환표를 따른다.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -6017,7 +6270,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>사용자는 챌린지 추천에 필요한 생활습관 정보를 설문지 형태로 입력할 수 있어야 한다.</t>
+          <t>사용자는 챌린지 추천에 필요한 생활습관 정보를 설문지 형태로 입력할 수 있어야 한다. 설문 응답 중 외식·배달 빈도, 아침 식사 빈도, 신체활동(종목·시간)은 모델 B 입력으로도 사용한다.</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
@@ -6032,7 +6285,7 @@
       </c>
       <c r="I17" s="19" t="inlineStr">
         <is>
-          <t>모든 문항은 주관식이 아닌 선택지로 제공한다. 앞 문항의 답에 따라 불필요한 문항은 건너뛴다. 운동은 종목을 고르면 강도가 자동 분류되도록 한다. 단계 표시와 조건부 문항 건너뛰기를 제공한다. 나트륨 문항은 REQ-PRED-008 의 5문항 점수화 규칙을 따른다. (PRD CH-01)</t>
+          <t>모든 문항은 주관식이 아닌 선택지로 제공한다. 앞 문항의 답에 따라 불필요한 문항은 건너뛴다. 운동은 종목을 고르면 강도가 자동 분류되도록 한다. 단계 표시와 조건부 문항 건너뛰기를 제공한다. 나트륨 문항은 REQ-PRED-008 의 5문항 점수화 규칙을 따른다. (PRD CH-01) 설문 응답 → 모델 B 입력 변환은 모델 문서의 입력 변환표를 따른다.</t>
         </is>
       </c>
       <c r="J17" s="19" t="inlineStr">
@@ -6235,7 +6488,7 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>단일 모델</t>
+          <t>두 모델</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -6245,7 +6498,7 @@
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>사용자는 모델 A의 결과로 10년 내 관상동맥질환 발병 위험을 확인할 수 있어야 한다.</t>
+          <t>사용자는 모델 A의 결과로 10년 내 관상동맥질환 발병 위험을, 모델 B의 결과로 현재 고혈압 경계군과 닮은 정도와 그에 기여한 요인을 확인할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -6260,7 +6513,7 @@
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>결과는 진단이 아닌 선별 정보. 위험 범주는 정상·경계·위험 3단계로 하고 색상(초록·노랑·빨강)과 텍스트를 함께 표시한다. 구간 기준은 모델 문서에 따른다. 정상은 추가 안내 없음, 경계는 기여 요인과 챌린지를 함께 제시, 위험은 REQ-PRED-005(검사·상담 안내)로 연결한다.</t>
+          <t>결과는 진단이 아닌 선별 정보. 위험 범주는 정상·경계·위험 3단계로 하고 색상(초록·노랑·빨강)과 텍스트를 함께 표시한다. 구간 기준은 모델 문서에 따른다. 정상은 추가 안내 없음, 경계는 기여 요인과 챌린지를 함께 제시, 위험은 REQ-PRED-005(검사·상담 안내)로 연결한다. 정상·경계·위험 3단계와 구간 기준은 모델 A 결과에 적용한다. 모델 B 결과는 판정이 아니라 기여 요인 설명과 챌린지 근거로 사용한다. 두 모델의 결과를 하나로 합산하지 않는다.</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -6520,17 +6773,17 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>카드 2개</t>
+          <t>카드 3개</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>위험 · 혈관 나이</t>
+          <t>위험 · 혈관 나이 · 현재 프로필</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>예측 결과는 카드 2개로 나누어 제시한다. 첫 번째 카드는 10년 내 관상동맥질환 발병 위험과 위험 구간, 두 번째 카드는 혈관 나이와 실제 나이 비교를 담는다.</t>
+          <t>예측 결과는 카드 3개로 나누어 제시한다. 첫 번째 카드는 10년 내 관상동맥질환 발병 위험과 위험 구간, 두 번째 카드는 혈관 나이와 실제 나이 비교, 세 번째 카드는 모델 B의 현재 위험 프로필과 개선 가능 1위 요인을 담는다.</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -6545,7 +6798,7 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>혈관 나이는 추정치임을 함께 표기하고 NFR-SAFE-001을 따른다.</t>
+          <t>카드를 하나의 종합 점수로 합치지 않는다. 혈관 나이는 추정치임을 함께 표기하고 NFR-SAFE-001을 따른다.</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -10681,17 +10934,17 @@
       </c>
       <c r="D99" s="14" t="inlineStr">
         <is>
-          <t>단일 모델</t>
+          <t>모델 이원화</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>학습 데이터</t>
+          <t>독립 학습</t>
         </is>
       </c>
       <c r="F99" s="14" t="inlineStr">
         <is>
-          <t>예측 모델은 모델 A(10년 관상동맥질환 예측) 하나만 사용한다. 모델 B(현재 경계군 분류)는 사용하지 않는다.</t>
+          <t>모델 A(장기 위험)와 모델 B(현재 위험)는 서로 다른 데이터셋으로 각각 독립적으로 학습하며, 두 데이터를 하나로 합쳐 학습하지 않는다.</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">
@@ -10706,7 +10959,7 @@
       </c>
       <c r="I99" s="14" t="inlineStr">
         <is>
-          <t>모델 A는 Framingham Heart Study(미국, 코호트, 10년 후 CHD 예측) 데이터셋을 사용한다. 학습 코드·아티팩트(모델 파일·스케일러)는 버전별로 분리해 관리한다.</t>
+          <t>모델 A는 Framingham Heart Study(미국, 코호트, 10년 후 CHD 예측), 모델 B는 국민건강영양조사 2022-2024(한국, 횡단면, 현재 경계군 여부 예측) 데이터셋을 사용한다. 두 모델의 학습 코드·아티팩트(모델 파일·스케일러)는 분리해 관리한다.</t>
         </is>
       </c>
       <c r="J99" s="14" t="inlineStr">
@@ -10829,6 +11082,120 @@
         </is>
       </c>
       <c r="K101" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="inlineStr">
+        <is>
+          <t>NFR-ML-008</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>모집단</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>학습 대상</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>고혈압군 제외</t>
+        </is>
+      </c>
+      <c r="F102" s="14" t="inlineStr">
+        <is>
+          <t>모델 B의 학습 데이터 모집단은 정상 또는 경계군에 해당하는 응답자로 한정하며, 이미 고혈압(4단계)에 해당하는 응답자는 학습 대상에서 제외한다.</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H102" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I102" s="14" t="inlineStr">
+        <is>
+          <t>HE_HP=1(정상), 2·3(경계군)에 해당하는 응답자만 학습에 포함하고, HE_HP=4(고혈압)는 제외한다. 이는 학습 데이터 구성 단계의 필터링이며, 서비스 시점의 사용자 자격 판단(REQ-ELIG-002, 자기보고 기반)과는 별개 기준이다.</t>
+        </is>
+      </c>
+      <c r="J102" s="14" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K102" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PRED-009</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>위험 예측</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="inlineStr">
+        <is>
+          <t>대상군 정의</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t>경계군 분류</t>
+        </is>
+      </c>
+      <c r="F103" s="14" t="inlineStr">
+        <is>
+          <t>모델 B의 라벨은 정상(0) vs 경계군(1, 주의혈압·고혈압전단계)의 이진 분류로 정의한다. 학습 데이터 모집단 구성은 NFR-ML-008을 따른다.</t>
+        </is>
+      </c>
+      <c r="G103" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H103" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I103" s="14" t="inlineStr">
+        <is>
+          <t>라벨은 국민건강영양조사 HE_HP 기준 1→0, 2·3→1로 정의하고 4(고혈압)는 학습에서 제외한다. 학습 모집단 필터링(NFR-ML-008)은 서비스 시점의 예측 대상 판단(REQ-ELIG-002)과 별개 기준이다.</t>
+        </is>
+      </c>
+      <c r="J103" s="14" t="inlineStr">
+        <is>
+          <t>W06 예측 결과 · XAI 설명</t>
+        </is>
+      </c>
+      <c r="K103" s="14" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -10847,7 +11214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11232,6 +11599,33 @@
       <c r="E14" s="14" t="inlineStr">
         <is>
           <t>모델 B 제외(팀 결정)로 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>모델·예측</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>REQ-PRED-009</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>REQ-PRED-009, NFR-ML-008</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>복원</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>1차 멘토링(9/28) — 모델 B 복원</t>
         </is>
       </c>
     </row>

--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1946,6 +1946,43 @@
       <c r="G20" s="27" t="inlineStr">
         <is>
           <t>v1.8의 "팀 결정 — 모델 B 제외"(9/28 17:22)는 1차 멘토링(9/28 19:31) 전 결정. 한 번 음주량 선택지는 학습 데이터(BD2_1) 구간 그대로(1–2 / 3–4 / 5–6 / 7–9 / 10잔 이상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>모델 B 입력에 외식·아침·신체활동 포함, 나트륨 5문항 0~2점(mg 컷 재현 안 됨), 대체 규칙에 모델 기여도 사용, 흡연 1문항(전자담배 구분 없음), 잔 정의 없음, 미션은 예시만</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>모델 B v0.2.0(9개 피처, 외식·아침·신체활동 제외) 반영: REQ-HEALTH-002·005·008, REQ-PRED-003·008, REQ-CHAL-008·009·010, NFR-ML-006 수정, 미션 카탈로그 확정(미션 9개, 체중 관리 MVP 제외). 상세 구현 명세는 modeling/handoff/생활습관_입력_가이드.md</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>모델 B에서 세 피처를 빼도 성능 차이 없음(테스트 AUC 0.7454 → 0.7435), 운동·외식 반대 방향 학습, 9/28 결정(챌린지 근거는 지침·문헌). 나트륨은 24시간 소변으로 검증된 한국인 나트륨 지수로 교체</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
+        <is>
+          <t>흡연은 모델 B에서 반대 방향이라 화면에서 숨기고 금연 근거는 모델 A·문헌</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.00500011" customWidth="1" min="1" max="1"/>
@@ -5298,6 +5335,276 @@
       <c r="E108" s="27" t="inlineStr">
         <is>
           <t>1차 멘토링(9/28) — 모델 B 먼저 개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B109" s="27" t="inlineStr">
+        <is>
+          <t>REQ-HEALTH-002</t>
+        </is>
+      </c>
+      <c r="C109" s="27" t="inlineStr">
+        <is>
+          <t>건강정보</t>
+        </is>
+      </c>
+      <c r="D109" s="27" t="inlineStr">
+        <is>
+          <t>전자담배 문항 추가, 선택 항목 운동 빈도 삭제, 흡연·음주 조사표 문구·잔 기준표</t>
+        </is>
+      </c>
+      <c r="E109" s="27" t="inlineStr">
+        <is>
+          <t>모델 B v0.2.0·생활습관 입력 가이드 (2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>REQ-HEALTH-005</t>
+        </is>
+      </c>
+      <c r="C110" s="27" t="inlineStr">
+        <is>
+          <t>건강정보</t>
+        </is>
+      </c>
+      <c r="D110" s="27" t="inlineStr">
+        <is>
+          <t>생활습관 설문을 챌린지 판정 전용으로 변경(모델 B 입력 아님), 설문 구성 확정</t>
+        </is>
+      </c>
+      <c r="E110" s="27" t="inlineStr">
+        <is>
+          <t>모델 B v0.2.0·생활습관 입력 가이드 (2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>REQ-HEALTH-008</t>
+        </is>
+      </c>
+      <c r="C111" s="27" t="inlineStr">
+        <is>
+          <t>건강정보</t>
+        </is>
+      </c>
+      <c r="D111" s="27" t="inlineStr">
+        <is>
+          <t>4주 재입력에 몸무게·허리둘레·흡연·전자담배·음주 추가, "최근 4주" 문구</t>
+        </is>
+      </c>
+      <c r="E111" s="27" t="inlineStr">
+        <is>
+          <t>모델 B v0.2.0·생활습관 입력 가이드 (2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-003</t>
+        </is>
+      </c>
+      <c r="C112" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D112" s="27" t="inlineStr">
+        <is>
+          <t>반대 방향 요인 미표시, 요인은 설명용(챌린지 추천에 미사용)</t>
+        </is>
+      </c>
+      <c r="E112" s="27" t="inlineStr">
+        <is>
+          <t>모델 B v0.2.0·생활습관 입력 가이드 (2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-008</t>
+        </is>
+      </c>
+      <c r="C113" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D113" s="27" t="inlineStr">
+        <is>
+          <t>나트륨 5문항 → 나트륨 지수 11문항·계산식·등급</t>
+        </is>
+      </c>
+      <c r="E113" s="27" t="inlineStr">
+        <is>
+          <t>모델 B v0.2.0·생활습관 입력 가이드 (2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-008</t>
+        </is>
+      </c>
+      <c r="C114" s="27" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D114" s="27" t="inlineStr">
+        <is>
+          <t>고정 칸 대체 순서(나트륨 → 신체 활동 → 외식·배달 → 아침), 모델 기여도 미사용</t>
+        </is>
+      </c>
+      <c r="E114" s="27" t="inlineStr">
+        <is>
+          <t>모델 B v0.2.0·생활습관 입력 가이드 (2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-009</t>
+        </is>
+      </c>
+      <c r="C115" s="27" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D115" s="27" t="inlineStr">
+        <is>
+          <t>미션별 난이도 1개 고정, 걸음 수만 사용자별 목표</t>
+        </is>
+      </c>
+      <c r="E115" s="27" t="inlineStr">
+        <is>
+          <t>모델 B v0.2.0·생활습관 입력 가이드 (2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B116" s="27" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-010</t>
+        </is>
+      </c>
+      <c r="C116" s="27" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D116" s="27" t="inlineStr">
+        <is>
+          <t>잔 기준표·기록 선택지 추가</t>
+        </is>
+      </c>
+      <c r="E116" s="27" t="inlineStr">
+        <is>
+          <t>모델 B v0.2.0·생활습관 입력 가이드 (2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B117" s="27" t="inlineStr">
+        <is>
+          <t>NFR-ML-006</t>
+        </is>
+      </c>
+      <c r="C117" s="27" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D117" s="27" t="inlineStr">
+        <is>
+          <t>챌린지 채택 기준을 모델 A 요인 → 임상시험·메타분석·정부 지침 근거로 변경</t>
+        </is>
+      </c>
+      <c r="E117" s="27" t="inlineStr">
+        <is>
+          <t>모델 B v0.2.0·생활습관 입력 가이드 (2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B118" s="27" t="inlineStr">
+        <is>
+          <t>미션 카탈로그</t>
+        </is>
+      </c>
+      <c r="C118" s="27" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D118" s="27" t="inlineStr">
+        <is>
+          <t>미션 9개 확정, 체중 관리 MVP 제외</t>
+        </is>
+      </c>
+      <c r="E118" s="27" t="inlineStr">
+        <is>
+          <t>모델 B v0.2.0·생활습관 입력 가이드 (2026-10-07)</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6406,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>사용자는 위험 예측 모델에 필요한 건강정보를 입력할 수 있어야 한다. 필수 항목은 수축기혈압·이완기혈압·신장·체중·허리둘레·흡연 여부·음주 빈도·한 번 음주량(마시는 사람만)·당뇨병 여부·고혈압 진단·치료 상태(진단 없음 / 진단받았지만 약은 안 먹음 / 진단받았고 약을 먹는 중)·총콜레스테롤·HDL콜레스테롤·부모 고혈압 가족력이며, 선택 항목은 공복혈당·운동 빈도이다. 나이·성별은 REQ-HEALTH-001의 프로필 정보를 그대로 참조한다.</t>
+          <t>사용자는 위험 예측 모델에 필요한 건강정보를 입력할 수 있어야 한다. 필수 항목은 수축기혈압·이완기혈압·신장·체중·허리둘레·흡연 여부(일반담배)·전자담배 사용 여부·음주 빈도·한 번 음주량(마시는 사람만)·당뇨병 여부·고혈압 진단·치료 상태(진단 없음 / 진단받았지만 약은 안 먹음 / 진단받았고 약을 먹는 중)·총콜레스테롤·HDL콜레스테롤·부모 고혈압 가족력이며, 선택 항목은 공복혈당이다. 나이·성별은 REQ-HEALTH-001의 프로필 정보를 그대로 참조한다.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -6114,7 +6421,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>필수·선택 항목과 단위를 구분(혈압 mmHg, 신장 cm, 체중 kg, 허리둘레 cm, 콜레스테롤 mg/dL). BMI는 신장·체중에서 서버가 계산하며 사용자가 직접 입력하지 않는다. 선택 항목이 비어도 예측은 수행하되 결과에 정확도 한계를 표시. 입력 계약을 스키마 버전으로 추적. 성별·나이는 REQ-HEALTH-001에서 1회만 수집하며, 검진 입력 시 다시 요청하지 않는다. 음주 빈도·한 번 음주량·흡연 여부의 선택지는 모델 문서의 입력 변환표를 따른다.</t>
+          <t>필수·선택 항목과 단위를 구분(혈압 mmHg, 신장 cm, 체중 kg, 허리둘레 cm, 콜레스테롤 mg/dL). BMI는 신장·체중에서 서버가 계산하며 사용자가 직접 입력하지 않는다. 선택 항목이 비어도 예측은 수행하되 결과에 정확도 한계를 표시. 입력 계약을 스키마 버전으로 추적. 성별·나이는 REQ-HEALTH-001에서 1회만 수집하며, 검진 입력 시 다시 요청하지 않는다. 음주 빈도·한 번 음주량·흡연 여부의 선택지는 모델 문서의 입력 변환표를 따른다. 흡연(일반담배)·음주 문항은 국민건강영양조사 조사표 문구를 그대로 쓰고, 전자담배는 별도 문항으로 받는다(모델 입력 아님). 한 번 음주량 아래에 잔 기준표를 표시한다. 문구·선택지·저장값은 modeling/handoff/생활습관_입력_가이드.md §1.1을 따른다.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -6270,7 +6577,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>사용자는 챌린지 추천에 필요한 생활습관 정보를 설문지 형태로 입력할 수 있어야 한다. 설문 응답 중 외식·배달 빈도, 아침 식사 빈도, 신체활동(종목·시간)은 모델 B 입력으로도 사용한다.</t>
+          <t>사용자는 챌린지 추천에 필요한 생활습관 정보를 설문지 형태로 입력할 수 있어야 한다. 생활습관 설문은 챌린지 추천 판정 전용이며 예측 모델 입력이 아니다(모델 B v0.2.0).</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
@@ -6285,7 +6592,7 @@
       </c>
       <c r="I17" s="19" t="inlineStr">
         <is>
-          <t>모든 문항은 주관식이 아닌 선택지로 제공한다. 앞 문항의 답에 따라 불필요한 문항은 건너뛴다. 운동은 종목을 고르면 강도가 자동 분류되도록 한다. 단계 표시와 조건부 문항 건너뛰기를 제공한다. 나트륨 문항은 REQ-PRED-008 의 5문항 점수화 규칙을 따른다. (PRD CH-01) 설문 응답 → 모델 B 입력 변환은 모델 문서의 입력 변환표를 따른다.</t>
+          <t>모든 문항은 주관식이 아닌 선택지로 제공한다(걸음 수만 숫자 입력). 설문 단계: 짠맛·나트륨(나트륨 지수 11문항, REQ-PRED-008) → 신체 활동 → 외식·배달 → 아침 식사 → 혈압 측정. 문항을 건너뛰어도 예측은 수행하고, 해당 카테고리만 추천에서 제외한다. 문구·선택지·저장값은 modeling/handoff/생활습관_입력_가이드.md §1.2를 따른다.</t>
         </is>
       </c>
       <c r="J17" s="19" t="inlineStr">
@@ -6441,7 +6748,7 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>재입력은 두 주기로 나눈다. 4주 사이클 종료 시에는 생활습관 재설문과 혈압만 받고, 혈액검사 수치를 포함한 전체 검진값은 3~6개월 주기로 받는다.</t>
+          <t>재입력은 두 주기로 나눈다. 4주 사이클 종료 시에는 혈압·몸무게·허리둘레·흡연·전자담배·음주와 생활습관 재설문을 받고, 혈액검사 수치를 포함한 전체 검진값은 3~6개월 주기로 받는다.</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -6456,7 +6763,7 @@
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>4주 재입력 항목은 모델 A 입력 중 4주 사이 바뀔 수 있는 항목(혈압·흡연 상태 등)과 일치해야 한다. 전체 재입력 전에는 혈당·콜레스테롤을 직전 값으로 유지하고 그 사실을 화면에 표시한다.</t>
+          <t>4주 재입력 항목은 모델 B 입력 중 4주 사이 바뀔 수 있는 항목(몸무게·허리둘레·흡연·음주)과 혈압을 포함한다. 음주·생활습관 문항은 "최근 4주 동안"으로 기간 문구만 바꾼다. 다시 받지 않는 항목(키·콜레스테롤·당뇨·고혈압 진단·가족력)은 직전 값을 유지하고 그 사실을 화면에 표시한다. 상세는 modeling/handoff/생활습관_입력_가이드.md §6을 따른다.</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
@@ -6627,7 +6934,7 @@
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
-          <t>위험을 높이는 방향(양의 기여도)의 요인 중 1위만 강조해 표시한다. 위험을 낮추는 방향(음의 기여도)의 요인은 강조 표시하지 않는다. 개선 가능 요인은 챌린지로 연결.</t>
+          <t>위험을 높이는 방향(양의 기여도)의 요인 중 1위만 강조해 표시한다. 위험을 낮추는 방향(음의 기여도)의 요인은 강조 표시하지 않는다. 학습 방향이 상식과 반대인 요인(direction_matches_expectation=false, 모델 B의 현재·과거 흡연)은 요인 목록에 표시하지 않는다. 요인은 결과 설명용이며, 챌린지 추천은 REQ-CHAL-008의 설문·건강정보 규칙으로 정한다.</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -7296,7 +7603,7 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>흡연·음주에 해당하지 않는 사용자에게는 고정 미션 자리를 나트륨 조절 미션으로 대체해야 한다.</t>
+          <t>흡연·음주에 해당하지 않는 사용자에게는 고정 미션 자리를 정해진 순서(나트륨 → 신체 활동 → 외식·배달 → 아침 식사)의 미션으로 대체해야 한다.</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -7311,7 +7618,7 @@
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>건강정보 입력(흡연 여부·음주 빈도)에서 비흡연·비음주로 판정되면 해당 고정 칸을 나트륨 미션으로 채운다. 나트륨도 이미 낮으면 기여도가 가장 큰 개선 가능 요인으로 대체한다.</t>
+          <t>건강정보 입력에서 비흡연(일반담배·전자담배 모두 사용 안 함)·비음주(평생 안 마심 또는 최근 1년간 안 마심)로 판정되면 해당 고정 칸을 대체 순서에서 조건이 맞는 첫 카테고리의 대표 미션으로 채운다. 두 칸은 서로 다른 카테고리로 채우고, 해당 카테고리가 없으면 비운다. 모델 출력(기여도)은 대체 판정에 쓰지 않는다. 상세는 modeling/handoff/생활습관_입력_가이드.md §3을 따른다.</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
@@ -7353,7 +7660,7 @@
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>챌린지는 초기 설문 결과에 따라 상·중·하 난이도로 구분해 제시해야 한다.</t>
+          <t>챌린지는 상·중·하 난이도를 표시해 제시해야 한다.</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -7368,7 +7675,7 @@
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>같은 챌린지라도 현재 수준에서 한 단계만 올린 목표를 제시한다. 사이클 종료 후 난이도를 조정할 수 있다.</t>
+          <t>미션마다 난이도 1개를 고정한다(미션 9개, modeling/handoff/생활습관_입력_가이드.md §4). 걸음 수 미션만 사용자별 목표(평소 걸음 + 2,000보)를 쓴다.</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
@@ -7425,7 +7732,7 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>선택지는 남성 2잔·여성 1잔 이하까지만 제공한다. 초과 시 경고 문구를 노출하되 서비스 이용을 제한하지 않는다. 문구는 금주를 우선 권고하는 최신 지침을 따른다.</t>
+          <t>선택지는 남성 2잔·여성 1잔 이하까지만 제공한다. 초과 시 경고 문구를 노출하되 서비스 이용을 제한하지 않는다. 문구는 금주를 우선 권고하는 최신 지침을 따른다. 잔은 설문과 같은 기준(소주 1병 = 7잔, 캔맥주 355ml = 1.5잔, 맥주 500ml = 2잔, 와인 1병 = 5잔, 막걸리 1병 = 3잔)으로 센다. 기록 선택지: 남성 안 마심·1잔·2잔·3잔 이상 / 여성 안 마심·1잔·2잔 이상.</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
@@ -10203,7 +10510,7 @@
       </c>
       <c r="F86" s="21" t="inlineStr">
         <is>
-          <t>챌린지 후보로 채택되는 생활습관 항목은 모델 A에서 바꿀 수 있는 위험 요인(수축기혈압·콜레스테롤 등)과 연결되는 것이어야 한다.</t>
+          <t>챌린지 후보로 채택되는 생활습관 항목은 혈압 감소 효과가 임상시험·메타분석으로 확인되었거나 정부 지침에 근거한 것이어야 한다.</t>
         </is>
       </c>
       <c r="G86" s="21" t="inlineStr">
@@ -10218,7 +10525,7 @@
       </c>
       <c r="I86" s="21" t="inlineStr">
         <is>
-          <t>모델 A의 수정 가능 요인(SHAP 중요도 상위 5위 이내)과 연결되는 챌린지를 후보로 채택한다. 연결 근거가 없는 항목은 후보에서 제외하거나 참고용으로만 표시한다. 분석 결과는 REQ-CHAL의 고정·선택 미션 분류 근거로 사용한다.</t>
+          <t>모델 근거(모델 B: 허리둘레·BMI·음주 / 모델 A: 흡연·수축기혈압)와 지침·문헌 근거(나트륨·신체 활동·외식·아침 식사)를 구분해 표시한다. 지침·문헌 근거 미션은 "위험을 높인 요인"으로 표현하지 않는다. 미션별 근거는 modeling/handoff/생활습관_입력_가이드.md 부록 B를 따른다.</t>
         </is>
       </c>
       <c r="J86" s="21" t="inlineStr">
@@ -11001,7 +11308,7 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>사용자는 나트륨 섭취 수준을 5문항 설문으로 응답하고, 그 응답이 점수화·등급화되어 챌린지 추천·제외 판단(나트륨 미션 후보)에 반영되어야 한다.</t>
+          <t>사용자는 나트륨 섭취 수준을 나트륨 지수(Lee 등 2022, 11문항) 설문으로 응답하고, 그 응답이 추정 나트륨 섭취량과 등급으로 계산되어 챌린지 추천·제외 판단(나트륨 미션 후보)에 반영되어야 한다.</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
@@ -11016,7 +11323,7 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>5개 문항(국물·김치·면류·절임·양념) 각 0~2점, 합산 0~10점. 0~3점=하(≤2,088mg), 4~6점=중(2,088~3,363mg), 7~10점=상(&gt;3,363mg)으로 매핑해 챌린지 후보 판정에 사용한다(예측 모델 입력이 아님). 등급 컷은 KNHANES 2022-2024 병합 데이터의 나트륨 섭취량 실측 삼분위수 기준이다.</t>
+          <t>나트륨 지수: 짠맛 습관 1문항(10~50점) + 식행동 10문항(합 20~100점)과 성별·연령대·BMI로 추정 나트륨(mg/일)을 계산하고, 지수 = 추정량 ÷ 20. 등급: 75 미만 주의(적음), 75~100 매우 적정, 100 초과~150 적정, 150 초과~250 주의(많음), 250 초과 심각. 지수 150 초과면 나트륨 챌린지 후보. 예측 모델 입력이 아니다. 계산식·문항은 modeling/handoff/생활습관_입력_가이드.md §1.2·§2.1을 따른다.</t>
         </is>
       </c>
       <c r="J100" s="14" t="inlineStr">
@@ -11704,32 +12011,32 @@
       </c>
       <c r="B2" s="25" t="inlineStr">
         <is>
-          <t>국물, 인스턴트, 김치·젓갈, 추가 간</t>
+          <t>나트륨 지수 11문항(REQ-PRED-008)</t>
         </is>
       </c>
       <c r="C2" s="25" t="inlineStr">
         <is>
-          <t>섭취 빈도가 높으면 추천</t>
+          <t>나트륨 지수 150 초과면 추천</t>
         </is>
       </c>
       <c r="D2" s="25" t="inlineStr">
         <is>
-          <t>국물 남기기, 라면 줄이기</t>
+          <t>국물 남기기(하, 주 5회), 음식에 소금·간장 더 넣지 않기(중, 주 5회)</t>
         </is>
       </c>
       <c r="E2" s="25" t="inlineStr">
         <is>
-          <t>기본 또는 선택</t>
+          <t>대체 1순위 · 선택</t>
         </is>
       </c>
       <c r="F2" s="25" t="inlineStr">
         <is>
-          <t>사진·자기 기록</t>
+          <t>자기 기록</t>
         </is>
       </c>
       <c r="G2" s="25" t="inlineStr">
         <is>
-          <t>의료 검토 후 문구 확정</t>
+          <t>He 2013 Cochrane: 소금 하루 4.4g 감량 시 수축기 −4.18mmHg</t>
         </is>
       </c>
       <c r="H2" s="25" t="inlineStr">
@@ -11746,32 +12053,32 @@
       </c>
       <c r="B3" s="25" t="inlineStr">
         <is>
-          <t>주간 활동 시간, 근력운동 일수, 좌식 시간</t>
+          <t>평소 일주일 운동 시간, 휴대폰 건강 앱 평소 걸음 수</t>
         </is>
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>활동이 부족하면 걷기·저강도 활동 추천</t>
+          <t>주 150분 미만이면 추천</t>
         </is>
       </c>
       <c r="D3" s="25" t="inlineStr">
         <is>
-          <t>하루 걷기, 발뒤꿈치 들기</t>
+          <t>걸음 수 평소 + 2,000보(하, 주 5일), 빠르게 걷기 30분(중, 주 5일), 벽 스쿼트 2분 × 4번(상, 주 3회, 혈압 160/100 이상 제외)</t>
         </is>
       </c>
       <c r="E3" s="25" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>대체 2순위 · 선택</t>
         </is>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>자동 기록·사진</t>
+          <t>자기 기록</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>개인 상태 고려 필요</t>
+          <t>Igarashi 2018, Cochrane 2021(걷기), Edwards 2023 BJSM(등척성)</t>
         </is>
       </c>
       <c r="H3" s="25" t="inlineStr">
@@ -11788,22 +12095,22 @@
       </c>
       <c r="B4" s="25" t="inlineStr">
         <is>
-          <t>흡연 여부, 음주 빈도 (건강정보 입력에서 수집, 둘 다 필수)</t>
+          <t>흡연(일반담배)·전자담배·음주 빈도 (건강정보 입력, 필수)</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>비흡연이면 금연 칸, 비음주면 절주 칸을 나트륨 미션으로 대체</t>
+          <t>흡연·전자담배 사용자는 금연 칸, 음주자는 절주 칸. 비해당이면 대체 순서(REQ-CHAL-008)</t>
         </is>
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>금연, 절주·음주 없는 날</t>
+          <t>금연 유지(일반담배·전자담배, 주 7일), 절주(마신 날도 남 2잔·여 1잔 이하, 주 7일)</t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
         <is>
-          <t>기본</t>
+          <t>고정</t>
         </is>
       </c>
       <c r="F4" s="25" t="inlineStr">
@@ -11813,7 +12120,7 @@
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>의료·정책 검토 필요</t>
+          <t>Hackshaw 2018 BMJ(저흡연도 위험), Roerecke 2017 Lancet Public Health(절주)</t>
         </is>
       </c>
       <c r="H4" s="25" t="inlineStr">
@@ -11830,22 +12137,22 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>외식·배달 빈도, 식사 유형, 집밥 횟수</t>
+          <t>평소 일주일 외식·배달 횟수</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>외식·배달 빈도가 높으면 추천</t>
+          <t>주 5–6회 이상이면 추천</t>
         </is>
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t>배달 줄이기, 저염 집밥</t>
+          <t>외식·배달 때 "싱겁게" 요청하기(중, 주 3회)</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>대체 3순위 · 선택</t>
         </is>
       </c>
       <c r="F5" s="25" t="inlineStr">
@@ -11855,7 +12162,7 @@
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>행동 문구 검토</t>
+          <t>나트륨 지수 문항 + He 2013</t>
         </is>
       </c>
       <c r="H5" s="25" t="inlineStr">
@@ -11872,37 +12179,37 @@
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>주간 아침 식사일, 결식 이유</t>
+          <t>평소 일주일 아침 식사 횟수</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>결식 빈도가 높으면 후보로 제안</t>
+          <t>주 3–4회 이하(주 3일 이상 결식)면 추천</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>아침 식사 주 5일</t>
+          <t>아침 식사 하기(하, 주 5일)</t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>대체 4순위 · 선택</t>
         </is>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>사진·자기 기록</t>
+          <t>자기 기록(사진 선택)</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>별도 근거 확인 필요</t>
+          <t>한국인을 위한 식생활지침 2021(아침식사 권장), Wicherski 2021(결식 정의)</t>
         </is>
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t>검토</t>
+          <t>MVP</t>
         </is>
       </c>
     </row>
@@ -11981,7 +12288,7 @@
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>상세 정책 미정</t>
+          <t>MVP 제외</t>
         </is>
       </c>
       <c r="H8" s="25" t="inlineStr">

--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1983,6 +1983,43 @@
       <c r="G21" s="27" t="inlineStr">
         <is>
           <t>흡연은 모델 B에서 반대 방향이라 화면에서 숨기고 금연 근거는 모델 A·문헌</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>v2.1</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>절주 대상 = 조금이라도 마시는 사람 전부, 금연 대상에 전자담배만 쓰는 사람 포함, 나트륨 지수를 검증 범위 밖 사용자에게도 계산, 외식 미션이 나트륨 조건 없이 소금 감량 근거 사용</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-008(금연 칸 = 일반담배 흡연자, 절주 칸 = 한 번 3잔 이상), REQ-PRED-008(나트륨 지수 적용 범위), 미션 카탈로그(나트륨·흡연·음주·외식 행) 수정</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>근거 연구 대상과 적용 대상 대조 결과 불일치 4건 수정 (팀원 지적: 절주 근거는 하루 2잔 넘게 마시던 사람 대상)</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="inlineStr">
+        <is>
+          <t>대조표: modeling/handoff/생활습관_입력_가이드.md 부록 A-3</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.00500011" customWidth="1" min="1" max="1"/>
@@ -5605,6 +5642,87 @@
       <c r="E118" s="27" t="inlineStr">
         <is>
           <t>모델 B v0.2.0·생활습관 입력 가이드 (2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B119" s="27" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-008</t>
+        </is>
+      </c>
+      <c r="C119" s="27" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D119" s="27" t="inlineStr">
+        <is>
+          <t>금연 칸 = 일반담배 흡연자, 절주 칸 = 한 번 3잔 이상 (근거 대상에 맞춤)</t>
+        </is>
+      </c>
+      <c r="E119" s="27" t="inlineStr">
+        <is>
+          <t>근거 대상 대조 (v2.1, 2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B120" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-008</t>
+        </is>
+      </c>
+      <c r="C120" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D120" s="27" t="inlineStr">
+        <is>
+          <t>나트륨 지수 적용 범위(19–69세, 고혈압·당뇨 없음) 밖은 계산 안 하고 나트륨 후보로</t>
+        </is>
+      </c>
+      <c r="E120" s="27" t="inlineStr">
+        <is>
+          <t>근거 대상 대조 (v2.1, 2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B121" s="27" t="inlineStr">
+        <is>
+          <t>미션 카탈로그</t>
+        </is>
+      </c>
+      <c r="C121" s="27" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D121" s="27" t="inlineStr">
+        <is>
+          <t>나트륨·흡연·음주·외식 행 대상 조건 수정</t>
+        </is>
+      </c>
+      <c r="E121" s="27" t="inlineStr">
+        <is>
+          <t>근거 대상 대조 (v2.1, 2026-10-07)</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7736,7 @@
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>건강정보 입력에서 비흡연(일반담배·전자담배 모두 사용 안 함)·비음주(평생 안 마심 또는 최근 1년간 안 마심)로 판정되면 해당 고정 칸을 대체 순서에서 조건이 맞는 첫 카테고리의 대표 미션으로 채운다. 두 칸은 서로 다른 카테고리로 채우고, 해당 카테고리가 없으면 비운다. 모델 출력(기여도)은 대체 판정에 쓰지 않는다. 상세는 modeling/handoff/생활습관_입력_가이드.md §3을 따른다.</t>
+          <t>건강정보 입력에서 금연 칸 비해당(일반담배 현재 흡연이 아님. 전자담배만 쓰는 경우 포함)·절주 칸 비해당(음주하지 않거나 한 번 음주량 1–2잔)으로 판정되면 해당 고정 칸을 대체 순서에서 조건이 맞는 첫 카테고리의 대표 미션으로 채운다. 금연·절주 칸 기준은 근거 연구 대상(일반담배 흡연자, 하루 2잔 넘게 마시던 사람)에 맞춘다. 두 칸은 서로 다른 카테고리로 채우고, 해당 카테고리가 없으면 비운다. 모델 출력(기여도)은 대체 판정에 쓰지 않는다. 상세는 modeling/handoff/생활습관_입력_가이드.md §3을 따른다.</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
@@ -11323,7 +11441,7 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>나트륨 지수: 짠맛 습관 1문항(10~50점) + 식행동 10문항(합 20~100점)과 성별·연령대·BMI로 추정 나트륨(mg/일)을 계산하고, 지수 = 추정량 ÷ 20. 등급: 75 미만 주의(적음), 75~100 매우 적정, 100 초과~150 적정, 150 초과~250 주의(많음), 250 초과 심각. 지수 150 초과면 나트륨 챌린지 후보. 예측 모델 입력이 아니다. 계산식·문항은 modeling/handoff/생활습관_입력_가이드.md §1.2·§2.1을 따른다.</t>
+          <t>나트륨 지수: 짠맛 습관 1문항(10~50점) + 식행동 10문항(합 20~100점)과 성별·연령대·BMI로 추정 나트륨(mg/일)을 계산하고, 지수 = 추정량 ÷ 20. 등급: 75 미만 주의(적음), 75~100 매우 적정, 100 초과~150 적정, 150 초과~250 주의(많음), 250 초과 심각. 지수 150 초과면 나트륨 챌린지 후보. 계산식은 고혈압·당뇨 진단이 없는 19–69세로 만든 식이므로, 70세 이상·고혈압 진단·치료 중·당뇨인 사용자는 지수를 계산·표시하지 않고 나트륨 챌린지 후보로 둔다. 예측 모델 입력이 아니다. 계산식·문항은 modeling/handoff/생활습관_입력_가이드.md §1.2·§2.1을 따른다.</t>
         </is>
       </c>
       <c r="J100" s="14" t="inlineStr">
@@ -12016,7 +12134,7 @@
       </c>
       <c r="C2" s="25" t="inlineStr">
         <is>
-          <t>나트륨 지수 150 초과면 추천</t>
+          <t>나트륨 지수 150 초과, 또는 지수 적용 범위 밖(70세 이상·고혈압·당뇨)이면 추천</t>
         </is>
       </c>
       <c r="D2" s="25" t="inlineStr">
@@ -12100,12 +12218,12 @@
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>흡연·전자담배 사용자는 금연 칸, 음주자는 절주 칸. 비해당이면 대체 순서(REQ-CHAL-008)</t>
+          <t>일반담배 현재 흡연자는 금연 칸, 한 번 3잔 이상 마시는 음주자는 절주 칸. 비해당이면 대체 순서(REQ-CHAL-008)</t>
         </is>
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>금연 유지(일반담배·전자담배, 주 7일), 절주(마신 날도 남 2잔·여 1잔 이하, 주 7일)</t>
+          <t>금연 유지(일반담배, 전자담배로 바꾸지 않기, 주 7일), 절주(마신 날도 남 2잔·여 1잔 이하, 주 7일)</t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
@@ -12142,7 +12260,7 @@
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>주 5–6회 이상이면 추천</t>
+          <t>외식·배달 주 5–6회 이상 그리고 나트륨 챌린지 대상이면 추천</t>
         </is>
       </c>
       <c r="D5" s="25" t="inlineStr">

--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2020,6 +2020,43 @@
       <c r="G22" s="27" t="inlineStr">
         <is>
           <t>대조표: modeling/handoff/생활습관_입력_가이드.md 부록 A-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>v2.2</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>혈압 = 주 1회 상시 기록(카탈로그 "복약·측정"), 완료한 챌린지 = 다음 사이클 후보에서 제외, 체중 관리 = Backlog, 카테고리 5~6개</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>혈압 = 시작·4주 재입력 때 입력(아침이나 저녁 중 편한 시간에 두 번 재서 평균, 학회 측정법), 카탈로그 "혈압 측정"으로 이름 변경, 완료한 챌린지 = 이어서 고를 수 있음(축하 문구), 체중 관리 WT-1 MVP, 카테고리 7개·미션 10개, 프로그램 4사이클(16주), NFR-SAFE-007 문구 규칙임을 명시</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>2차 멘토링(10/7)·팀 결정(10/8): 정상·경계인은 집에 혈압계가 없는 경우가 많아 매주 측정은 이탈 위험, 4주로는 습관이 굳지 않음(중앙값 66일), WT-1 신설</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>상세: modeling/handoff/생활습관_입력_가이드.md 맨 위 "변경 이력"</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.00500011" customWidth="1" min="1" max="1"/>
@@ -2932,6 +2969,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="8" t="n">
         <v>1</v>
@@ -5723,6 +5761,168 @@
       <c r="E121" s="27" t="inlineStr">
         <is>
           <t>근거 대상 대조 (v2.1, 2026-10-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B122" s="27" t="inlineStr">
+        <is>
+          <t>미션 카탈로그</t>
+        </is>
+      </c>
+      <c r="C122" s="27" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D122" s="27" t="inlineStr">
+        <is>
+          <t>"복약·측정" → "혈압 측정". 주 1회 상시 기록 → 시작·4주 재입력 때 입력(아침이나 저녁 중 편한 시간에 두 번 재서 평균)</t>
+        </is>
+      </c>
+      <c r="E122" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 (v2.2, 2026-10-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B123" s="27" t="inlineStr">
+        <is>
+          <t>미션 카탈로그</t>
+        </is>
+      </c>
+      <c r="C123" s="27" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D123" s="27" t="inlineStr">
+        <is>
+          <t>체중 관리 Backlog → WT-1 끼니마다 밥 2/3공기(BMI 25 이상) MVP</t>
+        </is>
+      </c>
+      <c r="E123" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 (v2.2, 2026-10-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B124" s="27" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-001</t>
+        </is>
+      </c>
+      <c r="C124" s="27" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D124" s="27" t="inlineStr">
+        <is>
+          <t>카테고리 5~6개·챌린지 30개 → 카테고리 7개·미션 10개</t>
+        </is>
+      </c>
+      <c r="E124" s="27" t="inlineStr">
+        <is>
+          <t>PR #38 리뷰 요청 반영 (v2.2, 2026-10-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B125" s="27" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-002</t>
+        </is>
+      </c>
+      <c r="C125" s="27" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D125" s="27" t="inlineStr">
+        <is>
+          <t>완료한 챌린지 후보 제외 → 이어서 고를 수 있음(완료함·축하 문구), 4사이클·완료 기준 80%</t>
+        </is>
+      </c>
+      <c r="E125" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 (v2.2, 2026-10-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B126" s="27" t="inlineStr">
+        <is>
+          <t>REQ-DASH-010</t>
+        </is>
+      </c>
+      <c r="C126" s="27" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="D126" s="27" t="inlineStr">
+        <is>
+          <t>혈압 점 = 시작·4주 재입력 값(주간 기록 없음)</t>
+        </is>
+      </c>
+      <c r="E126" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 (v2.2, 2026-10-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B127" s="27" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-007</t>
+        </is>
+      </c>
+      <c r="C127" s="27" t="inlineStr">
+        <is>
+          <t>안전성</t>
+        </is>
+      </c>
+      <c r="D127" s="27" t="inlineStr">
+        <is>
+          <t>복약 안내 기능 없음, 결과·추천 문구 규칙임을 명시</t>
+        </is>
+      </c>
+      <c r="E127" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 (v2.2, 2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7537,7 @@
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>카테고리는 5~6개, 전체 챌린지는 30개 내외. 설문에서 해당 없음으로 판정된 챌린지는 후보에서 제외한다. 추천 목록과 함께 제외된 미션과 그 이유도 보여준다. (PRD CH-02)</t>
+          <t>카테고리 7개(금연·절주·나트륨·신체 활동·외식·배달·아침 식사·체중 관리), 미션 10개(modeling/handoff/생활습관_입력_가이드.md §4). 설문에서 해당 없음으로 판정된 챌린지는 후보에서 제외한다. 추천 목록과 함께 제외된 미션과 그 이유도 보여준다. (PRD CH-02)</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
@@ -7379,7 +7579,7 @@
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>사용자는 4주 단위 챌린지 사이클을 시작할 수 있어야 하며, 완료한 챌린지는 다음 사이클 후보에서 제외되어야 한다.</t>
+          <t>사용자는 4주 단위 챌린지 사이클을 시작할 수 있어야 하며, 완료한 챌린지는 다음 사이클에서도 이어서 고를 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -7394,7 +7594,7 @@
       </c>
       <c r="I29" s="23" t="inlineStr">
         <is>
-          <t>사이클 시작일·종료일 저장. 진행 중 사이클은 1개. 완료 처리된 챌린지는 다음 사이클 후보 목록에서 선택 불가로 표시한다. 데모 시연은 사이클을 줄이지 않고 테스트 계정에 완주 이력을 미리 채워 대응한다.</t>
+          <t>사이클 시작일·종료일 저장. 진행 중 사이클은 1개. 프로그램은 4주 사이클 × 4번(16주). 사이클 종료 시 4주 달성률 80% 이상인 미션은 완료로 처리하고, 다음 사이클 후보에 "완료함" 표시와 축하·이어서 하기 문구를 함께 보여준다(습관 형성 중앙값 66일, modeling/handoff/생활습관_입력_가이드.md §3.4·B-21). 데모 시연은 사이클을 줄이지 않고 테스트 계정에 완주 이력을 미리 채워 대응한다.</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -8420,7 +8620,7 @@
       </c>
       <c r="I47" s="23" t="inlineStr">
         <is>
-          <t>기준선에 수치 라벨을 표기. 구간은 색상 외 텍스트를 병기(NFR-ACC-003).</t>
+          <t>기준선에 수치 라벨을 표기. 구간은 색상 외 텍스트를 병기(NFR-ACC-003). 혈압 점은 시작 입력과 4주 재입력 값(사이클마다 1개)이다. 주간 혈압 기록은 없다(modeling/handoff/생활습관_입력_가이드.md §5.3).</t>
         </is>
       </c>
       <c r="J47" s="23" t="inlineStr">
@@ -9332,7 +9532,7 @@
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>복약 응답자에게는 생활습관 개선 문구만 제시(NFR-SAFE-002 연계).</t>
+          <t>복약 응답자에게는 생활습관 개선 문구만 제시(NFR-SAFE-002 연계). 서비스에 복약 안내 기능은 없다. 이 규칙은 결과 화면·챌린지·추천 문구(LLM 생성 문구 포함)가 "약 대신 생활습관"처럼 복약 중단·감량으로 읽히지 않게 막는 문구 규칙이다.</t>
         </is>
       </c>
       <c r="J63" s="9" t="inlineStr">
@@ -12334,37 +12534,37 @@
     <row r="7">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>복약·측정</t>
+          <t>혈압 측정</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>복약 여부, 혈압 측정 가능 여부</t>
+          <t>혈압을 잴 수 있는 곳(집 혈압계 · 약국·보건소 · 어렵다)</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>측정 수단이 있으면 주 1회 혈압 기록 안내</t>
+          <t>모든 사용자: 시작할 때와 4주 재입력 때 혈압 입력</t>
         </is>
       </c>
       <c r="D7" s="25" t="inlineStr">
         <is>
-          <t>주 1회 같은 시간 혈압 기록</t>
+          <t>4주마다 혈압 입력 — 아침이나 저녁 중 편한 시간에, 의자에 앉아 1~2분 쉰 다음 1~2분 간격으로 두 번 재서 평균 저장</t>
         </is>
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>상시 기록 (3개 미션에 포함하지 않음)</t>
+          <t>4주 재입력 항목 (3개 미션에 포함하지 않음, 달성률에 넣지 않음)</t>
         </is>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>측정 기록</t>
+          <t>측정값 입력</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>의료 검토 후 확정</t>
+          <t>대한고혈압학회 가정혈압포럼 position statement (Ihm 등, Clin Hypertens 2022;28:38)</t>
         </is>
       </c>
       <c r="H7" s="25" t="inlineStr">
@@ -12381,22 +12581,22 @@
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>BMI, 최근 체중 변화, 야식</t>
+          <t>키·몸무게(BMI 계산, 화면 미표시), 허리둘레</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>추가 생활습관 후보</t>
+          <t>BMI 25 이상이면 추천 (대체 순서에는 없음)</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>야식 줄이기 등</t>
+          <t>끼니마다 밥 2/3공기(중, 주 5일)</t>
         </is>
       </c>
       <c r="E8" s="25" t="inlineStr">
         <is>
-          <t>선택 후보</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="F8" s="25" t="inlineStr">
@@ -12406,12 +12606,12 @@
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>MVP 제외</t>
+          <t>Neter 2003 Hypertension(1kg 감량당 수축기 −1.05mmHg), 대한비만학회 2022(BMI 25)</t>
         </is>
       </c>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>MVP</t>
         </is>
       </c>
     </row>

--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -2041,7 +2041,7 @@
       </c>
       <c r="D23" s="27" t="inlineStr">
         <is>
-          <t>혈압 = 시작·4주 재입력 때 입력(아침이나 저녁 중 편한 시간에 두 번 재서 평균, 학회 측정법), 카탈로그 "혈압 측정"으로 이름 변경, 완료한 챌린지 = 이어서 고를 수 있음(축하 문구), 체중 관리 WT-1 MVP, 카테고리 7개·미션 10개, 프로그램 4사이클(16주), NFR-SAFE-007 문구 규칙임을 명시</t>
+          <t>혈압 = 시작·4주 재입력 때 입력(아침이나 저녁 중 편한 시간에 두 번 재서 평균, 학회 측정법), 카탈로그 "혈압 측정"으로 이름 변경, 완료한 챌린지 = 이어서 고를 수 있음(축하 문구), 체중 관리 WT-1 MVP, 카테고리 7개·미션 10개, 프로그램 3사이클(12주), NFR-SAFE-007 문구 규칙임을 명시</t>
         </is>
       </c>
       <c r="E23" s="27" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="D125" s="27" t="inlineStr">
         <is>
-          <t>완료한 챌린지 후보 제외 → 이어서 고를 수 있음(완료함·축하 문구), 4사이클·완료 기준 80%</t>
+          <t>완료한 챌린지 후보 제외 → 이어서 고를 수 있음(완료함·축하 문구), 3사이클(12주)·완료 기준 80%</t>
         </is>
       </c>
       <c r="E125" s="27" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="I29" s="23" t="inlineStr">
         <is>
-          <t>사이클 시작일·종료일 저장. 진행 중 사이클은 1개. 프로그램은 4주 사이클 × 4번(16주). 사이클 종료 시 4주 달성률 80% 이상인 미션은 완료로 처리하고, 다음 사이클 후보에 "완료함" 표시와 축하·이어서 하기 문구를 함께 보여준다(습관 형성 중앙값 66일, modeling/handoff/생활습관_입력_가이드.md §3.4·B-21). 데모 시연은 사이클을 줄이지 않고 테스트 계정에 완주 이력을 미리 채워 대응한다.</t>
+          <t>사이클 시작일·종료일 저장. 진행 중 사이클은 1개. 프로그램은 4주 사이클 × 3번(12주, 84일). 사이클 종료 시 4주 달성률 80% 이상인 미션은 완료로 처리하고, 다음 사이클 후보에 "완료함" 표시와 축하·이어서 하기 문구를 함께 보여준다(습관 형성 중앙값 66일, modeling/handoff/생활습관_입력_가이드.md §3.4·B-21). 데모 시연은 사이클을 줄이지 않고 테스트 계정에 완주 이력을 미리 채워 대응한다.</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">

--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경 이력" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항 정의서" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문서 대조" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="미션 카탈로그" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지표 · 이벤트" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 흐름" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="평가기준 대응표" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ID Naming" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보류 · 결정 필요" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="개정이력" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변경 이력" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="요구사항 정의서" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="문서 대조" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="미션 카탈로그" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="지표 · 이벤트" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="화면 흐름" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="화면 목록" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="평가기준 대응표" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ID Naming" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="보류 · 결정 필요" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'요구사항 정의서'!$A$1:$K$101</definedName>
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2057,43 @@
       <c r="G23" s="27" t="inlineStr">
         <is>
           <t>상세: modeling/handoff/생활습관_입력_가이드.md 맨 위 "변경 이력"</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t>v2.3</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>모델 A 범주 정상·경계·위험(확률 % 비표시), 모델 B = 경계군과 닮은 정도, 카드 ② = 혈관 나이·실제 나이 비교, 잠정 모델 고지, HDL 필수, 설문 파생 가중치 피드백 보정</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-001·005·006, REQ-ELIG-002, REQ-DASH-001, REQ-HEALTH-002, NFR-SAFE-003·005, NFR-ML-007, NFR-OPS-004, NFR-FEED-002, 화면 목록 W06·W07·W11-2 수정. 모델 A v0.2.0(양호·주의·높음, 확률 % 참고 신호, 상위 %·혈관 나이 한국 기준), 모델 B 비교 3단계</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>모델 A v0.2.0 한국인 보정(10/20), 4차 멘토링(10/20) 확률 표시 허용·한계 명시, 결과 화면 정리(#185, 10/23)</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>확인 요청·체험 종료 후 항목 4건은 "보류 · 결정 필요" 시트</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.00500011" customWidth="1" min="1" max="1"/>
@@ -2566,6 +2603,274 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>W11-2</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>화면 목록</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>4주 비교</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>혈관 나이·요인 순위</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>표시 여부</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>4주 전·후 비교에 혈관 나이 전·후와 위험 요인 순위 변화 한 줄을 표시할지 정한다.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>진행하면 서버 비교 응답에 혈관 나이 전·후·요인 순위를 추가하고 4주 비교·12주 화면에 표시한다. 혈관 나이는 혈압 10mmHg 변화에도 2살 이상 움직이므로 변동 안내 문구를 함께 설계한다.</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>W11-2 4주 전 · 후 비교</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>체험 종료(10/25) 후 결정</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>백엔드 담당, 화면 담당</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>REQ-HEALTH-002, REQ-HEALTH-007</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>건강정보</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>입력 항목</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>공복혈당</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>수집 중단</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>공복혈당은 어떤 모델·추천 규칙에도 쓰지 않으므로 수집 항목과 확인 화면 지표에서 뺀다.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>입력 화면·확인 화면·내 데이터·마이페이지에서 칸을 없애고, 개인정보 수집 항목(동의서)에서 빼고 정책 버전을 올린다. 식약처 질의서 입력 목록도 맞춘다.</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>W04 건강정보 입력, W05 입력 검토</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>체험 종료(10/25) 후 진행</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>화면 담당, 동의·정책 담당</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>REQ-PRED-002</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>비동기 분석</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>작업 큐</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>동작 방식</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>문서는 작업 큐 접수(202)와 상태 조회를 전제로 하는데, 구현은 요청 즉시 계산해 결과를 돌려준다(201). 문서를 구현에 맞출지 정한다.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>구현에 맞추면 수용 기준을 "요청 즉시 계산해 201로 결과 반환, 실패 시 오류 사유 표시"로 바꾼다.</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>W05 입력 검토 · 분석 대기</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>확인 요청</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>백엔드 담당</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-001</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>안전성</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>결과 표현</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>위험 선별</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>면책 안내</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>예측 결과 화면(결과·홈·내 데이터·12주)과 예측 API 응답(disclaimer)에는 면책 문구가 있다. 4주 전·후 비교 화면, 내 변화 탭과 4주 비교 API 응답(챌린지 리뷰)에는 보이는 면책 문구가 없다(확률 근거 버튼 안에만 있음).</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>4주 비교·내 변화 화면에 면책 문구 한 줄을 추가하고, 챌린지 리뷰 응답에 disclaimer를 넣을지 정한다.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>W11-2 4주 전 · 후 비교, W11 추이 · 변화 추적</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>확인 요청</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>화면 담당, 백엔드 담당</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -2578,7 +2883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.00500011" customWidth="1" min="1" max="1"/>
@@ -2969,7 +3274,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="8" t="n">
         <v>1</v>
@@ -5923,6 +6227,330 @@
       <c r="E127" s="27" t="inlineStr">
         <is>
           <t>팀 결정 (v2.2, 2026-10-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B128" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-001</t>
+        </is>
+      </c>
+      <c r="C128" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D128" s="27" t="inlineStr">
+        <is>
+          <t>모델 A 범주 양호·주의·높음(JAS 2%·9%), 확률 %를 참고 신호로 표시 / 모델 B = 혈압이 정상인 사람들과 비교 3단계(판정 아님, 숫자 비표시)</t>
+        </is>
+      </c>
+      <c r="E128" s="27" t="inlineStr">
+        <is>
+          <t>모델 A v0.2.0·4차 멘토링 (v2.3, 2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B129" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-005</t>
+        </is>
+      </c>
+      <c r="C129" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D129" s="27" t="inlineStr">
+        <is>
+          <t>검사·상담 권고 조건 = 모델 A 높음 또는 입력 혈압 140/90 이상</t>
+        </is>
+      </c>
+      <c r="E129" s="27" t="inlineStr">
+        <is>
+          <t>모델 A v0.2.0·4차 멘토링 (v2.3, 2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B130" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-006</t>
+        </is>
+      </c>
+      <c r="C130" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D130" s="27" t="inlineStr">
+        <is>
+          <t>카드 ② 혈관 나이 + 같은 성별·연령대 상위 %·계산 근거, 카드 ③ 생활습관·체형 비교 3단계·비교 기준</t>
+        </is>
+      </c>
+      <c r="E130" s="27" t="inlineStr">
+        <is>
+          <t>모델 A v0.2.0·4차 멘토링 (v2.3, 2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B131" s="27" t="inlineStr">
+        <is>
+          <t>REQ-ELIG-002</t>
+        </is>
+      </c>
+      <c r="C131" s="27" t="inlineStr">
+        <is>
+          <t>이용 적합성</t>
+        </is>
+      </c>
+      <c r="D131" s="27" t="inlineStr">
+        <is>
+          <t>모델 A 제외 대상 = 관상동맥질환(협심증·심근경색) 진단자로 확정</t>
+        </is>
+      </c>
+      <c r="E131" s="27" t="inlineStr">
+        <is>
+          <t>모델 A v0.2.0·4차 멘토링 (v2.3, 2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B132" s="27" t="inlineStr">
+        <is>
+          <t>REQ-DASH-001</t>
+        </is>
+      </c>
+      <c r="C132" s="27" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="D132" s="27" t="inlineStr">
+        <is>
+          <t>위험 구간 이름 정상·경계·위험 → 양호·주의·높음</t>
+        </is>
+      </c>
+      <c r="E132" s="27" t="inlineStr">
+        <is>
+          <t>모델 A v0.2.0·4차 멘토링 (v2.3, 2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B133" s="27" t="inlineStr">
+        <is>
+          <t>REQ-HEALTH-002</t>
+        </is>
+      </c>
+      <c r="C133" s="27" t="inlineStr">
+        <is>
+          <t>건강정보</t>
+        </is>
+      </c>
+      <c r="D133" s="27" t="inlineStr">
+        <is>
+          <t>필수 항목에서 HDL콜레스테롤 삭제(입력 화면에서 받지 않음, 모델 미사용)</t>
+        </is>
+      </c>
+      <c r="E133" s="27" t="inlineStr">
+        <is>
+          <t>입력 화면·모델 입력과 대조 (v2.3, 2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B134" s="27" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-003</t>
+        </is>
+      </c>
+      <c r="C134" s="27" t="inlineStr">
+        <is>
+          <t>안전성</t>
+        </is>
+      </c>
+      <c r="D134" s="27" t="inlineStr">
+        <is>
+          <t>확률 단정 금지·범주만 표시 → 확률을 참고 신호로 표시하고 확률 근거에 계산 방식·기준·한계 명시</t>
+        </is>
+      </c>
+      <c r="E134" s="27" t="inlineStr">
+        <is>
+          <t>4차 멘토링(10/20) 확률 표시 허용·한계 명시 (v2.3, 2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B135" s="27" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-005</t>
+        </is>
+      </c>
+      <c r="C135" s="27" t="inlineStr">
+        <is>
+          <t>안전성</t>
+        </is>
+      </c>
+      <c r="D135" s="27" t="inlineStr">
+        <is>
+          <t>잠정 모델 고지 → 근거 버튼(확률 근거·계산 근거·비교 기준)으로 데이터 출처·보정 방식·한계 고지</t>
+        </is>
+      </c>
+      <c r="E135" s="27" t="inlineStr">
+        <is>
+          <t>학습 데이터 확정(모델 A·B v0.2.0) (v2.3, 2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B136" s="27" t="inlineStr">
+        <is>
+          <t>NFR-ML-007</t>
+        </is>
+      </c>
+      <c r="C136" s="27" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D136" s="27" t="inlineStr">
+        <is>
+          <t>모델 A v0.2.0 한국인 보정(Jee 2014 성별 절편), 상위 %·혈관 나이 기준 = 국민건강영양조사 2022~2024</t>
+        </is>
+      </c>
+      <c r="E136" s="27" t="inlineStr">
+        <is>
+          <t>모델 A v0.2.0·4차 멘토링 (v2.3, 2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B137" s="27" t="inlineStr">
+        <is>
+          <t>NFR-OPS-004</t>
+        </is>
+      </c>
+      <c r="C137" s="27" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D137" s="27" t="inlineStr">
+        <is>
+          <t>모델 변경 이력 기록 방식 = 예측별 모델 버전 저장 + 버전별 모델 파일 + 모델 개발 계획 변경 이력 표</t>
+        </is>
+      </c>
+      <c r="E137" s="27" t="inlineStr">
+        <is>
+          <t>구현 방식과 대조 (v2.3, 2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B138" s="27" t="inlineStr">
+        <is>
+          <t>NFR-FEED-002</t>
+        </is>
+      </c>
+      <c r="C138" s="27" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="D138" s="27" t="inlineStr">
+        <is>
+          <t>설문 파생 가중치를 피드백으로 보정 → 나트륨 지수는 근거 문헌 계산식을 그대로 쓰고 임의 보정하지 않음</t>
+        </is>
+      </c>
+      <c r="E138" s="27" t="inlineStr">
+        <is>
+          <t>설문은 모델 입력이 아님(v2.0), 검증된 계산식 유지 (v2.3, 2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B139" s="27" t="inlineStr">
+        <is>
+          <t>화면 목록</t>
+        </is>
+      </c>
+      <c r="C139" s="27" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="D139" s="27" t="inlineStr">
+        <is>
+          <t>W06 결과 구성, W07 진입 조건(모델 A 높음 또는 혈압 140/90 이상), W11-2 혈관 나이·요인 순위 변화는 보류로 이동</t>
+        </is>
+      </c>
+      <c r="E139" s="27" t="inlineStr">
+        <is>
+          <t>모델 A v0.2.0·4차 멘토링 (v2.3, 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -6511,7 +7139,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>기진단자에게 위험 확률을 생성·표시하지 않는다. 챌린지·대시보드는 계속 이용 가능. 고혈압 진단자와 혈압약 복용자는 모델 A 예측 대상이며(모델 B 결과는 생성하지 않음) 고혈압 진단·치료 상태는 모델 입력으로 수집한다. (심혈관질환 진단자 제외 범위는 모델 문서의 적용 대상 정의 확인 후 확정)</t>
+          <t>기진단자에게 위험 확률을 생성·표시하지 않는다. 챌린지·대시보드는 계속 이용 가능. 고혈압 진단자와 혈압약 복용자는 모델 A 예측 대상이며(모델 B 결과는 생성하지 않음) 고혈압 진단·치료 상태는 모델 입력으로 수집한다. 모델 A 제외 대상은 관상동맥질환(협심증·심근경색) 진단자로 확정.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -6724,7 +7352,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>사용자는 위험 예측 모델에 필요한 건강정보를 입력할 수 있어야 한다. 필수 항목은 수축기혈압·이완기혈압·신장·체중·허리둘레·흡연 여부(일반담배)·전자담배 사용 여부·음주 빈도·한 번 음주량(마시는 사람만)·당뇨병 여부·고혈압 진단·치료 상태(진단 없음 / 진단받았지만 약은 안 먹음 / 진단받았고 약을 먹는 중)·총콜레스테롤·HDL콜레스테롤·부모 고혈압 가족력이며, 선택 항목은 공복혈당이다. 나이·성별은 REQ-HEALTH-001의 프로필 정보를 그대로 참조한다.</t>
+          <t>사용자는 위험 예측 모델에 필요한 건강정보를 입력할 수 있어야 한다. 필수 항목은 수축기혈압·이완기혈압·신장·체중·허리둘레·흡연 여부(일반담배)·전자담배 사용 여부·음주 빈도·한 번 음주량(마시는 사람만)·당뇨병 여부·고혈압 진단·치료 상태(진단 없음 / 진단받았지만 약은 안 먹음 / 진단받았고 약을 먹는 중)·총콜레스테롤·부모 고혈압 가족력이며, 선택 항목은 공복혈당이다. 나이·성별은 REQ-HEALTH-001의 프로필 정보를 그대로 참조한다.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -7123,7 +7751,7 @@
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>사용자는 모델 A의 결과로 10년 내 관상동맥질환 발병 위험을, 모델 B의 결과로 현재 고혈압 경계군과 닮은 정도와 그에 기여한 요인을 확인할 수 있어야 한다.</t>
+          <t>사용자는 모델 A의 결과로 10년 내 심장 혈관 건강 신호(관상동맥질환 10년 위험 추정)를, 모델 B의 결과로 혈압이 정상인 사람들과 생활습관·체형이 얼마나 비슷한지를 확인할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -7138,7 +7766,7 @@
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>결과는 진단이 아닌 선별 정보. 위험 범주는 정상·경계·위험 3단계로 하고 색상(초록·노랑·빨강)과 텍스트를 함께 표시한다. 구간 기준은 모델 문서에 따른다. 정상은 추가 안내 없음, 경계는 기여 요인과 챌린지를 함께 제시, 위험은 REQ-PRED-005(검사·상담 안내)로 연결한다. 정상·경계·위험 3단계와 구간 기준은 모델 A 결과에 적용한다. 모델 B 결과는 판정이 아니라 기여 요인 설명과 챌린지 근거로 사용한다. 두 모델의 결과를 하나로 합산하지 않는다.</t>
+          <t>결과는 진단이 아닌 참고 정보. 모델 A는 한국인 기준으로 보정한 확률(%)을 "생활습관 관리용 참고 신호"로 표시하고, 범주는 양호(&lt;2%)·주의(2~9%)·높음(≥9%) 3단계(일본 동맥경화학회 JAS 2017 기준 참고)로 텍스트·아이콘·단계 막대와 함께 표시한다. 범주와 상관없이 바꿀 수 있는 요인과 관련 챌린지를 함께 안내하고, 높음은 REQ-PRED-005(검사·상담 안내)로 연결한다. 모델 B는 판정하지 않고 비슷한 편 / 조금 달라요 / 많이 달라요 3단계로만 표시하며 확률 숫자는 보여주지 않는다. 구간 기준은 모델 문서에 따른다. 두 모델의 결과를 하나로 합산하지 않는다.</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -7351,7 +7979,7 @@
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>위험 단계로 분류된 사용자는 의료기관 검사·상담 권고 안내를 확인할 수 있어야 한다.</t>
+          <t>모델 A가 높음(≥9%)이거나 입력 혈압이 140/90mmHg 이상인 사용자는 의료기관 검사·상담 권고 안내를 확인할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -7408,7 +8036,7 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>예측 결과는 카드 3개로 나누어 제시한다. 첫 번째 카드는 10년 내 관상동맥질환 발병 위험과 위험 구간, 두 번째 카드는 혈관 나이와 실제 나이 비교, 세 번째 카드는 모델 B의 현재 위험 프로필과 개선 가능 1위 요인을 담는다.</t>
+          <t>예측 결과는 카드 3개로 나누어 제시한다. 첫 번째 카드는 10년 내 심장 혈관 건강 신호(확률·범주)와 확률 근거, 두 번째 카드는 혈관 나이(추정)와 같은 성별·연령대 상위 %(참고용), 계산 근거, 세 번째 카드는 모델 B의 생활습관·체형 비교 3단계와 비교 기준을 담는다.</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -7423,7 +8051,7 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>카드를 하나의 종합 점수로 합치지 않는다. 혈관 나이는 추정치임을 함께 표기하고 NFR-SAFE-001을 따른다.</t>
+          <t>카드를 하나의 종합 점수로 합치지 않는다. 혈관 나이는 추정치임을 함께 표기하고 NFR-SAFE-001을 따른다. 혈관 나이와 상위 %의 기준은 국민건강영양조사 2022~2024 같은 성별·연령대 한국 성인이다.</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -8107,7 +8735,7 @@
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>대시보드에 표시하는 검진 지표는 1개(혈압). 측정 기준일과 면책 문구를 함께 표시. 위험 구간은 정상·경계·위험 3단계를 색상과 텍스트로 함께 제시한다(NFR-ACC-003).</t>
+          <t>대시보드에 표시하는 검진 지표는 1개(혈압). 측정 기준일과 면책 문구를 함께 표시. 위험 구간은 양호·주의·높음 3단계를 텍스트와 아이콘으로 함께 제시한다(NFR-ACC-003).</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
@@ -9118,7 +9746,7 @@
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>설문 응답에서 파생 피처를 만들 때 쓰는 가중치는 피드백과 실측 데이터로 보정할 수 있어야 한다.</t>
+          <t>설문 응답으로 만드는 파생 점수(나트륨 지수)는 근거 문헌의 계산식을 그대로 쓰고, 피드백으로 임의 보정하지 않는다.</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -9133,7 +9761,7 @@
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
-          <t>가중치를 코드가 아닌 설정으로 관리하고 변경 이력을 남긴다.</t>
+          <t>계산식과 출처를 modeling/handoff/생활습관_입력_가이드.md에 명시한다. 계산식을 바꿀 때는 근거 문헌을 갖추고 버전과 변경 이력을 남긴다.</t>
         </is>
       </c>
       <c r="J56" s="9" t="inlineStr">
@@ -9304,7 +9932,7 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>확률 단정 표현 금지. 범주형 위험 신호로 표시.</t>
+          <t>확률은 "생활습관 관리용 참고 신호"로 표시하고, 발병을 단정하는 표현("~에 걸릴 확률")은 쓰지 않는다. 확률 근거 버튼에 계산 방식(미국 Framingham 모델을 한국인 평균에 맞춰 보정)과 범주 기준(일본 동맥경화학회 참고), 진단을 대신하지 않음을 표시한다(4차 멘토링 2026-10-20 결정).</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
@@ -9403,7 +10031,7 @@
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>학습 데이터가 확정되기 전의 잠정 모델을 사용하는 동안에는 결과 화면에 그 사실을 고지해야 한다.</t>
+          <t>결과 화면은 모델의 데이터 출처·보정 방식·한계를 근거 버튼(확률 근거·계산 근거·비교 기준)으로 알리고, 진단을 대신하지 않음을 표시해야 한다.</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
@@ -9418,7 +10046,7 @@
       </c>
       <c r="I61" s="23" t="inlineStr">
         <is>
-          <t>결과 화면에 모델의 확정 여부를 표기한다. 확정 후 문구를 제거하는 절차를 정의한다.</t>
+          <t>모델 A 확률 카드에는 확률 근거, 혈관 나이 카드에는 계산 근거, 모델 B 카드에는 비교 기준 버튼을 둔다. 모델 버전이 바뀌면 근거 문구도 함께 갱신한다.</t>
         </is>
       </c>
       <c r="J61" s="23" t="inlineStr">
@@ -11356,7 +11984,7 @@
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
-          <t>변경 일시·변경자·사유를 기록. 과거 예측 결과에서 사용 버전을 역추적 가능.</t>
+          <t>예측마다 모델 코드·버전을 저장해 과거 결과의 사용 버전을 역추적할 수 있다. 계수 변경 이력은 버전별 모델 파일(modeling/model_a·model_b/artifacts)과 docs/모델_개발_계획_고혈압.md 변경 이력 표에 변경 일시·내용·근거로 기록하고, 변경자는 git 커밋 기록으로 확인한다.</t>
         </is>
       </c>
       <c r="J95" s="9" t="inlineStr">
@@ -11584,7 +12212,7 @@
       </c>
       <c r="I99" s="14" t="inlineStr">
         <is>
-          <t>모델 A는 Framingham Heart Study(미국, 코호트, 10년 후 CHD 예측), 모델 B는 국민건강영양조사 2022-2024(한국, 횡단면, 현재 경계군 여부 예측) 데이터셋을 사용한다. 두 모델의 학습 코드·아티팩트(모델 파일·스케일러)는 분리해 관리한다.</t>
+          <t>모델 A는 Framingham Heart Study(미국, 코호트, 10년 후 CHD 예측), 모델 B는 국민건강영양조사 2022-2024(한국, 횡단면, 현재 경계군 여부 예측) 데이터셋을 사용한다. 두 모델의 학습 코드·아티팩트(모델 파일·스케일러)는 분리해 관리한다. 모델 A v0.2.0은 Framingham 계수를 유지하고 성별 절편만 한국인 평균 10년 위험(Jee 2014, 남 1.03%·여 0.40%)에 맞춰 재보정했다. 같은 성별·연령대 상위 %와 혈관 나이의 기준은 국민건강영양조사 2022~2024 만 32~70세다.</t>
         </is>
       </c>
       <c r="J99" s="14" t="inlineStr">
@@ -14244,7 +14872,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>위험 범주 표시, 주요 기여 요인 목록(방향·중요도), 면책 문구</t>
+          <t>입력 혈압 판정, 심장 혈관 건강 신호(확률·범주·확률 근거), 혈관 나이(같은 성별·연령대 상위 %·계산 근거), 바꿀 수 있는 요인, 생활습관·체형 비교(3단계·비교 기준), 면책 문구</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14266,7 +14894,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>고위험 → 의료기관</t>
+          <t>모델 A 높음 또는 혈압 140/90 이상 → 의료기관</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -14406,7 +15034,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>시작·4주 후 위험도 비교, 혈관 나이 변화, 혈압 추이, 순위 변화 한 줄 해석, 다음 4주 챌린지 선택</t>
+          <t>시작·4주 후 심장 혈관 건강 신호·생활습관·체형 비교, 혈압·몸무게·허리둘레 변화, 미션 달성률·습관 변화, 다음 4주 챌린지 선택 (혈관 나이·요인 순위 변화는 보류 · 결정 필요 시트 참고)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">

--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -2661,7 +2661,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>김혜성</t>
+          <t>모델링 담당</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>김혜성</t>
+          <t>모델링 담당</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>김혜성</t>
+          <t>모델링 담당</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>김혜성</t>
+          <t>모델링 담당</t>
         </is>
       </c>
     </row>

--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -2857,7 +2857,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>확인 요청</t>
+          <t>체험 종료(10/25) 후 결정</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">

--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="개정이력" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변경 이력" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="요구사항 정의서" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="문서 대조" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="미션 카탈로그" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="지표 · 이벤트" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="화면 흐름" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="화면 목록" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="평가기준 대응표" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="ID Naming" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="보류 · 결정 필요" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경 이력" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요구사항 정의서" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문서 대조" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="미션 카탈로그" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지표 · 이벤트" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 흐름" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="평가기준 대응표" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ID Naming" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보류 · 결정 필요" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'요구사항 정의서'!$A$1:$K$101</definedName>
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2097,6 +2097,43 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>v2.4</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>커뮤니티·파이·파티·공통 챌린지·푸시·문의·공지·관리자 요구사항 없음 / 화면 목록이 W12까지 / 보류 항목 미반영 / 공복혈당 수집 / 예측 요청 작업 큐 서술 / 4주 비교·내 변화 화면 면책 문구 없음 / 만 14세 미만 법정대리인 동의 요구(서비스는 만 19세 이상으로 제한)</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>신규 요구사항 REQ-COMM-001~014, REQ-PIE-001~004, REQ-CHARA-001~003, REQ-PARTY-001~005, REQ-CCHAL-001~005, REQ-PUSH-001~007, REQ-INQ-001~004, REQ-NOTICE-001~002, REQ-CHAL-012·013, REQ-DASH-012·013, REQ-ADM-001~013 추가, 화면 목록에 W13~W23·A01~A04, ID Naming 접두사 10개 추가 / 보류 3건 반영: 공복혈당 수집 중단(REQ-HEALTH-002·007), 예측 요청은 즉시 계산·201 반환(REQ-PRED-002), W11·W11-2 면책 문구(NFR-SAFE-001), 보류 시트 3건 상태 '반영' / 법정대리인 동의 삭제 → 만 19세 이상 가입(REQ-CONSENT-003, REQ-USER-001, REQ-ELIG-001 수정)</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>지인 체험 배포(10/22) 이후 구현된 기능을 요구사항·와이어프레임(v6)에 맞춤, 1차 체험 종료(10/25) 후 결정 대기 항목 처리</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="inlineStr">
+        <is>
+          <t>이슬</t>
+        </is>
+      </c>
+      <c r="G25" s="27" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-011은 v1.5에서 삭제된 번호라 12주 요구사항은 012부터 사용. W11-2 혈관 나이·요인 순위 표시는 아직 결정 전이라 보류 시트에 남겨 둠</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2108,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.00500011" customWidth="1" min="1" max="1"/>
@@ -2504,6 +2541,176 @@
       <c r="C23" s="5" t="inlineStr">
         <is>
           <t>로그·상태 점검·배포</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>COMM</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>기능구분</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>커뮤니티 글·댓글·프로필·신고</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>PIE</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>기능구분</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>파이 적립·사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>CHARA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>기능구분</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>캐릭터 꾸미기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>PARTY</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>기능구분</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>챌린지 파티</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>CCHAL</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>기능구분</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>공통 챌린지</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>PUSH</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>기능구분</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>푸시 알림·리마인드</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>INQ</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>기능구분</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>1:1 문의·비회원 문의</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NOTICE</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>기능구분</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>기능구분</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>관리자 기능</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>관리자 화면 ID. A{2자리} (컴퓨터 화면)</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2930,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>체험 종료(10/25) 후 진행</t>
+          <t>반영 (v2.4)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -2790,7 +2997,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>확인 요청</t>
+          <t>반영 (v2.4)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -2857,7 +3064,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>체험 종료(10/25) 후 결정</t>
+          <t>반영 (v2.4)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -6566,7 +6773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.00500011" customWidth="1" min="1" max="1"/>
@@ -6683,7 +6890,7 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>성공 201. 중복 이메일 409. 비밀번호 정책 위반 시 필드별 오류 표시.</t>
+          <t>성공 201. 중복 이메일 409. 비밀번호 정책 위반 시 필드별 오류 표시. 만 19세 미만 생년월일은 403(AUTH_ADULT_ONLY).</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -6995,22 +7202,22 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>법정대리인</t>
+          <t>가입 연령</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>만 14세 미만</t>
+          <t>만 19세 이상</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>동의 확인</t>
+          <t>연령 확인</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>만 14세 미만 사용자는 법정대리인의 동의를 받아야 서비스 이용을 시작할 수 있어야 한다.</t>
+          <t>서비스는 만 19세 이상만 가입·이용할 수 있어야 한다. 만 19세 미만은 법정대리인 동의 절차 없이 가입하지 않는다.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -7025,7 +7232,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>생년월일로 만 14세 미만을 판별해 법정대리인 동의 단계를 노출. 법정대리인 동의 여부와 시각을 저장. 미동의 상태에서는 건강정보 입력 API 403. 동의 확인용으로 수집한 법정대리인 정보는 동의 목적 외로 쓰지 않으며, 동의가 확인되지 않으면 수집일로부터 5일 이내 파기. 근거: 개인정보보호법 제22조의2.</t>
+          <t>가입 화면에서 생년월일로 만 19세 미만이면 가입을 막고 '만 19세 이상만 가입할 수 있어요'를 안내한다. 가입 동의에 '[필수] 만 19세 이상입니다'를 둔다. 서버도 같은 기준으로 403(AUTH_ADULT_ONLY)을 반환한다. 이용약관과 같은 기준. 법정대리인 정보는 수집하지 않는다.</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -7082,7 +7289,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>범위 밖 연령은 예측을 생성하지 않고 사유를 안내. 적용 연령은 모델 문서와 일치. 연령으로 가입을 막지 않으며, 범위 밖 사용자도 챌린지·대시보드·기록은 그대로 이용한다. 빠지는 것은 위험 예측 기능뿐이다.</t>
+          <t>범위 밖 연령은 예측을 생성하지 않고 사유를 안내. 적용 연령은 모델 문서와 일치. 가입은 만 19세 이상만 가능하며(REQ-CONSENT-003), 모델 적용 범위(만 32~70세) 밖이어도 만 19세 이상이면 챌린지·대시보드·기록은 그대로 이용한다. 빠지는 것은 위험 예측 기능뿐이다.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -7352,7 +7559,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>사용자는 위험 예측 모델에 필요한 건강정보를 입력할 수 있어야 한다. 필수 항목은 수축기혈압·이완기혈압·신장·체중·허리둘레·흡연 여부(일반담배)·전자담배 사용 여부·음주 빈도·한 번 음주량(마시는 사람만)·당뇨병 여부·고혈압 진단·치료 상태(진단 없음 / 진단받았지만 약은 안 먹음 / 진단받았고 약을 먹는 중)·총콜레스테롤·부모 고혈압 가족력이며, 선택 항목은 공복혈당이다. 나이·성별은 REQ-HEALTH-001의 프로필 정보를 그대로 참조한다.</t>
+          <t>사용자는 위험 예측 모델에 필요한 건강정보를 입력할 수 있어야 한다. 필수 항목은 수축기혈압·이완기혈압·신장·체중·허리둘레·흡연 여부(일반담배)·전자담배 사용 여부·음주 빈도·한 번 음주량(마시는 사람만)·당뇨병 여부·고혈압 진단·치료 상태(진단 없음 / 진단받았지만 약은 안 먹음 / 진단받았고 약을 먹는 중)·총콜레스테롤·부모 고혈압 가족력이다. 공복혈당은 어떤 모델·추천 규칙에도 쓰지 않아 수집하지 않는다(v2.4). 나이·성별은 REQ-HEALTH-001의 프로필 정보를 그대로 참조한다.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -7637,7 +7844,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>사용자는 입력을 마친 뒤 적격성 판정 결과와 체질량지수·혈압·공복혈당·총콜레스테롤 4개 지표를 확인하고 수정할 수 있어야 한다.</t>
+          <t>사용자는 입력을 마친 뒤 적격성 판정 결과와 체질량지수·혈압·총콜레스테롤 3개 지표를 확인하고 수정할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -7808,7 +8015,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>예측 요청은 작업 큐에 접수되고 사용자는 대기·실행·완료·실패 상태를 조회할 수 있어야 한다.</t>
+          <t>예측 요청은 입력을 받는 즉시 계산해 결과를 돌려주고, 실패하면 사유를 보여 주며 다시 시도할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -7823,7 +8030,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>접수 202 + job_id 반환. 상태 조회 API 제공. 실패 시 재시도 가능 여부 표시.</t>
+          <t>요청 즉시 계산해 201로 결과 반환. 실패 시 오류 사유와 재시도 가능 여부 표시. (v2.4: 구현에 맞춤)</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -9818,12 +10025,12 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>결과가 표시되는 모든 화면·API 응답에 면책 문구 포함.</t>
+          <t>결과가 표시되는 모든 화면·API 응답에 면책 문구 포함. 4주 전·후 비교(W11-2)와 내 변화(W11) 화면에도 면책 문구 한 줄을 보여 준다(v2.4).</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>W06 예측 결과 · XAI 설명, W07 검사 · 상담 안내, W08 대시보드 (홈)</t>
+          <t>W06 예측 결과 · XAI 설명, W07 검사 · 상담 안내, W08 대시보드 (홈), W11 추이 · 변화 추적, W11-2 4주 전 · 후 비교</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
@@ -12449,6 +12656,3483 @@
         </is>
       </c>
       <c r="K103" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-001</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>피드</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>글 목록</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>최신·인기</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 커뮤니티 피드에서 다른 이용자가 올린 글을 최신순 또는 인기순으로 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H104" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>20개씩 더 보기. 화면 맨 위에서 아래로 당기면 새로고침. 인기순은 최근 일정 기간의 좋아요 순.</t>
+        </is>
+      </c>
+      <c r="J104" s="14" t="inlineStr">
+        <is>
+          <t>W13 커뮤니티 피드</t>
+        </is>
+      </c>
+      <c r="K104" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-002</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>피드</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>분류·검색</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
+        <is>
+          <t>칩·검색어</t>
+        </is>
+      </c>
+      <c r="F105" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 분류(식단·운동·챌린지 인증·고민과 꿀팁)를 고르거나 검색어로 글을 찾을 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G105" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H105" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I105" s="14" t="inlineStr">
+        <is>
+          <t>분류는 한 번에 하나만 켜진다. 결과가 없으면 '찾는 글이 없어요'를 보여 준다.</t>
+        </is>
+      </c>
+      <c r="J105" s="14" t="inlineStr">
+        <is>
+          <t>W13 커뮤니티 피드</t>
+        </is>
+      </c>
+      <c r="K105" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-003</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>글</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>글 상세</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="inlineStr">
+        <is>
+          <t>읽기·좋아요</t>
+        </is>
+      </c>
+      <c r="F106" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 글을 열어 읽고 좋아요를 누르거나 취소할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G106" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H106" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I106" s="14" t="inlineStr">
+        <is>
+          <t>한 사람이 글 하나에 좋아요 한 번. 글쓴이 아바타·닉네임을 누르면 프로필(W16)로 이동.</t>
+        </is>
+      </c>
+      <c r="J106" s="14" t="inlineStr">
+        <is>
+          <t>W13 커뮤니티 피드, W15 글 상세 · 댓글 · 답글 · 좋아요</t>
+        </is>
+      </c>
+      <c r="K106" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-004</t>
+        </is>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>글</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="inlineStr">
+        <is>
+          <t>글쓰기</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="inlineStr">
+        <is>
+          <t>분류·제목·본문·사진</t>
+        </is>
+      </c>
+      <c r="F107" s="14" t="inlineStr">
+        <is>
+          <t>닉네임이 있는 이용자는 분류·제목·본문을 적고 사진을 최대 3장 붙여 글을 올릴 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G107" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H107" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I107" s="14" t="inlineStr">
+        <is>
+          <t>제목·본문이 비면 올릴 수 없다. 닉네임이 없으면 닉네임 정하기로 이동(NICKNAME_REQUIRED). 사진은 올릴 때 자동 점검하고 걸리면 다시 고르게 안내한다.</t>
+        </is>
+      </c>
+      <c r="J107" s="14" t="inlineStr">
+        <is>
+          <t>W14 글쓰기</t>
+        </is>
+      </c>
+      <c r="K107" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-005</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>글</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="inlineStr">
+        <is>
+          <t>챌린지 붙이기</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="inlineStr">
+        <is>
+          <t>인증 카드</t>
+        </is>
+      </c>
+      <c r="F108" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 자신이 인증한 챌린지(고정·선택·파티·공통)를 글에 카드로 붙일 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G108" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H108" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I108" s="14" t="inlineStr">
+        <is>
+          <t>내가 인증한 챌린지만 붙일 수 있다. 카드에는 챌린지 이름과 인증 일수를 보여 준다.</t>
+        </is>
+      </c>
+      <c r="J108" s="14" t="inlineStr">
+        <is>
+          <t>W14 글쓰기, W15 글 상세 · 댓글 · 답글 · 좋아요</t>
+        </is>
+      </c>
+      <c r="K108" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-006</t>
+        </is>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C109" s="14" t="inlineStr">
+        <is>
+          <t>댓글</t>
+        </is>
+      </c>
+      <c r="D109" s="14" t="inlineStr">
+        <is>
+          <t>댓글·답글</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="inlineStr">
+        <is>
+          <t>작성·수정·삭제</t>
+        </is>
+      </c>
+      <c r="F109" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 글에 댓글을 달고 댓글에 답글을 한 단계까지 달 수 있으며 자기 댓글을 수정·삭제할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G109" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H109" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I109" s="14" t="inlineStr">
+        <is>
+          <t>답글에 단 답글은 원 댓글 아래로 붙는다. 답글이 달린 댓글을 지우면 '삭제된 댓글이에요'로 자리만 남기고 본문은 DB에서 비운다. 답글이 모두 사라지면 자리도 사라진다.</t>
+        </is>
+      </c>
+      <c r="J109" s="14" t="inlineStr">
+        <is>
+          <t>W15 글 상세 · 댓글 · 답글 · 좋아요</t>
+        </is>
+      </c>
+      <c r="K109" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-007</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="inlineStr">
+        <is>
+          <t>게시 안내</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="inlineStr">
+        <is>
+          <t>개인정보·사진 점검</t>
+        </is>
+      </c>
+      <c r="F110" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티는 건강정보와 개인정보를 올리지 않도록 안내하고, 사진은 얼굴·개인정보 가능성을 자동 점검해야 한다.</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H110" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I110" s="14" t="inlineStr">
+        <is>
+          <t>피드·글쓰기 화면에 안내 문구 표시. 점검에 걸린 사진은 올라가지 않고 이유와 함께 다른 사진으로 바꾸게 한다.</t>
+        </is>
+      </c>
+      <c r="J110" s="14" t="inlineStr">
+        <is>
+          <t>W13 커뮤니티 피드, W14 글쓰기</t>
+        </is>
+      </c>
+      <c r="K110" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-008</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="inlineStr">
+        <is>
+          <t>신고</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
+        <is>
+          <t>사유·자동 숨김</t>
+        </is>
+      </c>
+      <c r="F111" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 글·댓글을 신고할 수 있어야 하고, 신고가 쌓이면 운영자가 확인하기 전까지 자동으로 숨겨져야 한다.</t>
+        </is>
+      </c>
+      <c r="G111" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H111" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I111" s="14" t="inlineStr">
+        <is>
+          <t>사유: 건강정보·개인정보 / 광고·스팸 / 욕설·비방 / 기타. 신고한 글·댓글은 내 화면에서 바로 빠진다. 서로 다른 신고자 3명 이상이면 자동 숨김.</t>
+        </is>
+      </c>
+      <c r="J111" s="14" t="inlineStr">
+        <is>
+          <t>W15 글 상세 · 댓글 · 답글 · 좋아요</t>
+        </is>
+      </c>
+      <c r="K111" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-009</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>댓글</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t>댓글 좋아요</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t>누르기·취소</t>
+        </is>
+      </c>
+      <c r="F112" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 댓글에 좋아요를 누르거나 취소할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G112" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H112" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I112" s="14" t="inlineStr">
+        <is>
+          <t>한 사람이 댓글 하나에 한 번. 내 댓글에도 누를 수 있다. 삭제·숨김 댓글에는 누를 수 없다.</t>
+        </is>
+      </c>
+      <c r="J112" s="14" t="inlineStr">
+        <is>
+          <t>W15 글 상세 · 댓글 · 답글 · 좋아요</t>
+        </is>
+      </c>
+      <c r="K112" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-010</t>
+        </is>
+      </c>
+      <c r="B113" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>글</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>내 글 관리</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t>삭제·숨김 안내</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
+        <is>
+          <t>글쓴이는 자기 글을 삭제할 수 있어야 하고, 운영 정책으로 숨겨진 글은 글쓴이에게만 안내와 함께 보여야 한다.</t>
+        </is>
+      </c>
+      <c r="G113" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H113" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I113" s="14" t="inlineStr">
+        <is>
+          <t>숨김 글은 다른 사람에게 보이지 않고 글쓴이에게는 숨김 안내를 보여 준다.</t>
+        </is>
+      </c>
+      <c r="J113" s="14" t="inlineStr">
+        <is>
+          <t>W13 커뮤니티 피드, W15 글 상세 · 댓글 · 답글 · 좋아요</t>
+        </is>
+      </c>
+      <c r="K113" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-011</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>프로필</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t>사람 프로필</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>글·댓글 보기</t>
+        </is>
+      </c>
+      <c r="F114" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 다른 이용자의 프로필에서 캐릭터·닉네임·인기도와 쓴 글·댓글(각 최근 20개)을 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G114" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H114" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I114" s="14" t="inlineStr">
+        <is>
+          <t>글 탭·댓글 탭 개수 표시. 글·댓글을 누르면 해당 글(댓글은 그 댓글 위치)로 이동. 닉네임이 바뀌면 예전 주소는 열리지 않는다.</t>
+        </is>
+      </c>
+      <c r="J114" s="14" t="inlineStr">
+        <is>
+          <t>W16 사람 프로필 · 인기도</t>
+        </is>
+      </c>
+      <c r="K114" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-012</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>프로필</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="inlineStr">
+        <is>
+          <t>인기도</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
+        <is>
+          <t>하트 주기</t>
+        </is>
+      </c>
+      <c r="F115" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 다른 이용자에게 인기도 하트를 줄 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G115" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H115" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I115" s="14" t="inlineStr">
+        <is>
+          <t>한 사람이 여러 사람에게 각각 한 번씩, 같은 사람에게는 한 번만. 취소할 수 없다(누르기 전 확인). 내 프로필에는 줄 수 없다. 닉네임이 없으면 줄 수 없다.</t>
+        </is>
+      </c>
+      <c r="J115" s="14" t="inlineStr">
+        <is>
+          <t>W16 사람 프로필 · 인기도</t>
+        </is>
+      </c>
+      <c r="K115" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-013</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>프로필</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>노출 제외</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>숨김·신고·파티</t>
+        </is>
+      </c>
+      <c r="F116" s="14" t="inlineStr">
+        <is>
+          <t>프로필의 글·댓글 목록에서는 운영팀이 숨긴 것, 내가 신고한 것, 파티 안 글을 빼야 한다.</t>
+        </is>
+      </c>
+      <c r="G116" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H116" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I116" s="14" t="inlineStr">
+        <is>
+          <t>세 가지 모두 목록과 개수에서 제외된다.</t>
+        </is>
+      </c>
+      <c r="J116" s="14" t="inlineStr">
+        <is>
+          <t>W16 사람 프로필 · 인기도</t>
+        </is>
+      </c>
+      <c r="K116" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="13" t="inlineStr">
+        <is>
+          <t>REQ-COMM-014</t>
+        </is>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>닉네임</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="inlineStr">
+        <is>
+          <t>닉네임 정하기</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t>중복 확인</t>
+        </is>
+      </c>
+      <c r="F117" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 커뮤니티에서 쓸 닉네임을 정할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G117" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H117" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I117" s="14" t="inlineStr">
+        <is>
+          <t>닉네임은 중복될 수 없다. 처음 정할 때만 파이 10개를 준다(REQ-PIE-001). 닉네임이 없으면 글쓰기·댓글·좋아요·파티·공통 챌린지를 쓸 수 없다.</t>
+        </is>
+      </c>
+      <c r="J117" s="14" t="inlineStr">
+        <is>
+          <t>W17 닉네임 정하기 · 캐릭터 꾸미기</t>
+        </is>
+      </c>
+      <c r="K117" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PIE-001</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>파이</t>
+        </is>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>적립</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="inlineStr">
+        <is>
+          <t>지급 규칙</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t>활동 보상</t>
+        </is>
+      </c>
+      <c r="F118" s="14" t="inlineStr">
+        <is>
+          <t>서비스는 활동에 따라 파이를 적립해야 한다.</t>
+        </is>
+      </c>
+      <c r="G118" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H118" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I118" s="14" t="inlineStr">
+        <is>
+          <t>오늘 미션 모두 완료 하루 한 번 +5, 5일 연속 +10, 4주 완주 1·2·3차 각 +50, 공통 챌린지 1위 300·2위 200·3위 100·완주 20, 파티 전원 인증 +3, 글쓰기 하루 3번까지 +2, 닉네임 처음 정하기 +10. 같은 일로 두 번 적립되지 않는다(회원·이유·기준 번호 중복 방지).</t>
+        </is>
+      </c>
+      <c r="J118" s="14" t="inlineStr">
+        <is>
+          <t>W14 글쓰기, W18 파이</t>
+        </is>
+      </c>
+      <c r="K118" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PIE-002</t>
+        </is>
+      </c>
+      <c r="B119" s="14" t="inlineStr">
+        <is>
+          <t>파이</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="inlineStr">
+        <is>
+          <t>캐릭터 상점</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="F119" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 파이로 캐릭터 아이템을 살 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G119" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H119" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I119" s="14" t="inlineStr">
+        <is>
+          <t>고른 유료 아이템 값이 내 파이보다 크면 '파이가 N개 모자라요'로 저장이 막힌다. 구매는 마이너스 내역으로 남고 이미 산 아이템은 다시 사지 않는다.</t>
+        </is>
+      </c>
+      <c r="J119" s="14" t="inlineStr">
+        <is>
+          <t>W17 닉네임 정하기 · 캐릭터 꾸미기, W18 파이</t>
+        </is>
+      </c>
+      <c r="K119" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PIE-003</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
+        <is>
+          <t>파이</t>
+        </is>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>조회</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="inlineStr">
+        <is>
+          <t>잔액·내역</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t>최근 내역</t>
+        </is>
+      </c>
+      <c r="F120" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 내 파이 잔액과 최근 내역(이유·증감)을 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G120" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H120" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I120" s="14" t="inlineStr">
+        <is>
+          <t>내역은 더 보기로 이어서 본다. 현금으로 바꿀 수 없다는 안내를 보여 준다. 건강정보 동의를 철회하면 파이·배지·파티 기록이 지워진다.</t>
+        </is>
+      </c>
+      <c r="J120" s="14" t="inlineStr">
+        <is>
+          <t>W18 파이</t>
+        </is>
+      </c>
+      <c r="K120" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PIE-004</t>
+        </is>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>파이</t>
+        </is>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>적립</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="inlineStr">
+        <is>
+          <t>가입 감사 선물</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="inlineStr">
+        <is>
+          <t>기간 한정</t>
+        </is>
+      </c>
+      <c r="F121" s="14" t="inlineStr">
+        <is>
+          <t>지정한 기간에 가입한 이용자는 감사 선물 파이를 한 번 받을 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G121" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H121" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I121" s="14" t="inlineStr">
+        <is>
+          <t>10/22~23 가입자가 홈·공지사항의 '파이 받기' 카드에서 200파이를 한 번 받는다. 기한(10/25) 뒤에는 받을 수 없다.</t>
+        </is>
+      </c>
+      <c r="J121" s="14" t="inlineStr">
+        <is>
+          <t>W18 파이</t>
+        </is>
+      </c>
+      <c r="K121" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CHARA-001</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="inlineStr">
+        <is>
+          <t>캐릭터</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>꾸미기</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="inlineStr">
+        <is>
+          <t>6개 부분</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t>몸체·색·눈 색·표정·얼굴·머리</t>
+        </is>
+      </c>
+      <c r="F122" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 캐릭터의 몸체·색·눈 색·표정·얼굴·머리를 골라 꾸밀 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G122" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H122" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I122" s="14" t="inlineStr">
+        <is>
+          <t>아이템마다 '기본'(무료) 또는 파이 가격을 보여 준다. 고른 모습은 미리보기에 바로 반영된다.</t>
+        </is>
+      </c>
+      <c r="J122" s="14" t="inlineStr">
+        <is>
+          <t>W17 닉네임 정하기 · 캐릭터 꾸미기</t>
+        </is>
+      </c>
+      <c r="K122" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CHARA-002</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
+        <is>
+          <t>캐릭터</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>꾸미기</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="inlineStr">
+        <is>
+          <t>눈 색</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t>8가지</t>
+        </is>
+      </c>
+      <c r="F123" s="14" t="inlineStr">
+        <is>
+          <t>눈 색은 8가지를 제공한다.</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H123" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I123" s="14" t="inlineStr">
+        <is>
+          <t>검정·파랑·초록·갈색·보라는 무료, 빨강·분홍·금색은 10파이. 눈 색은 눈에만 적용된다.</t>
+        </is>
+      </c>
+      <c r="J123" s="14" t="inlineStr">
+        <is>
+          <t>W17 닉네임 정하기 · 캐릭터 꾸미기</t>
+        </is>
+      </c>
+      <c r="K123" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CHARA-003</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
+        <is>
+          <t>캐릭터</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>노출</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="inlineStr">
+        <is>
+          <t>캐릭터 표시</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>피드·댓글·프로필·파티</t>
+        </is>
+      </c>
+      <c r="F124" s="14" t="inlineStr">
+        <is>
+          <t>내 캐릭터는 피드·댓글·프로필·파티원 목록에서 같은 모습으로 보여야 한다.</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H124" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I124" s="14" t="inlineStr">
+        <is>
+          <t>닉네임으로 그 사람의 캐릭터를 불러온다.</t>
+        </is>
+      </c>
+      <c r="J124" s="14" t="inlineStr">
+        <is>
+          <t>W13 커뮤니티 피드, W16 사람 프로필 · 인기도, W17 닉네임 정하기 · 캐릭터 꾸미기, W19 챌린지 파티</t>
+        </is>
+      </c>
+      <c r="K124" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PARTY-001</t>
+        </is>
+      </c>
+      <c r="B125" s="14" t="inlineStr">
+        <is>
+          <t>파티</t>
+        </is>
+      </c>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>만들기</t>
+        </is>
+      </c>
+      <c r="D125" s="14" t="inlineStr">
+        <is>
+          <t>파티 만들기</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>이름·소개·챌린지</t>
+        </is>
+      </c>
+      <c r="F125" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 파티를 만들 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H125" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t>파티 이름 2~12자, 한 줄 소개(선택), 파티 챌린지 선택(흡연·음주 제외), 파티장 포함 최대 6명. 한 사람당 파티 하나.</t>
+        </is>
+      </c>
+      <c r="J125" s="14" t="inlineStr">
+        <is>
+          <t>W19 챌린지 파티</t>
+        </is>
+      </c>
+      <c r="K125" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PARTY-002</t>
+        </is>
+      </c>
+      <c r="B126" s="14" t="inlineStr">
+        <is>
+          <t>파티</t>
+        </is>
+      </c>
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>참여</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="inlineStr">
+        <is>
+          <t>초대 코드</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr">
+        <is>
+          <t>코드 입력</t>
+        </is>
+      </c>
+      <c r="F126" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 초대 코드를 입력해 파티에 들어갈 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H126" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I126" s="14" t="inlineStr">
+        <is>
+          <t>초대 코드를 아는 사람만 들어올 수 있다. 이미 파티가 있으면 PARTY_ALREADY_JOINED, 코드 오류·인원 초과는 안내 후 다시 입력.</t>
+        </is>
+      </c>
+      <c r="J126" s="14" t="inlineStr">
+        <is>
+          <t>W19 챌린지 파티</t>
+        </is>
+      </c>
+      <c r="K126" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PARTY-003</t>
+        </is>
+      </c>
+      <c r="B127" s="14" t="inlineStr">
+        <is>
+          <t>파티</t>
+        </is>
+      </c>
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>현황</t>
+        </is>
+      </c>
+      <c r="D127" s="14" t="inlineStr">
+        <is>
+          <t>파티원 인증 현황</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="inlineStr">
+        <is>
+          <t>오늘 완료·연속</t>
+        </is>
+      </c>
+      <c r="F127" s="14" t="inlineStr">
+        <is>
+          <t>파티원은 파티원별 오늘 인증 여부와 파티 연속 인증 일수를 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H127" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I127" s="14" t="inlineStr">
+        <is>
+          <t>오늘 완료 인원, 파티 연속 인증 일수, 파티원별 완료·미완료와 진행 일수를 보여 준다. 파티 나가기는 확인창을 거친다.</t>
+        </is>
+      </c>
+      <c r="J127" s="14" t="inlineStr">
+        <is>
+          <t>W19 챌린지 파티</t>
+        </is>
+      </c>
+      <c r="K127" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PARTY-004</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="inlineStr">
+        <is>
+          <t>파티</t>
+        </is>
+      </c>
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>보상</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="inlineStr">
+        <is>
+          <t>전원 인증</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
+        <is>
+          <t>파이 +3</t>
+        </is>
+      </c>
+      <c r="F128" s="14" t="inlineStr">
+        <is>
+          <t>파티원 모두가 그날 인증하면 파티원 각자에게 파이를 주고 파티 연속 인증을 이어 가야 한다.</t>
+        </is>
+      </c>
+      <c r="G128" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H128" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I128" s="14" t="inlineStr">
+        <is>
+          <t>하루 한 번 +3. 전원이 인증하지 못한 날은 연속 인증이 끊긴다.</t>
+        </is>
+      </c>
+      <c r="J128" s="14" t="inlineStr">
+        <is>
+          <t>W19 챌린지 파티</t>
+        </is>
+      </c>
+      <c r="K128" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PARTY-005</t>
+        </is>
+      </c>
+      <c r="B129" s="14" t="inlineStr">
+        <is>
+          <t>파티</t>
+        </is>
+      </c>
+      <c r="C129" s="14" t="inlineStr">
+        <is>
+          <t>피드</t>
+        </is>
+      </c>
+      <c r="D129" s="14" t="inlineStr">
+        <is>
+          <t>파티 피드</t>
+        </is>
+      </c>
+      <c r="E129" s="14" t="inlineStr">
+        <is>
+          <t>파티원 전용 글</t>
+        </is>
+      </c>
+      <c r="F129" s="14" t="inlineStr">
+        <is>
+          <t>파티원은 파티원에게만 보이는 글을 쓰고 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G129" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H129" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I129" s="14" t="inlineStr">
+        <is>
+          <t>파티 글은 전체 피드·프로필에 나오지 않는다. 파티가 없어지면 파티 글과 좋아요·댓글·신고도 함께 지워진다.</t>
+        </is>
+      </c>
+      <c r="J129" s="14" t="inlineStr">
+        <is>
+          <t>W19 챌린지 파티</t>
+        </is>
+      </c>
+      <c r="K129" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CCHAL-001</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="inlineStr">
+        <is>
+          <t>공통 챌린지</t>
+        </is>
+      </c>
+      <c r="C130" s="14" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>목록·상태</t>
+        </is>
+      </c>
+      <c r="E130" s="14" t="inlineStr">
+        <is>
+          <t>진행 중·예정·종료</t>
+        </is>
+      </c>
+      <c r="F130" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 모두가 함께하는 공통 챌린지 목록을 상태별로 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G130" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H130" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I130" s="14" t="inlineStr">
+        <is>
+          <t>제목·기간·참가 인원·인증 방식·내 순위를 보여 준다.</t>
+        </is>
+      </c>
+      <c r="J130" s="14" t="inlineStr">
+        <is>
+          <t>W20 공통 챌린지</t>
+        </is>
+      </c>
+      <c r="K130" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CCHAL-002</t>
+        </is>
+      </c>
+      <c r="B131" s="14" t="inlineStr">
+        <is>
+          <t>공통 챌린지</t>
+        </is>
+      </c>
+      <c r="C131" s="14" t="inlineStr">
+        <is>
+          <t>참여</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>참여하기</t>
+        </is>
+      </c>
+      <c r="E131" s="14" t="inlineStr">
+        <is>
+          <t>닉네임 필요</t>
+        </is>
+      </c>
+      <c r="F131" s="14" t="inlineStr">
+        <is>
+          <t>닉네임이 있는 이용자는 공통 챌린지에 참여할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H131" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I131" s="14" t="inlineStr">
+        <is>
+          <t>닉네임이 없으면 닉네임 정하기로 이동. 건강정보 동의를 철회하면 참여·인증이 막힌다.</t>
+        </is>
+      </c>
+      <c r="J131" s="14" t="inlineStr">
+        <is>
+          <t>W20 공통 챌린지</t>
+        </is>
+      </c>
+      <c r="K131" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CCHAL-003</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="inlineStr">
+        <is>
+          <t>공통 챌린지</t>
+        </is>
+      </c>
+      <c r="C132" s="14" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>하루 인증</t>
+        </is>
+      </c>
+      <c r="E132" s="14" t="inlineStr">
+        <is>
+          <t>걸음 수·직접</t>
+        </is>
+      </c>
+      <c r="F132" s="14" t="inlineStr">
+        <is>
+          <t>참여자는 기간 중 하루에 한 번 인증할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G132" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H132" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I132" s="14" t="inlineStr">
+        <is>
+          <t>걸음 수 방식은 하루 목표 걸음 수 이상일 때 인증, 직접 방식은 버튼 한 번. 기간이 지나면 인증 버튼이 꺼진다.</t>
+        </is>
+      </c>
+      <c r="J132" s="14" t="inlineStr">
+        <is>
+          <t>W20 공통 챌린지</t>
+        </is>
+      </c>
+      <c r="K132" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CCHAL-004</t>
+        </is>
+      </c>
+      <c r="B133" s="14" t="inlineStr">
+        <is>
+          <t>공통 챌린지</t>
+        </is>
+      </c>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>순위·보상</t>
+        </is>
+      </c>
+      <c r="E133" s="14" t="inlineStr">
+        <is>
+          <t>인증 일수 기준</t>
+        </is>
+      </c>
+      <c r="F133" s="14" t="inlineStr">
+        <is>
+          <t>순위는 인증한 일수로만 정하고 순위·완주에 따라 파이를 줘야 한다.</t>
+        </is>
+      </c>
+      <c r="G133" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H133" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I133" s="14" t="inlineStr">
+        <is>
+          <t>1위 300·2위 200·3위 100·완주 20(최대 +300). 완주 기준은 따로 정하지 않으면 전체 일수의 70%. 순위 확정 전에는 '순위 확정을 기다리고 있어요'를 보여 준다.</t>
+        </is>
+      </c>
+      <c r="J133" s="14" t="inlineStr">
+        <is>
+          <t>W20 공통 챌린지</t>
+        </is>
+      </c>
+      <c r="K133" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CCHAL-005</t>
+        </is>
+      </c>
+      <c r="B134" s="14" t="inlineStr">
+        <is>
+          <t>공통 챌린지</t>
+        </is>
+      </c>
+      <c r="C134" s="14" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D134" s="14" t="inlineStr">
+        <is>
+          <t>개설·확정</t>
+        </is>
+      </c>
+      <c r="E134" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F134" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 공통 챌린지를 열고, 끝난 뒤 순위를 확정해 보상을 줄 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G134" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H134" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I134" s="14" t="inlineStr">
+        <is>
+          <t>시작한 뒤에는 기간·인증 방식을 바꿀 수 없다. 순위 확정은 되돌릴 수 없고 확정하면 파이가 바로 지급된다.</t>
+        </is>
+      </c>
+      <c r="J134" s="14" t="inlineStr">
+        <is>
+          <t>W20 공통 챌린지, A04 관리자 · 공통 챌린지 · 테스트 계정 삭제</t>
+        </is>
+      </c>
+      <c r="K134" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PUSH-001</t>
+        </is>
+      </c>
+      <c r="B135" s="14" t="inlineStr">
+        <is>
+          <t>푸시 알림</t>
+        </is>
+      </c>
+      <c r="C135" s="14" t="inlineStr">
+        <is>
+          <t>구독</t>
+        </is>
+      </c>
+      <c r="D135" s="14" t="inlineStr">
+        <is>
+          <t>알림 켜기·끄기</t>
+        </is>
+      </c>
+      <c r="E135" s="14" t="inlineStr">
+        <is>
+          <t>기기 구독</t>
+        </is>
+      </c>
+      <c r="F135" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 이 기기에서 푸시 알림을 켜고 끌 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G135" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H135" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I135" s="14" t="inlineStr">
+        <is>
+          <t>알림 받기 스위치. 아이폰은 홈 화면에 추가한 앱에서만, 안드로이드는 크롬에서 켠다. 카카오톡 등 앱 안 브라우저·차단 상태·미지원 브라우저는 안내를 보여 준다. 건강정보 동의를 철회하면 구독이 바로 지워진다.</t>
+        </is>
+      </c>
+      <c r="J135" s="14" t="inlineStr">
+        <is>
+          <t>W13 커뮤니티 피드, W22 알림 설정 · 더보기</t>
+        </is>
+      </c>
+      <c r="K135" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PUSH-002</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="inlineStr">
+        <is>
+          <t>푸시 알림</t>
+        </is>
+      </c>
+      <c r="C136" s="14" t="inlineStr">
+        <is>
+          <t>종류</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="inlineStr">
+        <is>
+          <t>댓글·답글·좋아요</t>
+        </is>
+      </c>
+      <c r="E136" s="14" t="inlineStr">
+        <is>
+          <t>반응 알림</t>
+        </is>
+      </c>
+      <c r="F136" s="14" t="inlineStr">
+        <is>
+          <t>내 글에 댓글·좋아요가 달리면 글쓴이에게, 내 댓글에 답글이 달리면 원 댓글 쓴 사람에게 알려야 한다.</t>
+        </is>
+      </c>
+      <c r="G136" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I136" s="14" t="inlineStr">
+        <is>
+          <t>본인이 한 일은 본인에게 보내지 않는다. 알림에는 댓글 내용을 넣지 않는다(잠금 화면 노출 방지). 알림에서 오면 그 댓글 위치로 이동해 잠깐 강조한다.</t>
+        </is>
+      </c>
+      <c r="J136" s="14" t="inlineStr">
+        <is>
+          <t>W15 글 상세 · 댓글 · 답글 · 좋아요, W22 알림 설정 · 더보기</t>
+        </is>
+      </c>
+      <c r="K136" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PUSH-003</t>
+        </is>
+      </c>
+      <c r="B137" s="14" t="inlineStr">
+        <is>
+          <t>푸시 알림</t>
+        </is>
+      </c>
+      <c r="C137" s="14" t="inlineStr">
+        <is>
+          <t>종류</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>문의 답변</t>
+        </is>
+      </c>
+      <c r="E137" s="14" t="inlineStr">
+        <is>
+          <t>답변 도착</t>
+        </is>
+      </c>
+      <c r="F137" s="14" t="inlineStr">
+        <is>
+          <t>남긴 문의에 답변이 달리면 문의한 이용자에게 알려야 한다.</t>
+        </is>
+      </c>
+      <c r="G137" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H137" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I137" s="14" t="inlineStr">
+        <is>
+          <t>알림에는 답변 내용을 넣지 않는다. 더보기·문의 목록에 '새 답변'을 표시한다.</t>
+        </is>
+      </c>
+      <c r="J137" s="14" t="inlineStr">
+        <is>
+          <t>W21 1:1 문의 · 비회원 문의 · 공지사항, W22 알림 설정 · 더보기</t>
+        </is>
+      </c>
+      <c r="K137" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PUSH-004</t>
+        </is>
+      </c>
+      <c r="B138" s="14" t="inlineStr">
+        <is>
+          <t>푸시 알림</t>
+        </is>
+      </c>
+      <c r="C138" s="14" t="inlineStr">
+        <is>
+          <t>종류</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="inlineStr">
+        <is>
+          <t>파티</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="inlineStr">
+        <is>
+          <t>새 멤버</t>
+        </is>
+      </c>
+      <c r="F138" s="14" t="inlineStr">
+        <is>
+          <t>파티에 새 멤버가 들어오면 이미 있던 파티원에게 알려야 한다.</t>
+        </is>
+      </c>
+      <c r="G138" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H138" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I138" s="14" t="inlineStr">
+        <is>
+          <t>새로 들어온 본인은 제외한다.</t>
+        </is>
+      </c>
+      <c r="J138" s="14" t="inlineStr">
+        <is>
+          <t>W19 챌린지 파티, W22 알림 설정 · 더보기</t>
+        </is>
+      </c>
+      <c r="K138" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PUSH-005</t>
+        </is>
+      </c>
+      <c r="B139" s="14" t="inlineStr">
+        <is>
+          <t>푸시 알림</t>
+        </is>
+      </c>
+      <c r="C139" s="14" t="inlineStr">
+        <is>
+          <t>종류</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="inlineStr">
+        <is>
+          <t>인기도</t>
+        </is>
+      </c>
+      <c r="E139" s="14" t="inlineStr">
+        <is>
+          <t>하트 받음</t>
+        </is>
+      </c>
+      <c r="F139" s="14" t="inlineStr">
+        <is>
+          <t>누군가 처음 인기도 하트를 주면 받는 사람에게 알려야 한다.</t>
+        </is>
+      </c>
+      <c r="G139" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H139" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I139" s="14" t="inlineStr">
+        <is>
+          <t>처음 줄 때만 알린다(취소가 없다). 설정은 '댓글·답글·좋아요'에 묶인다.</t>
+        </is>
+      </c>
+      <c r="J139" s="14" t="inlineStr">
+        <is>
+          <t>W16 사람 프로필 · 인기도, W22 알림 설정 · 더보기</t>
+        </is>
+      </c>
+      <c r="K139" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PUSH-006</t>
+        </is>
+      </c>
+      <c r="B140" s="14" t="inlineStr">
+        <is>
+          <t>푸시 알림</t>
+        </is>
+      </c>
+      <c r="C140" s="14" t="inlineStr">
+        <is>
+          <t>리마인드</t>
+        </is>
+      </c>
+      <c r="D140" s="14" t="inlineStr">
+        <is>
+          <t>저녁 8시</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="inlineStr">
+        <is>
+          <t>오늘 기록 전</t>
+        </is>
+      </c>
+      <c r="F140" s="14" t="inlineStr">
+        <is>
+          <t>오늘 미션을 다 하지 않은 이용자에게 저녁에 기록을 권하는 알림을 보내야 한다.</t>
+        </is>
+      </c>
+      <c r="G140" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H140" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I140" s="14" t="inlineStr">
+        <is>
+          <t>매일 저녁 8시. 조건에 맞는 문구를 무작위로 고르고 직전 문구는 제외한다. 사람·종류별 하루 한 번. 설정에서 끌 수 있다.</t>
+        </is>
+      </c>
+      <c r="J140" s="14" t="inlineStr">
+        <is>
+          <t>W22 알림 설정 · 더보기</t>
+        </is>
+      </c>
+      <c r="K140" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PUSH-007</t>
+        </is>
+      </c>
+      <c r="B141" s="14" t="inlineStr">
+        <is>
+          <t>푸시 알림</t>
+        </is>
+      </c>
+      <c r="C141" s="14" t="inlineStr">
+        <is>
+          <t>리마인드</t>
+        </is>
+      </c>
+      <c r="D141" s="14" t="inlineStr">
+        <is>
+          <t>아침 8시</t>
+        </is>
+      </c>
+      <c r="E141" s="14" t="inlineStr">
+        <is>
+          <t>아침 식사</t>
+        </is>
+      </c>
+      <c r="F141" s="14" t="inlineStr">
+        <is>
+          <t>아침 식사 미션을 하고 아직 기록하지 않은 이용자에게 아침에 알려야 한다.</t>
+        </is>
+      </c>
+      <c r="G141" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H141" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I141" s="14" t="inlineStr">
+        <is>
+          <t>매일 아침 8시. 사람·종류별 하루 한 번. 설정에서 끌 수 있다.</t>
+        </is>
+      </c>
+      <c r="J141" s="14" t="inlineStr">
+        <is>
+          <t>W22 알림 설정 · 더보기</t>
+        </is>
+      </c>
+      <c r="K141" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="13" t="inlineStr">
+        <is>
+          <t>REQ-INQ-001</t>
+        </is>
+      </c>
+      <c r="B142" s="14" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="C142" s="14" t="inlineStr">
+        <is>
+          <t>1:1 문의</t>
+        </is>
+      </c>
+      <c r="D142" s="14" t="inlineStr">
+        <is>
+          <t>문의하기</t>
+        </is>
+      </c>
+      <c r="E142" s="14" t="inlineStr">
+        <is>
+          <t>제목·내용</t>
+        </is>
+      </c>
+      <c r="F142" s="14" t="inlineStr">
+        <is>
+          <t>로그인한 이용자는 운영팀에 1:1 문의를 남길 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G142" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H142" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I142" s="14" t="inlineStr">
+        <is>
+          <t>제목·내용 입력. 건강정보를 적지 않도록 안내한다.</t>
+        </is>
+      </c>
+      <c r="J142" s="14" t="inlineStr">
+        <is>
+          <t>W21 1:1 문의 · 비회원 문의 · 공지사항</t>
+        </is>
+      </c>
+      <c r="K142" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="13" t="inlineStr">
+        <is>
+          <t>REQ-INQ-002</t>
+        </is>
+      </c>
+      <c r="B143" s="14" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="C143" s="14" t="inlineStr">
+        <is>
+          <t>1:1 문의</t>
+        </is>
+      </c>
+      <c r="D143" s="14" t="inlineStr">
+        <is>
+          <t>답변 확인</t>
+        </is>
+      </c>
+      <c r="E143" s="14" t="inlineStr">
+        <is>
+          <t>새 답변 표시</t>
+        </is>
+      </c>
+      <c r="F143" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 내 문의 목록과 답변을 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G143" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H143" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I143" s="14" t="inlineStr">
+        <is>
+          <t>상태 칩('새 답변'·'답변 대기'). 새 답변이 있으면 더보기 메뉴와 문의 목록에 표시한다.</t>
+        </is>
+      </c>
+      <c r="J143" s="14" t="inlineStr">
+        <is>
+          <t>W21 1:1 문의 · 비회원 문의 · 공지사항, A02 관리자 · 문의 · 비회원 문의</t>
+        </is>
+      </c>
+      <c r="K143" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="13" t="inlineStr">
+        <is>
+          <t>REQ-INQ-003</t>
+        </is>
+      </c>
+      <c r="B144" s="14" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="C144" s="14" t="inlineStr">
+        <is>
+          <t>비회원</t>
+        </is>
+      </c>
+      <c r="D144" s="14" t="inlineStr">
+        <is>
+          <t>비회원 문의</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="inlineStr">
+        <is>
+          <t>조회 번호</t>
+        </is>
+      </c>
+      <c r="F144" s="14" t="inlineStr">
+        <is>
+          <t>로그인·가입이 안 되는 사람은 로그인 없이 문의를 남기고 조회 번호로 답변을 확인할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G144" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H144" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I144" s="14" t="inlineStr">
+        <is>
+          <t>접수 직후 조회 번호를 한 번만 보여 준다. 조회 번호를 잃어버리면 다시 찾을 수 없다.</t>
+        </is>
+      </c>
+      <c r="J144" s="14" t="inlineStr">
+        <is>
+          <t>W21 1:1 문의 · 비회원 문의 · 공지사항</t>
+        </is>
+      </c>
+      <c r="K144" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="13" t="inlineStr">
+        <is>
+          <t>REQ-INQ-004</t>
+        </is>
+      </c>
+      <c r="B145" s="14" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="C145" s="14" t="inlineStr">
+        <is>
+          <t>비회원</t>
+        </is>
+      </c>
+      <c r="D145" s="14" t="inlineStr">
+        <is>
+          <t>보관 기간</t>
+        </is>
+      </c>
+      <c r="E145" s="14" t="inlineStr">
+        <is>
+          <t>30일 삭제</t>
+        </is>
+      </c>
+      <c r="F145" s="14" t="inlineStr">
+        <is>
+          <t>비회원 문의는 접수 30일 뒤 삭제해야 한다.</t>
+        </is>
+      </c>
+      <c r="G145" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H145" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I145" s="14" t="inlineStr">
+        <is>
+          <t>접수 후 30일이 지나면 삭제된다는 안내를 문의 화면에 보여 준다.</t>
+        </is>
+      </c>
+      <c r="J145" s="14" t="inlineStr">
+        <is>
+          <t>W21 1:1 문의 · 비회원 문의 · 공지사항</t>
+        </is>
+      </c>
+      <c r="K145" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="inlineStr">
+        <is>
+          <t>REQ-NOTICE-001</t>
+        </is>
+      </c>
+      <c r="B146" s="14" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>공지 올리기</t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F146" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 공지를 올리고 고치고 내릴 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G146" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H146" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I146" s="14" t="inlineStr">
+        <is>
+          <t>시작·끝 시각은 한국 시각. 올린 공지는 홈 팝업·종 알림·공지사항에 바로 보인다.</t>
+        </is>
+      </c>
+      <c r="J146" s="14" t="inlineStr">
+        <is>
+          <t>A03 관리자 · 공지 · 신고 · 글 관리</t>
+        </is>
+      </c>
+      <c r="K146" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="13" t="inlineStr">
+        <is>
+          <t>REQ-NOTICE-002</t>
+        </is>
+      </c>
+      <c r="B147" s="14" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="C147" s="14" t="inlineStr">
+        <is>
+          <t>이용자</t>
+        </is>
+      </c>
+      <c r="D147" s="14" t="inlineStr">
+        <is>
+          <t>공지 확인</t>
+        </is>
+      </c>
+      <c r="E147" s="14" t="inlineStr">
+        <is>
+          <t>NEW 표시</t>
+        </is>
+      </c>
+      <c r="F147" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 게시 중인 공지를 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G147" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H147" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I147" s="14" t="inlineStr">
+        <is>
+          <t>이용자별로 본 공지를 기록해 NEW 표시를 지운다. 공지가 없으면 '게시 중인 공지가 없어요'를 보여 준다.</t>
+        </is>
+      </c>
+      <c r="J147" s="14" t="inlineStr">
+        <is>
+          <t>W21 1:1 문의 · 비회원 문의 · 공지사항</t>
+        </is>
+      </c>
+      <c r="K147" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-012</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="C148" s="14" t="inlineStr">
+        <is>
+          <t>12주 프로그램</t>
+        </is>
+      </c>
+      <c r="D148" s="14" t="inlineStr">
+        <is>
+          <t>12주 계획</t>
+        </is>
+      </c>
+      <c r="E148" s="14" t="inlineStr">
+        <is>
+          <t>4주씩 3번</t>
+        </is>
+      </c>
+      <c r="F148" s="14" t="inlineStr">
+        <is>
+          <t>서비스는 12주를 4주씩 3번으로 나눠 일정(시작·1차 재입력·2차 재입력·12주 완료)을 보여 줘야 한다.</t>
+        </is>
+      </c>
+      <c r="G148" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H148" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I148" s="14" t="inlineStr">
+        <is>
+          <t>시작일 기준 4주마다 바뀐 항목만 다시 입력해 처음과 비교하도록 안내한다. 서버는 지금 12주를 한 번만 허용한다(12주를 마친 뒤 새 12주는 팀 결정 필요).</t>
+        </is>
+      </c>
+      <c r="J148" s="14" t="inlineStr">
+        <is>
+          <t>W23 내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
+        </is>
+      </c>
+      <c r="K148" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-013</t>
+        </is>
+      </c>
+      <c r="B149" s="14" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="C149" s="14" t="inlineStr">
+        <is>
+          <t>12주 프로그램</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="inlineStr">
+        <is>
+          <t>지난 12주 기록</t>
+        </is>
+      </c>
+      <c r="E149" s="14" t="inlineStr">
+        <is>
+          <t>마친 12주·진행 중</t>
+        </is>
+      </c>
+      <c r="F149" s="14" t="inlineStr">
+        <is>
+          <t>서비스는 마친 12주(평균 달성률)와 진행 중인 12주 기록을 보여 줘야 한다.</t>
+        </is>
+      </c>
+      <c r="G149" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H149" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I149" s="14" t="inlineStr">
+        <is>
+          <t>1차·2차까지만 마쳤으면 '지금까지 4주/8주'로 보여 준다.</t>
+        </is>
+      </c>
+      <c r="J149" s="14" t="inlineStr">
+        <is>
+          <t>W23 내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
+        </is>
+      </c>
+      <c r="K149" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="13" t="inlineStr">
+        <is>
+          <t>REQ-DASH-012</t>
+        </is>
+      </c>
+      <c r="B150" s="14" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="C150" s="14" t="inlineStr">
+        <is>
+          <t>12주 결과</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="inlineStr">
+        <is>
+          <t>12주 변화</t>
+        </is>
+      </c>
+      <c r="E150" s="14" t="inlineStr">
+        <is>
+          <t>표·그래프</t>
+        </is>
+      </c>
+      <c r="F150" s="14" t="inlineStr">
+        <is>
+          <t>12주를 마치면 시작과 12주 후의 혈압·체중·허리둘레·챌린지 달성률·건강 신호를 표와 수축기 혈압 선 그래프로 보여 줘야 한다.</t>
+        </is>
+      </c>
+      <c r="G150" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H150" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I150" s="14" t="inlineStr">
+        <is>
+          <t>그래프 점은 0·4·8주 재입력 때만 찍힌다. 같은 성별·연령대 상위 %는 참고용으로 표시하고 '계산 근거'를 연다. 혈압 그래프와 달성률은 인과를 암시하지 않게 따로 보여 준다. 면책 문구 한 줄(NFR-SAFE-001).</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="inlineStr">
+        <is>
+          <t>W23 내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
+        </is>
+      </c>
+      <c r="K150" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="13" t="inlineStr">
+        <is>
+          <t>REQ-DASH-013</t>
+        </is>
+      </c>
+      <c r="B151" s="14" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="C151" s="14" t="inlineStr">
+        <is>
+          <t>12주 결과</t>
+        </is>
+      </c>
+      <c r="D151" s="14" t="inlineStr">
+        <is>
+          <t>습관 변화</t>
+        </is>
+      </c>
+      <c r="E151" s="14" t="inlineStr">
+        <is>
+          <t>흡연·음주·모델 B</t>
+        </is>
+      </c>
+      <c r="F151" s="14" t="inlineStr">
+        <is>
+          <t>12주 결과에 흡연·음주 습관 변화, 4주마다 달성률, 생활습관·체형 비교(모델 B)를 보여 줘야 한다.</t>
+        </is>
+      </c>
+      <c r="G151" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H151" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I151" s="14" t="inlineStr">
+        <is>
+          <t>모델 B 비교는 값이 있을 때만 카드로 표시. 모델 A가 제외된 사람은 해당 카드 없이 모델 B만 보여 준다.</t>
+        </is>
+      </c>
+      <c r="J151" s="14" t="inlineStr">
+        <is>
+          <t>W23 내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
+        </is>
+      </c>
+      <c r="K151" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-001</t>
+        </is>
+      </c>
+      <c r="B152" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C152" s="14" t="inlineStr">
+        <is>
+          <t>가입자</t>
+        </is>
+      </c>
+      <c r="D152" s="14" t="inlineStr">
+        <is>
+          <t>가입자 목록</t>
+        </is>
+      </c>
+      <c r="E152" s="14" t="inlineStr">
+        <is>
+          <t>진행 단계·동의 상태</t>
+        </is>
+      </c>
+      <c r="F152" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 가입자의 진행 단계와 동의 상태를 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G152" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H152" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I152" s="14" t="inlineStr">
+        <is>
+          <t>단계(대상 확인·건강정보·설문·분석·챌린지)·상태(이용 중·탈퇴)로 거르고 이메일로 검색한다. 이메일은 가려서 표시하고 건강정보는 보여 주지 않는다.</t>
+        </is>
+      </c>
+      <c r="J152" s="14" t="inlineStr">
+        <is>
+          <t>A01 관리자 · 가입자 · 챌린지 통계 · 열람 기록</t>
+        </is>
+      </c>
+      <c r="K152" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-002</t>
+        </is>
+      </c>
+      <c r="B153" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C153" s="14" t="inlineStr">
+        <is>
+          <t>통계</t>
+        </is>
+      </c>
+      <c r="D153" s="14" t="inlineStr">
+        <is>
+          <t>챌린지 통계</t>
+        </is>
+      </c>
+      <c r="E153" s="14" t="inlineStr">
+        <is>
+          <t>달성률·포기율</t>
+        </is>
+      </c>
+      <c r="F153" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 미션별 선택·진행·달성·포기와 달성률·포기율을 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G153" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H153" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I153" s="14" t="inlineStr">
+        <is>
+          <t>참여자가 적으면 숫자 하나가 한 사람일 수 있다는 안내를 함께 보여 준다.</t>
+        </is>
+      </c>
+      <c r="J153" s="14" t="inlineStr">
+        <is>
+          <t>A01 관리자 · 가입자 · 챌린지 통계 · 열람 기록</t>
+        </is>
+      </c>
+      <c r="K153" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-003</t>
+        </is>
+      </c>
+      <c r="B154" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C154" s="14" t="inlineStr">
+        <is>
+          <t>감사</t>
+        </is>
+      </c>
+      <c r="D154" s="14" t="inlineStr">
+        <is>
+          <t>열람 기록</t>
+        </is>
+      </c>
+      <c r="E154" s="14" t="inlineStr">
+        <is>
+          <t>누가 무엇을</t>
+        </is>
+      </c>
+      <c r="F154" s="14" t="inlineStr">
+        <is>
+          <t>관리자가 보고 바꾼 일은 시각·관리자·동작·대상과 함께 기록되어 조회할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G154" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H154" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I154" s="14" t="inlineStr">
+        <is>
+          <t>가입자 상세·전체 이메일·문의 열람 등이 기록된다. 최근 50건을 보여 준다. 기록은 2년이 지나면 새 기록을 남길 때 삭제된다.</t>
+        </is>
+      </c>
+      <c r="J154" s="14" t="inlineStr">
+        <is>
+          <t>A01 관리자 · 가입자 · 챌린지 통계 · 열람 기록</t>
+        </is>
+      </c>
+      <c r="K154" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-004</t>
+        </is>
+      </c>
+      <c r="B155" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C155" s="14" t="inlineStr">
+        <is>
+          <t>권한</t>
+        </is>
+      </c>
+      <c r="D155" s="14" t="inlineStr">
+        <is>
+          <t>관리자 전용</t>
+        </is>
+      </c>
+      <c r="E155" s="14" t="inlineStr">
+        <is>
+          <t>접근 통제</t>
+        </is>
+      </c>
+      <c r="F155" s="14" t="inlineStr">
+        <is>
+          <t>관리자 화면과 API는 관리자 권한이 있는 계정만 쓸 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G155" s="14" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H155" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I155" s="14" t="inlineStr">
+        <is>
+          <t>일반 이용자 계정은 403 후 로그인 안내. 전체 이메일은 열람 기록이 남는 경우에만 보여 준다.</t>
+        </is>
+      </c>
+      <c r="J155" s="14" t="inlineStr">
+        <is>
+          <t>A01 관리자 · 가입자 · 챌린지 통계 · 열람 기록</t>
+        </is>
+      </c>
+      <c r="K155" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-005</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C156" s="14" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="D156" s="14" t="inlineStr">
+        <is>
+          <t>문의 답변</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="inlineStr">
+        <is>
+          <t>회원 문의</t>
+        </is>
+      </c>
+      <c r="F156" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 회원 문의를 열어 답변을 쓰고 지울 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G156" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H156" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I156" s="14" t="inlineStr">
+        <is>
+          <t>문의를 열면 열람 기록에 남는다. 답변을 저장하면 문의한 이용자에게 알림이 간다(REQ-PUSH-003).</t>
+        </is>
+      </c>
+      <c r="J156" s="14" t="inlineStr">
+        <is>
+          <t>A02 관리자 · 문의 · 비회원 문의</t>
+        </is>
+      </c>
+      <c r="K156" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-006</t>
+        </is>
+      </c>
+      <c r="B157" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C157" s="14" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="D157" s="14" t="inlineStr">
+        <is>
+          <t>비회원 문의 답변</t>
+        </is>
+      </c>
+      <c r="E157" s="14" t="inlineStr">
+        <is>
+          <t>조회 번호</t>
+        </is>
+      </c>
+      <c r="F157" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 비회원 문의에 답변할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G157" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H157" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I157" s="14" t="inlineStr">
+        <is>
+          <t>상태(답변 대기·완료)로 거른다. 열람은 기록된다.</t>
+        </is>
+      </c>
+      <c r="J157" s="14" t="inlineStr">
+        <is>
+          <t>A02 관리자 · 문의 · 비회원 문의</t>
+        </is>
+      </c>
+      <c r="K157" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-007</t>
+        </is>
+      </c>
+      <c r="B158" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C158" s="14" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="D158" s="14" t="inlineStr">
+        <is>
+          <t>공지 관리</t>
+        </is>
+      </c>
+      <c r="E158" s="14" t="inlineStr">
+        <is>
+          <t>올리기·수정·내리기</t>
+        </is>
+      </c>
+      <c r="F158" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 공지를 올리고 수정하고 지금 내릴 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G158" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H158" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I158" s="14" t="inlineStr">
+        <is>
+          <t>시작·끝 시각 지정. 올리기·수정은 열람 기록에 남는다.</t>
+        </is>
+      </c>
+      <c r="J158" s="14" t="inlineStr">
+        <is>
+          <t>A03 관리자 · 공지 · 신고 · 글 관리</t>
+        </is>
+      </c>
+      <c r="K158" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-008</t>
+        </is>
+      </c>
+      <c r="B159" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C159" s="14" t="inlineStr">
+        <is>
+          <t>신고</t>
+        </is>
+      </c>
+      <c r="D159" s="14" t="inlineStr">
+        <is>
+          <t>신고 처리</t>
+        </is>
+      </c>
+      <c r="E159" s="14" t="inlineStr">
+        <is>
+          <t>숨김·삭제·문제 없음</t>
+        </is>
+      </c>
+      <c r="F159" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 신고된 글·댓글을 숨기거나 삭제하거나 문제없음으로 처리할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G159" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H159" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I159" s="14" t="inlineStr">
+        <is>
+          <t>신고 건수·사유·자동 숨김 여부를 보여 준다. 삭제하면 되돌릴 수 없다.</t>
+        </is>
+      </c>
+      <c r="J159" s="14" t="inlineStr">
+        <is>
+          <t>A03 관리자 · 공지 · 신고 · 글 관리</t>
+        </is>
+      </c>
+      <c r="K159" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-009</t>
+        </is>
+      </c>
+      <c r="B160" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C160" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="D160" s="14" t="inlineStr">
+        <is>
+          <t>글 관리</t>
+        </is>
+      </c>
+      <c r="E160" s="14" t="inlineStr">
+        <is>
+          <t>전체 글·직접 처리</t>
+        </is>
+      </c>
+      <c r="F160" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 신고가 없어도 전체 글을 열람하고 숨김·삭제·다시 보이기를 할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G160" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H160" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I160" s="14" t="inlineStr">
+        <is>
+          <t>상태(보임·숨김·삭제됨)·검색어로 거른다. 삭제하면 내용과 사진이 지워진다. 작성자 계정은 이용 정지·삭제를 할 수 있다(REQ-ADM-013).</t>
+        </is>
+      </c>
+      <c r="J160" s="14" t="inlineStr">
+        <is>
+          <t>A03 관리자 · 공지 · 신고 · 글 관리</t>
+        </is>
+      </c>
+      <c r="K160" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-010</t>
+        </is>
+      </c>
+      <c r="B161" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C161" s="14" t="inlineStr">
+        <is>
+          <t>공통 챌린지</t>
+        </is>
+      </c>
+      <c r="D161" s="14" t="inlineStr">
+        <is>
+          <t>개설·수정·삭제</t>
+        </is>
+      </c>
+      <c r="E161" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F161" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 공통 챌린지를 열고 시작 전에 고치거나 지울 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G161" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H161" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I161" s="14" t="inlineStr">
+        <is>
+          <t>제목·인증 방식·기간·보상·완주 기준을 정한다. 순위가 확정된 챌린지는 고치거나 지울 수 없다.</t>
+        </is>
+      </c>
+      <c r="J161" s="14" t="inlineStr">
+        <is>
+          <t>A04 관리자 · 공통 챌린지 · 테스트 계정 삭제</t>
+        </is>
+      </c>
+      <c r="K161" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-011</t>
+        </is>
+      </c>
+      <c r="B162" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C162" s="14" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D162" s="14" t="inlineStr">
+        <is>
+          <t>테스트 계정 삭제</t>
+        </is>
+      </c>
+      <c r="E162" s="14" t="inlineStr">
+        <is>
+          <t>미리보기 후 삭제</t>
+        </is>
+      </c>
+      <c r="F162" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 이메일 패턴에 맞는 테스트 계정을 미리보기로 확인한 뒤 한꺼번에 삭제할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G162" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H162" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I162" s="14" t="inlineStr">
+        <is>
+          <t>미리보기에서 대상 수를 확인한 뒤 같은 수를 확인해야 삭제된다. 되돌릴 수 없다.</t>
+        </is>
+      </c>
+      <c r="J162" s="14" t="inlineStr">
+        <is>
+          <t>A04 관리자 · 공통 챌린지 · 테스트 계정 삭제</t>
+        </is>
+      </c>
+      <c r="K162" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-012</t>
+        </is>
+      </c>
+      <c r="B163" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C163" s="14" t="inlineStr">
+        <is>
+          <t>미션</t>
+        </is>
+      </c>
+      <c r="D163" s="14" t="inlineStr">
+        <is>
+          <t>미션 노출</t>
+        </is>
+      </c>
+      <c r="E163" s="14" t="inlineStr">
+        <is>
+          <t>켜기·끄기·순서</t>
+        </is>
+      </c>
+      <c r="F163" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 카테고리·미션의 노출을 켜고 끄고 카테고리 순서를 바꿀 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G163" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H163" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I163" s="14" t="inlineStr">
+        <is>
+          <t>규칙으로 정해진 고정 미션은 바꿀 수 없다.</t>
+        </is>
+      </c>
+      <c r="J163" s="14" t="inlineStr">
+        <is>
+          <t>A01 관리자 · 가입자 · 챌린지 통계 · 열람 기록</t>
+        </is>
+      </c>
+      <c r="K163" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-013</t>
+        </is>
+      </c>
+      <c r="B164" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C164" s="14" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="D164" s="14" t="inlineStr">
+        <is>
+          <t>이용 정지·삭제</t>
+        </is>
+      </c>
+      <c r="E164" s="14" t="inlineStr">
+        <is>
+          <t>작성자 계정</t>
+        </is>
+      </c>
+      <c r="F164" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 회원의 이용을 정지하거나 해제하고 계정을 삭제할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G164" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H164" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I164" s="14" t="inlineStr">
+        <is>
+          <t>삭제하면 건강정보와 글 등 모든 데이터가 지워지고 되돌릴 수 없다. 모든 처리는 열람 기록에 남는다.</t>
+        </is>
+      </c>
+      <c r="J164" s="14" t="inlineStr">
+        <is>
+          <t>A03 관리자 · 공지 · 신고 · 글 관리</t>
+        </is>
+      </c>
+      <c r="K164" s="14" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -14656,7 +18340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.005000109999999" customWidth="1" min="1" max="1"/>
@@ -15067,6 +18751,411 @@
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>REQ-USER-003, REQ-CONSENT-002, REQ-NOTI-001, REQ-FEED-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>커뮤니티 피드</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>피드 보기 → 글 열기 / 글쓰기 / 사람 프로필</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>탭(피드·챌린지·파티), 분류 칩, 안내 띠, 글 카드, 글쓰기 버튼</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>REQ-COMM-001, REQ-COMM-002, REQ-COMM-003, REQ-COMM-007, REQ-COMM-010, REQ-PUSH-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>글쓰기</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>분류 선택 → 제목·본문 → 챌린지 붙이기 → 올리기</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>올릴 곳, 분류 칩, 제목·본문, 챌린지 붙이기, 사진 3장, 파이 안내</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>REQ-COMM-004, REQ-COMM-005, REQ-COMM-007, REQ-PIE-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>글 상세 · 댓글 · 답글 · 좋아요</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>글 읽기 → 좋아요 → 댓글·답글 → 수정·삭제·신고</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>글 머리, 좋아요, 신고, 댓글·답글(한 단계), 댓글 좋아요, 입력줄</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>REQ-COMM-003, REQ-COMM-005, REQ-COMM-006, REQ-COMM-008, REQ-COMM-009, REQ-COMM-010, REQ-PUSH-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>사람 프로필 · 인기도</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>닉네임·아바타 → 글·댓글 → 인기도 하트</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>캐릭터·닉네임, 인기도 하트, 글·댓글 탭</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>REQ-COMM-011, REQ-COMM-012, REQ-COMM-013, REQ-CHARA-003, REQ-PUSH-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>닉네임 정하기 · 캐릭터 꾸미기</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>닉네임 → 캐릭터 → 파이로 아이템 구매 → 저장</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>미리보기, 6개 탭(몸체·색·눈 색·표정·얼굴·머리), 가격, 파이 잔액, 저장 버튼</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>REQ-COMM-014, REQ-CHARA-001, REQ-CHARA-002, REQ-CHARA-003, REQ-PIE-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>파이</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>내 파이 → 모으는 방법 → 최근 내역</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>잔액, 지급표, 최근 내역, 가입 감사 파이 받기</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>REQ-PIE-001, REQ-PIE-002, REQ-PIE-003, REQ-PIE-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>챌린지 파티</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>만들기 / 초대 코드 참여 → 파티 현황 → 파티 피드</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>파티 시작·만들기·현황·피드(W19-2~4 하위 화면)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>REQ-PARTY-001, REQ-PARTY-002, REQ-PARTY-003, REQ-PARTY-004, REQ-PARTY-005, REQ-PUSH-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>공통 챌린지</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>목록 → 참여 → 하루 인증 → 순위·완주 보상</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>목록(진행·예정·종료), 상세(규칙·보상·순위표), 인증 입력</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>REQ-CCHAL-001, REQ-CCHAL-002, REQ-CCHAL-003, REQ-CCHAL-004, REQ-CCHAL-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>1:1 문의 · 비회원 문의 · 공지사항</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>문의 남기기 → 답변 확인 / 공지 확인</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>문의 목록·작성, 비회원 문의(조회 번호), 공지 목록</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>REQ-INQ-001, REQ-INQ-002, REQ-INQ-003, REQ-INQ-004, REQ-NOTICE-002, REQ-PUSH-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>W22</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>알림 설정 · 더보기</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>더보기 → 알림 설정 → 켜기 → 종류별 선택</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>알림 스위치, 종류별 스위치 5개, 환경 안내(아이폰·안드로이드), 더보기 메뉴</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>REQ-PUSH-001, REQ-PUSH-002, REQ-PUSH-003, REQ-PUSH-004, REQ-PUSH-005, REQ-PUSH-006, REQ-PUSH-007, REQ-NOTI-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>W23</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>12주 계획 → 4주마다 재입력 → 12주 결과 → 지난 기록</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>12주 일정, 혈압 그래프, 전·후 표, 습관 변화, 4주마다 달성률</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-012, REQ-CHAL-013, REQ-DASH-012, REQ-DASH-013, NFR-SAFE-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>관리자 · 미션 · 가입자 · 통계 · 열람 기록</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>미션 노출 → 가입자 → 통계 → 열람 기록</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>왼쪽 메뉴(11개), 표, 필터, 검색</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>REQ-ADM-001, REQ-ADM-002, REQ-ADM-003, REQ-ADM-004, REQ-ADM-012</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>관리자 · 문의 · 비회원 문의</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>목록 → 열어서 답변</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>상태 필터, 문의 목록, 답변 입력</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>REQ-ADM-005, REQ-ADM-006, REQ-INQ-002, REQ-INQ-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>관리자 · 공지 · 신고 · 글 관리</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>공지 올리기 / 신고 처리 / 글 숨김·삭제</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>공지 폼, 신고 표, 글 표, 계정 정지·삭제</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>REQ-ADM-007, REQ-ADM-008, REQ-ADM-009, REQ-ADM-013, REQ-NOTICE-001, REQ-COMM-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>관리자 · 공통 챌린지 · 테스트 계정 삭제</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>공통 챌린지 열기·확정 / 테스트 계정 삭제</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>챌린지 폼·카드, 순위 확정, 미리보기·삭제</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>REQ-ADM-010, REQ-ADM-011, REQ-CCHAL-005</t>
         </is>
       </c>
     </row>

--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>커뮤니티·파이·파티·공통 챌린지·푸시·문의·공지·관리자 요구사항 없음 / 화면 목록이 W12까지 / 보류 항목 미반영 / 공복혈당 수집 / 예측 요청 작업 큐 서술 / 4주 비교·내 변화 화면 면책 문구 없음 / 만 14세 미만 법정대리인 동의 요구(서비스는 만 19세 이상으로 제한)</t>
+          <t>커뮤니티·파이·파티·공통 챌린지·푸시·문의·공지·관리자 요구사항 없음 / 화면 목록이 W12까지 / 보류 항목 미반영 / 공복혈당 수집 / 예측 요청 작업 큐 서술 / 4주 비교·내 변화 화면 면책 문구 없음 / 만 14세 미만 법정대리인 동의 요구(서비스는 만 19세 이상으로 제한) / 배지·캘린더·운영 현황 요구사항 없음</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
-          <t>신규 요구사항 REQ-COMM-001~014, REQ-PIE-001~004, REQ-CHARA-001~003, REQ-PARTY-001~005, REQ-CCHAL-001~005, REQ-PUSH-001~007, REQ-INQ-001~004, REQ-NOTICE-001~002, REQ-CHAL-012·013, REQ-DASH-012·013, REQ-ADM-001~013 추가, 화면 목록에 W13~W23·A01~A04, ID Naming 접두사 10개 추가 / 보류 3건 반영: 공복혈당 수집 중단(REQ-HEALTH-002·007), 예측 요청은 즉시 계산·201 반환(REQ-PRED-002), W11·W11-2 면책 문구(NFR-SAFE-001), 보류 시트 3건 상태 '반영' / 법정대리인 동의 삭제 → 만 19세 이상 가입(REQ-CONSENT-003, REQ-USER-001, REQ-ELIG-001 수정)</t>
+          <t>신규 요구사항 REQ-COMM-001~014, REQ-PIE-001~004, REQ-CHARA-001~003, REQ-PARTY-001~005, REQ-CCHAL-001~005, REQ-PUSH-001~007, REQ-INQ-001~004, REQ-NOTICE-001~002, REQ-CHAL-012·013, REQ-DASH-012·013, REQ-ADM-001~013 추가, 화면 목록에 W13~W23·A01~A04, ID Naming 접두사 10개 추가 / 보류 3건 반영: 공복혈당 수집 중단(REQ-HEALTH-002·007), 예측 요청은 즉시 계산·201 반환(REQ-PRED-002), W11·W11-2 면책 문구(NFR-SAFE-001), 보류 시트 3건 상태 '반영' / 법정대리인 동의 삭제 → 만 19세 이상 가입(REQ-CONSENT-003, REQ-USER-001, REQ-ELIG-001 수정) / 배지(REQ-BADGE-001·002), 캘린더(REQ-CAL-001~003), 관리자 운영 현황(REQ-ADM-014) 추가, 화면 목록에 W24·W08-2·A05</t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
@@ -2145,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.00500011" customWidth="1" min="1" max="1"/>
@@ -2711,6 +2711,40 @@
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>관리자 화면 ID. A{2자리} (컴퓨터 화면)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BADGE</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>기능구분</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>배지</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>기능구분</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>캘린더 일기·일정</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K164"/>
+  <dimension ref="A1:K170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.00500011" customWidth="1" min="1" max="1"/>
@@ -16133,6 +16167,348 @@
         </is>
       </c>
       <c r="K164" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="13" t="inlineStr">
+        <is>
+          <t>REQ-BADGE-001</t>
+        </is>
+      </c>
+      <c r="B165" s="14" t="inlineStr">
+        <is>
+          <t>배지</t>
+        </is>
+      </c>
+      <c r="C165" s="14" t="inlineStr">
+        <is>
+          <t>획득</t>
+        </is>
+      </c>
+      <c r="D165" s="14" t="inlineStr">
+        <is>
+          <t>획득 조건</t>
+        </is>
+      </c>
+      <c r="E165" s="14" t="inlineStr">
+        <is>
+          <t>연속·완주·기록</t>
+        </is>
+      </c>
+      <c r="F165" s="14" t="inlineStr">
+        <is>
+          <t>서비스는 습관을 이어 간 기록에 따라 배지를 줘야 한다.</t>
+        </is>
+      </c>
+      <c r="G165" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H165" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I165" s="14" t="inlineStr">
+        <is>
+          <t>연속 달성(첫 인증·3일·7일 연속, 1주 완주)과 완주·기록(운동 10회, 혈압 4번 기록, 1차·2차 4주 완주, 12주 완주) 배지를 준다. 같은 배지는 한 번만 받는다.</t>
+        </is>
+      </c>
+      <c r="J165" s="14" t="inlineStr">
+        <is>
+          <t>W24 내 배지</t>
+        </is>
+      </c>
+      <c r="K165" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="13" t="inlineStr">
+        <is>
+          <t>REQ-BADGE-002</t>
+        </is>
+      </c>
+      <c r="B166" s="14" t="inlineStr">
+        <is>
+          <t>배지</t>
+        </is>
+      </c>
+      <c r="C166" s="14" t="inlineStr">
+        <is>
+          <t>조회</t>
+        </is>
+      </c>
+      <c r="D166" s="14" t="inlineStr">
+        <is>
+          <t>내 배지</t>
+        </is>
+      </c>
+      <c r="E166" s="14" t="inlineStr">
+        <is>
+          <t>진행률·다음 배지</t>
+        </is>
+      </c>
+      <c r="F166" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 모은 배지 수, 다음 배지, 못 받은 배지의 진행 정도를 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G166" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H166" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I166" s="14" t="inlineStr">
+        <is>
+          <t>모은 개수 링, 다음 배지와 조건, 못 받은 배지는 한 만큼 채워서 표시. '배지는 습관을 이어 가는 기록일 뿐 건강 상태를 평가하지 않아요' 안내. 건강정보 동의를 철회하면 배지가 지워진다.</t>
+        </is>
+      </c>
+      <c r="J166" s="14" t="inlineStr">
+        <is>
+          <t>W24 내 배지</t>
+        </is>
+      </c>
+      <c r="K166" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CAL-001</t>
+        </is>
+      </c>
+      <c r="B167" s="14" t="inlineStr">
+        <is>
+          <t>캘린더</t>
+        </is>
+      </c>
+      <c r="C167" s="14" t="inlineStr">
+        <is>
+          <t>달력</t>
+        </is>
+      </c>
+      <c r="D167" s="14" t="inlineStr">
+        <is>
+          <t>월 달력</t>
+        </is>
+      </c>
+      <c r="E167" s="14" t="inlineStr">
+        <is>
+          <t>기록 표시</t>
+        </is>
+      </c>
+      <c r="F167" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 월 달력에서 사진이 있는 날·챌린지를 완료한 날·일정이 있는 날을 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G167" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H167" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I167" s="14" t="inlineStr">
+        <is>
+          <t>이전·다음 달 이동. 사진이 있는 날은 사진으로 칸을 채우고 일정은 점으로 표시한다. 대시보드 달력과 같은 모양을 쓴다.</t>
+        </is>
+      </c>
+      <c r="J167" s="14" t="inlineStr">
+        <is>
+          <t>W08-2 캘린더 상세 · 일기·사진·일정·할 일</t>
+        </is>
+      </c>
+      <c r="K167" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CAL-002</t>
+        </is>
+      </c>
+      <c r="B168" s="14" t="inlineStr">
+        <is>
+          <t>캘린더</t>
+        </is>
+      </c>
+      <c r="C168" s="14" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="D168" s="14" t="inlineStr">
+        <is>
+          <t>일기·사진</t>
+        </is>
+      </c>
+      <c r="E168" s="14" t="inlineStr">
+        <is>
+          <t>날짜별 저장</t>
+        </is>
+      </c>
+      <c r="F168" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 날짜별로 일기를 쓰고 사진을 붙일 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G168" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H168" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I168" s="14" t="inlineStr">
+        <is>
+          <t>일기는 '등록'을 눌러야 저장된다(자동 저장 아님). 저장 실패 시 '캘린더 저장에 실패했습니다'를 안내한다.</t>
+        </is>
+      </c>
+      <c r="J168" s="14" t="inlineStr">
+        <is>
+          <t>W08-2 캘린더 상세 · 일기·사진·일정·할 일</t>
+        </is>
+      </c>
+      <c r="K168" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CAL-003</t>
+        </is>
+      </c>
+      <c r="B169" s="14" t="inlineStr">
+        <is>
+          <t>캘린더</t>
+        </is>
+      </c>
+      <c r="C169" s="14" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="D169" s="14" t="inlineStr">
+        <is>
+          <t>일정·할 일</t>
+        </is>
+      </c>
+      <c r="E169" s="14" t="inlineStr">
+        <is>
+          <t>챌린지 연동</t>
+        </is>
+      </c>
+      <c r="F169" s="14" t="inlineStr">
+        <is>
+          <t>이용자는 일정과 할 일을 적고 고치고 지울 수 있어야 하며, 오늘의 챌린지 미션이 할 일에 자동으로 들어와야 한다.</t>
+        </is>
+      </c>
+      <c r="G169" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H169" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I169" s="14" t="inlineStr">
+        <is>
+          <t>할 일은 달력에 표시하지 않고 이 화면에서만 보여 준다. 일정은 달력에 점으로만 표시한다.</t>
+        </is>
+      </c>
+      <c r="J169" s="14" t="inlineStr">
+        <is>
+          <t>W08-2 캘린더 상세 · 일기·사진·일정·할 일</t>
+        </is>
+      </c>
+      <c r="K169" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-014</t>
+        </is>
+      </c>
+      <c r="B170" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C170" s="14" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D170" s="14" t="inlineStr">
+        <is>
+          <t>운영 현황</t>
+        </is>
+      </c>
+      <c r="E170" s="14" t="inlineStr">
+        <is>
+          <t>단계별·날짜별 집계</t>
+        </is>
+      </c>
+      <c r="F170" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 체험 진행 현황(단계별 사용자 수), 날짜별 가입·로그인, 동의·삭제 현황, 서비스 상태를 숫자로 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G170" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H170" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I170" s="14" t="inlineStr">
+        <is>
+          <t>집계 숫자만 보여 주고 개인 정보는 보여 주지 않는다. 14·30·90일 기간 선택. 집계 CSV를 내려받으면 관리자 열람 기록에 남는다. 로그인 기록은 93일 뒤 지워진다.</t>
+        </is>
+      </c>
+      <c r="J170" s="14" t="inlineStr">
+        <is>
+          <t>A05 관리자 · 운영 현황</t>
+        </is>
+      </c>
+      <c r="K170" s="14" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -18340,7 +18716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.005000109999999" customWidth="1" min="1" max="1"/>
@@ -18379,783 +18755,864 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>W01</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>서비스 소개 · 시작하기</t>
+          <t>관리자 · 미션 · 가입자 · 통계 · 열람 기록</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>소개 → 시작하기</t>
+          <t>미션 노출 → 가입자 → 통계 → 열람 기록</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>서비스 한 줄 소개, 핵심 기능 3단계 안내, 시작하기 CTA</t>
+          <t>왼쪽 메뉴(11개), 표, 필터, 검색</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REQ-ADM-001, REQ-ADM-002, REQ-ADM-003, REQ-ADM-004, REQ-ADM-012</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>W02</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>회원가입 · 로그인 · 동의</t>
+          <t>관리자 · 문의 · 비회원 문의</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>계정 생성 → 필수 동의</t>
+          <t>목록 → 열어서 답변</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>가입 폼, 로그인 폼, 비밀번호 재설정, 약관·건강정보 동의 체크</t>
+          <t>상태 필터, 문의 목록, 답변 입력</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>REQ-USER-001, REQ-USER-002, REQ-USER-004, REQ-CONSENT-001, REQ-CONSENT-003, NFR-SEC-003, NFR-SEC-006</t>
+          <t>REQ-ADM-005, REQ-ADM-006, REQ-INQ-002, REQ-INQ-003</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>W03</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>이용 적합성 · 응급 확인</t>
+          <t>관리자 · 공지 · 신고 · 글 관리</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>안전 문진 → 서비스 분기</t>
+          <t>공지 올리기 / 신고 처리 / 글 숨김·삭제</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>긴급 증상 문진, 119 전화 버튼, 연령·기진단 확인, 부적합 사유 안내</t>
+          <t>공지 폼, 신고 표, 글 표, 계정 정지·삭제</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>REQ-ELIG-001, REQ-ELIG-002, REQ-ELIG-003, REQ-ELIG-004, NFR-SAFE-004</t>
+          <t>REQ-ADM-007, REQ-ADM-008, REQ-ADM-009, REQ-ADM-013, REQ-NOTICE-001, REQ-COMM-008</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>W04</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>건강정보 입력</t>
+          <t>관리자 · 공통 챌린지 · 테스트 계정 삭제</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>직접 입력 → 검증</t>
+          <t>공통 챌린지 열기·확정 / 테스트 계정 삭제</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>기본 정보, 계측·혈압, 가족력, 검진 결과지 사진 채우기, 필드 오류 표시, 검진 이력 추가</t>
+          <t>챌린지 폼·카드, 순위 확정, 미리보기·삭제</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-001, REQ-HEALTH-002, REQ-HEALTH-003, REQ-HEALTH-004, REQ-HEALTH-006, REQ-HEALTH-008, NFR-SEC-003, NFR-SEC-005, NFR-SEC-006, NFR-SEC-007, NFR-OPS-006</t>
+          <t>REQ-ADM-010, REQ-ADM-011, REQ-CCHAL-005</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>W04-2</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>생활습관 설문</t>
+          <t>관리자 · 운영 현황</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>선택지 응답 → 조건부 건너뛰기 → 다음</t>
+          <t>기간 선택 → 단계별·날짜별 집계 → CSV</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>단계 표시(7단계), 선택형 문항, 운동 종목 선택·강도 자동 분류, 조건부 문항 건너뛰기, 이전·다음</t>
+          <t>체험 진행 현황, 날짜별 활동, 동의·삭제 현황, 서비스 상태, CSV</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-005, REQ-PRED-008, REQ-CHAL-001, REQ-CHAL-008</t>
+          <t>REQ-ADM-014</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>W05</t>
+          <t>W01</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>입력 검토 · 분석 대기</t>
+          <t>서비스 소개 · 시작하기</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>확인 → 비동기 분석</t>
+          <t>소개 → 시작하기</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>입력값 검토 요약, 분석 요청 버튼, 대기·실행·완료·실패·재시도 상태</t>
+          <t>서비스 한 줄 소개, 핵심 기능 3단계 안내, 시작하기 CTA</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-007, REQ-PRED-002, NFR-ASYNC-001</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>W06</t>
+          <t>W02</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>예측 결과 · XAI 설명</t>
+          <t>회원가입 · 로그인 · 동의</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>선별 결과 → 설명 → 다음 행동</t>
+          <t>계정 생성 → 필수 동의</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>입력 혈압 판정, 심장 혈관 건강 신호(확률·범주·확률 근거), 혈관 나이(같은 성별·연령대 상위 %·계산 근거), 바꿀 수 있는 요인, 생활습관·체형 비교(3단계·비교 기준), 면책 문구</t>
+          <t>가입 폼, 로그인 폼, 비밀번호 재설정, 약관·건강정보 동의 체크</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>REQ-PRED-001, REQ-PRED-003, REQ-PRED-006,  NFR-SAFE-001, NFR-SAFE-002, NFR-SAFE-003, NFR-SAFE-005, NFR-SAFE-007</t>
+          <t>REQ-USER-001, REQ-USER-002, REQ-USER-004, REQ-CONSENT-001, REQ-CONSENT-003, NFR-SEC-003, NFR-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>W07</t>
+          <t>W03</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>검사 · 상담 안내</t>
+          <t>이용 적합성 · 응급 확인</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>모델 A 높음 또는 혈압 140/90 이상 → 의료기관</t>
+          <t>안전 문진 → 서비스 분기</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>고위험 안내 문구, 검사 권고, 의료기관 정보, 면책 문구</t>
+          <t>긴급 증상 문진, 119 전화 버튼, 연령·기진단 확인, 부적합 사유 안내</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>REQ-PRED-005, NFR-SAFE-001</t>
+          <t>REQ-ELIG-001, REQ-ELIG-002, REQ-ELIG-003, REQ-ELIG-004, NFR-SAFE-004</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>W08</t>
+          <t>W04</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>대시보드 (홈)</t>
+          <t>건강정보 입력</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>상태 요약 → 오늘의 실천</t>
+          <t>직접 입력 → 검증</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>상단 네비게이션, 최신 위험도 카드, 오늘의 챌린지 진행률, 사이클 현황, 빈 상태 CTA</t>
+          <t>기본 정보, 계측·혈압, 가족력, 검진 결과지 사진 채우기, 필드 오류 표시, 검진 이력 추가</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>REQ-PRED-004, REQ-PRED-007, REQ-DASH-001, REQ-DASH-004, REQ-DASH-005, REQ-DASH-006, REQ-DASH-007, REQ-DASH-008, REQ-DASH-009, REQ-DASH-010, REQ-DASH-011, NFR-DASH-001, NFR-SAFE-001, NFR-SAFE-005</t>
+          <t>REQ-HEALTH-001, REQ-HEALTH-002, REQ-HEALTH-003, REQ-HEALTH-004, REQ-HEALTH-006, REQ-HEALTH-008, NFR-SEC-003, NFR-SEC-005, NFR-SEC-006, NFR-SEC-007, NFR-OPS-006</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>W09</t>
+          <t>W04-2</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>챌린지 선택</t>
+          <t>생활습관 설문</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>추천 → 선택 → 시작</t>
+          <t>선택지 응답 → 조건부 건너뛰기 → 다음</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>예측 근거별 챌린지 후보, 연결된 위험 요인 표시, 목표 횟수 설정, 사이클 시작, 고정 미션 2개, 제외한 챌린지·이유</t>
+          <t>단계 표시(7단계), 선택형 문항, 운동 종목 선택·강도 자동 분류, 조건부 문항 건너뛰기, 이전·다음</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>REQ-CHAL-001, REQ-CHAL-002, REQ-CHAL-003, REQ-CHAL-008, REQ-CHAL-009, NFR-DASH-001, REQ-FEED-003, NFR-SAFE-007</t>
+          <t>REQ-HEALTH-005, REQ-PRED-008, REQ-CHAL-001, REQ-CHAL-008</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W05</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>챌린지 수행 · 인증</t>
+          <t>입력 검토 · 분석 대기</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>목표 → 인증 → 달성률</t>
+          <t>확인 → 비동기 분석</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>오늘의 목표 목록, 인증하기, 당일 기록 수정, 주간·사이클 달성률, 식단 사진 업로드</t>
+          <t>입력값 검토 요약, 분석 요청 버튼, 대기·실행·완료·실패·재시도 상태</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>REQ-CHAL-004, REQ-CHAL-005, REQ-CHAL-006, REQ-CHAL-007, REQ-CHAL-010, REQ-DASH-008, REQ-DASH-009, NFR-DASH-001, REQ-RECO-002</t>
+          <t>REQ-HEALTH-007, REQ-PRED-002, NFR-ASYNC-001</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W06</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>추이 · 변화 추적</t>
+          <t>예측 결과 · XAI 설명</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>이력 → 차트</t>
+          <t>선별 결과 → 설명 → 다음 행동</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>예측 이력 차트, 최초 대비 증감(색상+기호), 기간 필터, 데이터 1건 이하 빈 상태</t>
+          <t>입력 혈압 판정, 심장 혈관 건강 신호(확률·범주·확률 근거), 혈관 나이(같은 성별·연령대 상위 %·계산 근거), 바꿀 수 있는 요인, 생활습관·체형 비교(3단계·비교 기준), 면책 문구</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>REQ-DASH-002, REQ-DASH-003, REQ-DASH-010, REQ-FEED-002, NFR-SAFE-005, NFR-ARCH-004</t>
+          <t>REQ-PRED-001, REQ-PRED-003, REQ-PRED-006,  NFR-SAFE-001, NFR-SAFE-002, NFR-SAFE-003, NFR-SAFE-005, NFR-SAFE-007</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>W11-2</t>
+          <t>W07</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>4주 전 · 후 비교</t>
+          <t>검사 · 상담 안내</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>재입력 → 같은 모델 → 변화</t>
+          <t>모델 A 높음 또는 혈압 140/90 이상 → 의료기관</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>시작·4주 후 심장 혈관 건강 신호·생활습관·체형 비교, 혈압·몸무게·허리둘레 변화, 미션 달성률·습관 변화, 다음 4주 챌린지 선택 (혈관 나이·요인 순위 변화는 보류 · 결정 필요 시트 참고)</t>
+          <t>고위험 안내 문구, 검사 권고, 의료기관 정보, 면책 문구</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-008, REQ-PRED-007, REQ-DASH-003, REQ-DASH-011</t>
+          <t>REQ-PRED-005, NFR-SAFE-001</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W08</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>피드백 · 마이페이지</t>
+          <t>대시보드 (홈)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>의견 → 저장 / 계정 관리</t>
+          <t>상태 요약 → 오늘의 실천</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>결과·추천 평가와 의견 입력, 알림 수신 설정, 동의 철회, 회원 탈퇴</t>
+          <t>상단 네비게이션, 최신 위험도 카드, 오늘의 챌린지 진행률, 사이클 현황, 빈 상태 CTA</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>REQ-USER-003, REQ-CONSENT-002, REQ-NOTI-001, REQ-FEED-001</t>
+          <t>REQ-PRED-004, REQ-PRED-007, REQ-DASH-001, REQ-DASH-004, REQ-DASH-005, REQ-DASH-006, REQ-DASH-007, REQ-DASH-008, REQ-DASH-009, REQ-DASH-010, REQ-DASH-011, NFR-DASH-001, NFR-SAFE-001, NFR-SAFE-005</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W08-2</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>커뮤니티 피드</t>
+          <t>캘린더 상세</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>피드 보기 → 글 열기 / 글쓰기 / 사람 프로필</t>
+          <t>날짜 선택 → 일기·사진·일정·할 일</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>탭(피드·챌린지·파티), 분류 칩, 안내 띠, 글 카드, 글쓰기 버튼</t>
+          <t>월 달력, 일기, 사진, 일정, 오늘 할 일(챌린지 연동)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-001, REQ-COMM-002, REQ-COMM-003, REQ-COMM-007, REQ-COMM-010, REQ-PUSH-001</t>
+          <t>REQ-CAL-001, REQ-CAL-002, REQ-CAL-003</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W09</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>글쓰기</t>
+          <t>챌린지 선택</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>분류 선택 → 제목·본문 → 챌린지 붙이기 → 올리기</t>
+          <t>추천 → 선택 → 시작</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>올릴 곳, 분류 칩, 제목·본문, 챌린지 붙이기, 사진 3장, 파이 안내</t>
+          <t>예측 근거별 챌린지 후보, 연결된 위험 요인 표시, 목표 횟수 설정, 사이클 시작, 고정 미션 2개, 제외한 챌린지·이유</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-004, REQ-COMM-005, REQ-COMM-007, REQ-PIE-001</t>
+          <t>REQ-CHAL-001, REQ-CHAL-002, REQ-CHAL-003, REQ-CHAL-008, REQ-CHAL-009, NFR-DASH-001, REQ-FEED-003, NFR-SAFE-007</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>글 상세 · 댓글 · 답글 · 좋아요</t>
+          <t>챌린지 수행 · 인증</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>글 읽기 → 좋아요 → 댓글·답글 → 수정·삭제·신고</t>
+          <t>목표 → 인증 → 달성률</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>글 머리, 좋아요, 신고, 댓글·답글(한 단계), 댓글 좋아요, 입력줄</t>
+          <t>오늘의 목표 목록, 인증하기, 당일 기록 수정, 주간·사이클 달성률, 식단 사진 업로드</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-003, REQ-COMM-005, REQ-COMM-006, REQ-COMM-008, REQ-COMM-009, REQ-COMM-010, REQ-PUSH-002</t>
+          <t>REQ-CHAL-004, REQ-CHAL-005, REQ-CHAL-006, REQ-CHAL-007, REQ-CHAL-010, REQ-DASH-008, REQ-DASH-009, NFR-DASH-001, REQ-RECO-002</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>사람 프로필 · 인기도</t>
+          <t>추이 · 변화 추적</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>닉네임·아바타 → 글·댓글 → 인기도 하트</t>
+          <t>이력 → 차트</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·닉네임, 인기도 하트, 글·댓글 탭</t>
+          <t>예측 이력 차트, 최초 대비 증감(색상+기호), 기간 필터, 데이터 1건 이하 빈 상태</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-011, REQ-COMM-012, REQ-COMM-013, REQ-CHARA-003, REQ-PUSH-005</t>
+          <t>REQ-DASH-002, REQ-DASH-003, REQ-DASH-010, REQ-FEED-002, NFR-SAFE-005, NFR-ARCH-004</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W11-2</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>닉네임 정하기 · 캐릭터 꾸미기</t>
+          <t>4주 전 · 후 비교</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>닉네임 → 캐릭터 → 파이로 아이템 구매 → 저장</t>
+          <t>재입력 → 같은 모델 → 변화</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>미리보기, 6개 탭(몸체·색·눈 색·표정·얼굴·머리), 가격, 파이 잔액, 저장 버튼</t>
+          <t>시작·4주 후 심장 혈관 건강 신호·생활습관·체형 비교, 혈압·몸무게·허리둘레 변화, 미션 달성률·습관 변화, 다음 4주 챌린지 선택 (혈관 나이·요인 순위 변화는 보류 · 결정 필요 시트 참고)</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-014, REQ-CHARA-001, REQ-CHARA-002, REQ-CHARA-003, REQ-PIE-002</t>
+          <t>REQ-HEALTH-008, REQ-PRED-007, REQ-DASH-003, REQ-DASH-011</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>파이</t>
+          <t>피드백 · 마이페이지</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>내 파이 → 모으는 방법 → 최근 내역</t>
+          <t>의견 → 저장 / 계정 관리</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>잔액, 지급표, 최근 내역, 가입 감사 파이 받기</t>
+          <t>결과·추천 평가와 의견 입력, 알림 수신 설정, 동의 철회, 회원 탈퇴</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>REQ-PIE-001, REQ-PIE-002, REQ-PIE-003, REQ-PIE-004</t>
+          <t>REQ-USER-003, REQ-CONSENT-002, REQ-NOTI-001, REQ-FEED-001</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>챌린지 파티</t>
+          <t>커뮤니티 피드</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>만들기 / 초대 코드 참여 → 파티 현황 → 파티 피드</t>
+          <t>피드 보기 → 글 열기 / 글쓰기 / 사람 프로필</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>파티 시작·만들기·현황·피드(W19-2~4 하위 화면)</t>
+          <t>탭(피드·챌린지·파티), 분류 칩, 안내 띠, 글 카드, 글쓰기 버튼</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>REQ-PARTY-001, REQ-PARTY-002, REQ-PARTY-003, REQ-PARTY-004, REQ-PARTY-005, REQ-PUSH-004</t>
+          <t>REQ-COMM-001, REQ-COMM-002, REQ-COMM-003, REQ-COMM-007, REQ-COMM-010, REQ-PUSH-001</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>공통 챌린지</t>
+          <t>글쓰기</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>목록 → 참여 → 하루 인증 → 순위·완주 보상</t>
+          <t>분류 선택 → 제목·본문 → 챌린지 붙이기 → 올리기</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>목록(진행·예정·종료), 상세(규칙·보상·순위표), 인증 입력</t>
+          <t>올릴 곳, 분류 칩, 제목·본문, 챌린지 붙이기, 사진 3장, 파이 안내</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>REQ-CCHAL-001, REQ-CCHAL-002, REQ-CCHAL-003, REQ-CCHAL-004, REQ-CCHAL-005</t>
+          <t>REQ-COMM-004, REQ-COMM-005, REQ-COMM-007, REQ-PIE-001</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>1:1 문의 · 비회원 문의 · 공지사항</t>
+          <t>글 상세 · 댓글 · 답글 · 좋아요</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>문의 남기기 → 답변 확인 / 공지 확인</t>
+          <t>글 읽기 → 좋아요 → 댓글·답글 → 수정·삭제·신고</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>문의 목록·작성, 비회원 문의(조회 번호), 공지 목록</t>
+          <t>글 머리, 좋아요, 신고, 댓글·답글(한 단계), 댓글 좋아요, 입력줄</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>REQ-INQ-001, REQ-INQ-002, REQ-INQ-003, REQ-INQ-004, REQ-NOTICE-002, REQ-PUSH-003</t>
+          <t>REQ-COMM-003, REQ-COMM-005, REQ-COMM-006, REQ-COMM-008, REQ-COMM-009, REQ-COMM-010, REQ-PUSH-002</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>알림 설정 · 더보기</t>
+          <t>사람 프로필 · 인기도</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>더보기 → 알림 설정 → 켜기 → 종류별 선택</t>
+          <t>닉네임·아바타 → 글·댓글 → 인기도 하트</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>알림 스위치, 종류별 스위치 5개, 환경 안내(아이폰·안드로이드), 더보기 메뉴</t>
+          <t>캐릭터·닉네임, 인기도 하트, 글·댓글 탭</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>REQ-PUSH-001, REQ-PUSH-002, REQ-PUSH-003, REQ-PUSH-004, REQ-PUSH-005, REQ-PUSH-006, REQ-PUSH-007, REQ-NOTI-001</t>
+          <t>REQ-COMM-011, REQ-COMM-012, REQ-COMM-013, REQ-CHARA-003, REQ-PUSH-005</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
+          <t>닉네임 정하기 · 캐릭터 꾸미기</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>12주 계획 → 4주마다 재입력 → 12주 결과 → 지난 기록</t>
+          <t>닉네임 → 캐릭터 → 파이로 아이템 구매 → 저장</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>12주 일정, 혈압 그래프, 전·후 표, 습관 변화, 4주마다 달성률</t>
+          <t>미리보기, 6개 탭(몸체·색·눈 색·표정·얼굴·머리), 가격, 파이 잔액, 저장 버튼</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>REQ-CHAL-012, REQ-CHAL-013, REQ-DASH-012, REQ-DASH-013, NFR-SAFE-001</t>
+          <t>REQ-COMM-014, REQ-CHARA-001, REQ-CHARA-002, REQ-CHARA-003, REQ-PIE-002</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 미션 · 가입자 · 통계 · 열람 기록</t>
+          <t>파이</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>미션 노출 → 가입자 → 통계 → 열람 기록</t>
+          <t>내 파이 → 모으는 방법 → 최근 내역</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>왼쪽 메뉴(11개), 표, 필터, 검색</t>
+          <t>잔액, 지급표, 최근 내역, 가입 감사 파이 받기</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-001, REQ-ADM-002, REQ-ADM-003, REQ-ADM-004, REQ-ADM-012</t>
+          <t>REQ-PIE-001, REQ-PIE-002, REQ-PIE-003, REQ-PIE-004</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 문의 · 비회원 문의</t>
+          <t>챌린지 파티</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>목록 → 열어서 답변</t>
+          <t>만들기 / 초대 코드 참여 → 파티 현황 → 파티 피드</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>상태 필터, 문의 목록, 답변 입력</t>
+          <t>파티 시작·만들기·현황·피드(W19-2~4 하위 화면)</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-005, REQ-ADM-006, REQ-INQ-002, REQ-INQ-003</t>
+          <t>REQ-PARTY-001, REQ-PARTY-002, REQ-PARTY-003, REQ-PARTY-004, REQ-PARTY-005, REQ-PUSH-004</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 공지 · 신고 · 글 관리</t>
+          <t>공통 챌린지</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>공지 올리기 / 신고 처리 / 글 숨김·삭제</t>
+          <t>목록 → 참여 → 하루 인증 → 순위·완주 보상</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>공지 폼, 신고 표, 글 표, 계정 정지·삭제</t>
+          <t>목록(진행·예정·종료), 상세(규칙·보상·순위표), 인증 입력</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-007, REQ-ADM-008, REQ-ADM-009, REQ-ADM-013, REQ-NOTICE-001, REQ-COMM-008</t>
+          <t>REQ-CCHAL-001, REQ-CCHAL-002, REQ-CCHAL-003, REQ-CCHAL-004, REQ-CCHAL-005</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 공통 챌린지 · 테스트 계정 삭제</t>
+          <t>1:1 문의 · 비회원 문의 · 공지사항</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>공통 챌린지 열기·확정 / 테스트 계정 삭제</t>
+          <t>문의 남기기 → 답변 확인 / 공지 확인</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>챌린지 폼·카드, 순위 확정, 미리보기·삭제</t>
+          <t>문의 목록·작성, 비회원 문의(조회 번호), 공지 목록</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-010, REQ-ADM-011, REQ-CCHAL-005</t>
+          <t>REQ-INQ-001, REQ-INQ-002, REQ-INQ-003, REQ-INQ-004, REQ-NOTICE-002, REQ-PUSH-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>W22</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>알림 설정 · 더보기</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>더보기 → 알림 설정 → 켜기 → 종류별 선택</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>알림 스위치, 종류별 스위치 5개, 환경 안내(아이폰·안드로이드), 더보기 메뉴</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>REQ-PUSH-001, REQ-PUSH-002, REQ-PUSH-003, REQ-PUSH-004, REQ-PUSH-005, REQ-PUSH-006, REQ-PUSH-007, REQ-NOTI-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>W23</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>12주 계획 → 4주마다 재입력 → 12주 결과 → 지난 기록</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>12주 일정, 혈압 그래프, 전·후 표, 습관 변화, 4주마다 달성률</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-012, REQ-CHAL-013, REQ-DASH-012, REQ-DASH-013, NFR-SAFE-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>W24</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>내 배지</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>배지 모으기 → 내 배지 확인</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>모은 개수 링, 다음 배지, 연속 달성·완주와 기록 배지, 진행률</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>REQ-BADGE-001, REQ-BADGE-002</t>
         </is>
       </c>
     </row>

--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -18755,864 +18755,864 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>W01</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 미션 · 가입자 · 통계 · 열람 기록</t>
+          <t>서비스 소개 · 시작하기</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>미션 노출 → 가입자 → 통계 → 열람 기록</t>
+          <t>소개 → 시작하기</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>왼쪽 메뉴(11개), 표, 필터, 검색</t>
+          <t>서비스 한 줄 소개, 핵심 기능 3단계 안내, 시작하기 CTA</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-001, REQ-ADM-002, REQ-ADM-003, REQ-ADM-004, REQ-ADM-012</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>W02</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 문의 · 비회원 문의</t>
+          <t>회원가입 · 로그인 · 동의</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>목록 → 열어서 답변</t>
+          <t>계정 생성 → 필수 동의</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>상태 필터, 문의 목록, 답변 입력</t>
+          <t>가입 폼, 로그인 폼, 비밀번호 재설정, 약관·건강정보 동의 체크</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-005, REQ-ADM-006, REQ-INQ-002, REQ-INQ-003</t>
+          <t>REQ-USER-001, REQ-USER-002, REQ-USER-004, REQ-CONSENT-001, REQ-CONSENT-003, NFR-SEC-003, NFR-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>W03</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 공지 · 신고 · 글 관리</t>
+          <t>이용 적합성 · 응급 확인</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>공지 올리기 / 신고 처리 / 글 숨김·삭제</t>
+          <t>안전 문진 → 서비스 분기</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>공지 폼, 신고 표, 글 표, 계정 정지·삭제</t>
+          <t>긴급 증상 문진, 119 전화 버튼, 연령·기진단 확인, 부적합 사유 안내</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-007, REQ-ADM-008, REQ-ADM-009, REQ-ADM-013, REQ-NOTICE-001, REQ-COMM-008</t>
+          <t>REQ-ELIG-001, REQ-ELIG-002, REQ-ELIG-003, REQ-ELIG-004, NFR-SAFE-004</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>W04</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 공통 챌린지 · 테스트 계정 삭제</t>
+          <t>건강정보 입력</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>공통 챌린지 열기·확정 / 테스트 계정 삭제</t>
+          <t>직접 입력 → 검증</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>챌린지 폼·카드, 순위 확정, 미리보기·삭제</t>
+          <t>기본 정보, 계측·혈압, 가족력, 검진 결과지 사진 채우기, 필드 오류 표시, 검진 이력 추가</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-010, REQ-ADM-011, REQ-CCHAL-005</t>
+          <t>REQ-HEALTH-001, REQ-HEALTH-002, REQ-HEALTH-003, REQ-HEALTH-004, REQ-HEALTH-006, REQ-HEALTH-008, NFR-SEC-003, NFR-SEC-005, NFR-SEC-006, NFR-SEC-007, NFR-OPS-006</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>W04-2</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 운영 현황</t>
+          <t>생활습관 설문</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>기간 선택 → 단계별·날짜별 집계 → CSV</t>
+          <t>선택지 응답 → 조건부 건너뛰기 → 다음</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>체험 진행 현황, 날짜별 활동, 동의·삭제 현황, 서비스 상태, CSV</t>
+          <t>단계 표시(7단계), 선택형 문항, 운동 종목 선택·강도 자동 분류, 조건부 문항 건너뛰기, 이전·다음</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-014</t>
+          <t>REQ-HEALTH-005, REQ-PRED-008, REQ-CHAL-001, REQ-CHAL-008</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>W01</t>
+          <t>W05</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>서비스 소개 · 시작하기</t>
+          <t>입력 검토 · 분석 대기</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>소개 → 시작하기</t>
+          <t>확인 → 비동기 분석</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>서비스 한 줄 소개, 핵심 기능 3단계 안내, 시작하기 CTA</t>
+          <t>입력값 검토 요약, 분석 요청 버튼, 대기·실행·완료·실패·재시도 상태</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REQ-HEALTH-007, REQ-PRED-002, NFR-ASYNC-001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>W02</t>
+          <t>W06</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>회원가입 · 로그인 · 동의</t>
+          <t>예측 결과 · XAI 설명</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>계정 생성 → 필수 동의</t>
+          <t>선별 결과 → 설명 → 다음 행동</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>가입 폼, 로그인 폼, 비밀번호 재설정, 약관·건강정보 동의 체크</t>
+          <t>입력 혈압 판정, 심장 혈관 건강 신호(확률·범주·확률 근거), 혈관 나이(같은 성별·연령대 상위 %·계산 근거), 바꿀 수 있는 요인, 생활습관·체형 비교(3단계·비교 기준), 면책 문구</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>REQ-USER-001, REQ-USER-002, REQ-USER-004, REQ-CONSENT-001, REQ-CONSENT-003, NFR-SEC-003, NFR-SEC-006</t>
+          <t>REQ-PRED-001, REQ-PRED-003, REQ-PRED-006,  NFR-SAFE-001, NFR-SAFE-002, NFR-SAFE-003, NFR-SAFE-005, NFR-SAFE-007</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>W03</t>
+          <t>W07</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>이용 적합성 · 응급 확인</t>
+          <t>검사 · 상담 안내</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>안전 문진 → 서비스 분기</t>
+          <t>모델 A 높음 또는 혈압 140/90 이상 → 의료기관</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>긴급 증상 문진, 119 전화 버튼, 연령·기진단 확인, 부적합 사유 안내</t>
+          <t>고위험 안내 문구, 검사 권고, 의료기관 정보, 면책 문구</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>REQ-ELIG-001, REQ-ELIG-002, REQ-ELIG-003, REQ-ELIG-004, NFR-SAFE-004</t>
+          <t>REQ-PRED-005, NFR-SAFE-001</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>W04</t>
+          <t>W08</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>건강정보 입력</t>
+          <t>대시보드 (홈)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>직접 입력 → 검증</t>
+          <t>상태 요약 → 오늘의 실천</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>기본 정보, 계측·혈압, 가족력, 검진 결과지 사진 채우기, 필드 오류 표시, 검진 이력 추가</t>
+          <t>상단 네비게이션, 최신 위험도 카드, 오늘의 챌린지 진행률, 사이클 현황, 빈 상태 CTA</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-001, REQ-HEALTH-002, REQ-HEALTH-003, REQ-HEALTH-004, REQ-HEALTH-006, REQ-HEALTH-008, NFR-SEC-003, NFR-SEC-005, NFR-SEC-006, NFR-SEC-007, NFR-OPS-006</t>
+          <t>REQ-PRED-004, REQ-PRED-007, REQ-DASH-001, REQ-DASH-004, REQ-DASH-005, REQ-DASH-006, REQ-DASH-007, REQ-DASH-008, REQ-DASH-009, REQ-DASH-010, REQ-DASH-011, NFR-DASH-001, NFR-SAFE-001, NFR-SAFE-005</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>W04-2</t>
+          <t>W08-2</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>생활습관 설문</t>
+          <t>캘린더 상세</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>선택지 응답 → 조건부 건너뛰기 → 다음</t>
+          <t>날짜 선택 → 일기·사진·일정·할 일</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>단계 표시(7단계), 선택형 문항, 운동 종목 선택·강도 자동 분류, 조건부 문항 건너뛰기, 이전·다음</t>
+          <t>월 달력, 일기, 사진, 일정, 오늘 할 일(챌린지 연동)</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-005, REQ-PRED-008, REQ-CHAL-001, REQ-CHAL-008</t>
+          <t>REQ-CAL-001, REQ-CAL-002, REQ-CAL-003</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>W05</t>
+          <t>W09</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>입력 검토 · 분석 대기</t>
+          <t>챌린지 선택</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>확인 → 비동기 분석</t>
+          <t>추천 → 선택 → 시작</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>입력값 검토 요약, 분석 요청 버튼, 대기·실행·완료·실패·재시도 상태</t>
+          <t>예측 근거별 챌린지 후보, 연결된 위험 요인 표시, 목표 횟수 설정, 사이클 시작, 고정 미션 2개, 제외한 챌린지·이유</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-007, REQ-PRED-002, NFR-ASYNC-001</t>
+          <t>REQ-CHAL-001, REQ-CHAL-002, REQ-CHAL-003, REQ-CHAL-008, REQ-CHAL-009, NFR-DASH-001, REQ-FEED-003, NFR-SAFE-007</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>W06</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>예측 결과 · XAI 설명</t>
+          <t>챌린지 수행 · 인증</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>선별 결과 → 설명 → 다음 행동</t>
+          <t>목표 → 인증 → 달성률</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>입력 혈압 판정, 심장 혈관 건강 신호(확률·범주·확률 근거), 혈관 나이(같은 성별·연령대 상위 %·계산 근거), 바꿀 수 있는 요인, 생활습관·체형 비교(3단계·비교 기준), 면책 문구</t>
+          <t>오늘의 목표 목록, 인증하기, 당일 기록 수정, 주간·사이클 달성률, 식단 사진 업로드</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>REQ-PRED-001, REQ-PRED-003, REQ-PRED-006,  NFR-SAFE-001, NFR-SAFE-002, NFR-SAFE-003, NFR-SAFE-005, NFR-SAFE-007</t>
+          <t>REQ-CHAL-004, REQ-CHAL-005, REQ-CHAL-006, REQ-CHAL-007, REQ-CHAL-010, REQ-DASH-008, REQ-DASH-009, NFR-DASH-001, REQ-RECO-002</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>W07</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>검사 · 상담 안내</t>
+          <t>추이 · 변화 추적</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>모델 A 높음 또는 혈압 140/90 이상 → 의료기관</t>
+          <t>이력 → 차트</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>고위험 안내 문구, 검사 권고, 의료기관 정보, 면책 문구</t>
+          <t>예측 이력 차트, 최초 대비 증감(색상+기호), 기간 필터, 데이터 1건 이하 빈 상태</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>REQ-PRED-005, NFR-SAFE-001</t>
+          <t>REQ-DASH-002, REQ-DASH-003, REQ-DASH-010, REQ-FEED-002, NFR-SAFE-005, NFR-ARCH-004</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>W08</t>
+          <t>W11-2</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>대시보드 (홈)</t>
+          <t>4주 전 · 후 비교</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>상태 요약 → 오늘의 실천</t>
+          <t>재입력 → 같은 모델 → 변화</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>상단 네비게이션, 최신 위험도 카드, 오늘의 챌린지 진행률, 사이클 현황, 빈 상태 CTA</t>
+          <t>시작·4주 후 심장 혈관 건강 신호·생활습관·체형 비교, 혈압·몸무게·허리둘레 변화, 미션 달성률·습관 변화, 다음 4주 챌린지 선택 (혈관 나이·요인 순위 변화는 보류 · 결정 필요 시트 참고)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>REQ-PRED-004, REQ-PRED-007, REQ-DASH-001, REQ-DASH-004, REQ-DASH-005, REQ-DASH-006, REQ-DASH-007, REQ-DASH-008, REQ-DASH-009, REQ-DASH-010, REQ-DASH-011, NFR-DASH-001, NFR-SAFE-001, NFR-SAFE-005</t>
+          <t>REQ-HEALTH-008, REQ-PRED-007, REQ-DASH-003, REQ-DASH-011</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>W08-2</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>캘린더 상세</t>
+          <t>피드백 · 마이페이지</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>날짜 선택 → 일기·사진·일정·할 일</t>
+          <t>의견 → 저장 / 계정 관리</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>월 달력, 일기, 사진, 일정, 오늘 할 일(챌린지 연동)</t>
+          <t>결과·추천 평가와 의견 입력, 알림 수신 설정, 동의 철회, 회원 탈퇴</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>REQ-CAL-001, REQ-CAL-002, REQ-CAL-003</t>
+          <t>REQ-USER-003, REQ-CONSENT-002, REQ-NOTI-001, REQ-FEED-001</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>W09</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>챌린지 선택</t>
+          <t>커뮤니티 피드</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>추천 → 선택 → 시작</t>
+          <t>피드 보기 → 글 열기 / 글쓰기 / 사람 프로필</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>예측 근거별 챌린지 후보, 연결된 위험 요인 표시, 목표 횟수 설정, 사이클 시작, 고정 미션 2개, 제외한 챌린지·이유</t>
+          <t>탭(피드·챌린지·파티), 분류 칩, 안내 띠, 글 카드, 글쓰기 버튼</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>REQ-CHAL-001, REQ-CHAL-002, REQ-CHAL-003, REQ-CHAL-008, REQ-CHAL-009, NFR-DASH-001, REQ-FEED-003, NFR-SAFE-007</t>
+          <t>REQ-COMM-001, REQ-COMM-002, REQ-COMM-003, REQ-COMM-007, REQ-COMM-010, REQ-PUSH-001</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>챌린지 수행 · 인증</t>
+          <t>글쓰기</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>목표 → 인증 → 달성률</t>
+          <t>분류 선택 → 제목·본문 → 챌린지 붙이기 → 올리기</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>오늘의 목표 목록, 인증하기, 당일 기록 수정, 주간·사이클 달성률, 식단 사진 업로드</t>
+          <t>올릴 곳, 분류 칩, 제목·본문, 챌린지 붙이기, 사진 3장, 파이 안내</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>REQ-CHAL-004, REQ-CHAL-005, REQ-CHAL-006, REQ-CHAL-007, REQ-CHAL-010, REQ-DASH-008, REQ-DASH-009, NFR-DASH-001, REQ-RECO-002</t>
+          <t>REQ-COMM-004, REQ-COMM-005, REQ-COMM-007, REQ-PIE-001</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>추이 · 변화 추적</t>
+          <t>글 상세 · 댓글 · 답글 · 좋아요</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>이력 → 차트</t>
+          <t>글 읽기 → 좋아요 → 댓글·답글 → 수정·삭제·신고</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>예측 이력 차트, 최초 대비 증감(색상+기호), 기간 필터, 데이터 1건 이하 빈 상태</t>
+          <t>글 머리, 좋아요, 신고, 댓글·답글(한 단계), 댓글 좋아요, 입력줄</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>REQ-DASH-002, REQ-DASH-003, REQ-DASH-010, REQ-FEED-002, NFR-SAFE-005, NFR-ARCH-004</t>
+          <t>REQ-COMM-003, REQ-COMM-005, REQ-COMM-006, REQ-COMM-008, REQ-COMM-009, REQ-COMM-010, REQ-PUSH-002</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>W11-2</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>4주 전 · 후 비교</t>
+          <t>사람 프로필 · 인기도</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>재입력 → 같은 모델 → 변화</t>
+          <t>닉네임·아바타 → 글·댓글 → 인기도 하트</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>시작·4주 후 심장 혈관 건강 신호·생활습관·체형 비교, 혈압·몸무게·허리둘레 변화, 미션 달성률·습관 변화, 다음 4주 챌린지 선택 (혈관 나이·요인 순위 변화는 보류 · 결정 필요 시트 참고)</t>
+          <t>캐릭터·닉네임, 인기도 하트, 글·댓글 탭</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-008, REQ-PRED-007, REQ-DASH-003, REQ-DASH-011</t>
+          <t>REQ-COMM-011, REQ-COMM-012, REQ-COMM-013, REQ-CHARA-003, REQ-PUSH-005</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>피드백 · 마이페이지</t>
+          <t>닉네임 정하기 · 캐릭터 꾸미기</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>의견 → 저장 / 계정 관리</t>
+          <t>닉네임 → 캐릭터 → 파이로 아이템 구매 → 저장</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>결과·추천 평가와 의견 입력, 알림 수신 설정, 동의 철회, 회원 탈퇴</t>
+          <t>미리보기, 6개 탭(몸체·색·눈 색·표정·얼굴·머리), 가격, 파이 잔액, 저장 버튼</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>REQ-USER-003, REQ-CONSENT-002, REQ-NOTI-001, REQ-FEED-001</t>
+          <t>REQ-COMM-014, REQ-CHARA-001, REQ-CHARA-002, REQ-CHARA-003, REQ-PIE-002</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>커뮤니티 피드</t>
+          <t>파이</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>피드 보기 → 글 열기 / 글쓰기 / 사람 프로필</t>
+          <t>내 파이 → 모으는 방법 → 최근 내역</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>탭(피드·챌린지·파티), 분류 칩, 안내 띠, 글 카드, 글쓰기 버튼</t>
+          <t>잔액, 지급표, 최근 내역, 가입 감사 파이 받기</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-001, REQ-COMM-002, REQ-COMM-003, REQ-COMM-007, REQ-COMM-010, REQ-PUSH-001</t>
+          <t>REQ-PIE-001, REQ-PIE-002, REQ-PIE-003, REQ-PIE-004</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>글쓰기</t>
+          <t>챌린지 파티</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>분류 선택 → 제목·본문 → 챌린지 붙이기 → 올리기</t>
+          <t>만들기 / 초대 코드 참여 → 파티 현황 → 파티 피드</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>올릴 곳, 분류 칩, 제목·본문, 챌린지 붙이기, 사진 3장, 파이 안내</t>
+          <t>파티 시작·만들기·현황·피드(W19-2~4 하위 화면)</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-004, REQ-COMM-005, REQ-COMM-007, REQ-PIE-001</t>
+          <t>REQ-PARTY-001, REQ-PARTY-002, REQ-PARTY-003, REQ-PARTY-004, REQ-PARTY-005, REQ-PUSH-004</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>글 상세 · 댓글 · 답글 · 좋아요</t>
+          <t>공통 챌린지</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>글 읽기 → 좋아요 → 댓글·답글 → 수정·삭제·신고</t>
+          <t>목록 → 참여 → 하루 인증 → 순위·완주 보상</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>글 머리, 좋아요, 신고, 댓글·답글(한 단계), 댓글 좋아요, 입력줄</t>
+          <t>목록(진행·예정·종료), 상세(규칙·보상·순위표), 인증 입력</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-003, REQ-COMM-005, REQ-COMM-006, REQ-COMM-008, REQ-COMM-009, REQ-COMM-010, REQ-PUSH-002</t>
+          <t>REQ-CCHAL-001, REQ-CCHAL-002, REQ-CCHAL-003, REQ-CCHAL-004, REQ-CCHAL-005</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>사람 프로필 · 인기도</t>
+          <t>1:1 문의 · 비회원 문의 · 공지사항</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>닉네임·아바타 → 글·댓글 → 인기도 하트</t>
+          <t>문의 남기기 → 답변 확인 / 공지 확인</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·닉네임, 인기도 하트, 글·댓글 탭</t>
+          <t>문의 목록·작성, 비회원 문의(조회 번호), 공지 목록</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-011, REQ-COMM-012, REQ-COMM-013, REQ-CHARA-003, REQ-PUSH-005</t>
+          <t>REQ-INQ-001, REQ-INQ-002, REQ-INQ-003, REQ-INQ-004, REQ-NOTICE-002, REQ-PUSH-003</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>닉네임 정하기 · 캐릭터 꾸미기</t>
+          <t>알림 설정 · 더보기</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>닉네임 → 캐릭터 → 파이로 아이템 구매 → 저장</t>
+          <t>더보기 → 알림 설정 → 켜기 → 종류별 선택</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>미리보기, 6개 탭(몸체·색·눈 색·표정·얼굴·머리), 가격, 파이 잔액, 저장 버튼</t>
+          <t>알림 스위치, 종류별 스위치 5개, 환경 안내(아이폰·안드로이드), 더보기 메뉴</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-014, REQ-CHARA-001, REQ-CHARA-002, REQ-CHARA-003, REQ-PIE-002</t>
+          <t>REQ-PUSH-001, REQ-PUSH-002, REQ-PUSH-003, REQ-PUSH-004, REQ-PUSH-005, REQ-PUSH-006, REQ-PUSH-007, REQ-NOTI-001</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>파이</t>
+          <t>내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>내 파이 → 모으는 방법 → 최근 내역</t>
+          <t>12주 계획 → 4주마다 재입력 → 12주 결과 → 지난 기록</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>잔액, 지급표, 최근 내역, 가입 감사 파이 받기</t>
+          <t>12주 일정, 혈압 그래프, 전·후 표, 습관 변화, 4주마다 달성률</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>REQ-PIE-001, REQ-PIE-002, REQ-PIE-003, REQ-PIE-004</t>
+          <t>REQ-CHAL-012, REQ-CHAL-013, REQ-DASH-012, REQ-DASH-013, NFR-SAFE-001</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>챌린지 파티</t>
+          <t>내 배지</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>만들기 / 초대 코드 참여 → 파티 현황 → 파티 피드</t>
+          <t>배지 모으기 → 내 배지 확인</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>파티 시작·만들기·현황·피드(W19-2~4 하위 화면)</t>
+          <t>모은 개수 링, 다음 배지, 연속 달성·완주와 기록 배지, 진행률</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>REQ-PARTY-001, REQ-PARTY-002, REQ-PARTY-003, REQ-PARTY-004, REQ-PARTY-005, REQ-PUSH-004</t>
+          <t>REQ-BADGE-001, REQ-BADGE-002</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>공통 챌린지</t>
+          <t>관리자 · 미션 · 가입자 · 통계 · 열람 기록</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>목록 → 참여 → 하루 인증 → 순위·완주 보상</t>
+          <t>미션 노출 → 가입자 → 통계 → 열람 기록</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>목록(진행·예정·종료), 상세(규칙·보상·순위표), 인증 입력</t>
+          <t>왼쪽 메뉴(11개), 표, 필터, 검색</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>REQ-CCHAL-001, REQ-CCHAL-002, REQ-CCHAL-003, REQ-CCHAL-004, REQ-CCHAL-005</t>
+          <t>REQ-ADM-001, REQ-ADM-002, REQ-ADM-003, REQ-ADM-004, REQ-ADM-012</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>1:1 문의 · 비회원 문의 · 공지사항</t>
+          <t>관리자 · 문의 · 비회원 문의</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>문의 남기기 → 답변 확인 / 공지 확인</t>
+          <t>목록 → 열어서 답변</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>문의 목록·작성, 비회원 문의(조회 번호), 공지 목록</t>
+          <t>상태 필터, 문의 목록, 답변 입력</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>REQ-INQ-001, REQ-INQ-002, REQ-INQ-003, REQ-INQ-004, REQ-NOTICE-002, REQ-PUSH-003</t>
+          <t>REQ-ADM-005, REQ-ADM-006, REQ-INQ-002, REQ-INQ-003</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>알림 설정 · 더보기</t>
+          <t>관리자 · 공지 · 신고 · 글 관리</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>더보기 → 알림 설정 → 켜기 → 종류별 선택</t>
+          <t>공지 올리기 / 신고 처리 / 글 숨김·삭제</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>알림 스위치, 종류별 스위치 5개, 환경 안내(아이폰·안드로이드), 더보기 메뉴</t>
+          <t>공지 폼, 신고 표, 글 표, 계정 정지·삭제</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>REQ-PUSH-001, REQ-PUSH-002, REQ-PUSH-003, REQ-PUSH-004, REQ-PUSH-005, REQ-PUSH-006, REQ-PUSH-007, REQ-NOTI-001</t>
+          <t>REQ-ADM-007, REQ-ADM-008, REQ-ADM-009, REQ-ADM-013, REQ-NOTICE-001, REQ-COMM-008</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
+          <t>관리자 · 공통 챌린지 · 테스트 계정 삭제</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>12주 계획 → 4주마다 재입력 → 12주 결과 → 지난 기록</t>
+          <t>공통 챌린지 열기·확정 / 테스트 계정 삭제</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>12주 일정, 혈압 그래프, 전·후 표, 습관 변화, 4주마다 달성률</t>
+          <t>챌린지 폼·카드, 순위 확정, 미리보기·삭제</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>REQ-CHAL-012, REQ-CHAL-013, REQ-DASH-012, REQ-DASH-013, NFR-SAFE-001</t>
+          <t>REQ-ADM-010, REQ-ADM-011, REQ-CCHAL-005</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>내 배지</t>
+          <t>관리자 · 운영 현황</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>배지 모으기 → 내 배지 확인</t>
+          <t>기간 선택 → 단계별·날짜별 집계 → CSV</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>모은 개수 링, 다음 배지, 연속 달성·완주와 기록 배지, 진행률</t>
+          <t>체험 진행 현황, 날짜별 활동, 동의·삭제 현황, 서비스 상태, CSV</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>REQ-BADGE-001, REQ-BADGE-002</t>
+          <t>REQ-ADM-014</t>
         </is>
       </c>
     </row>

--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>커뮤니티·파이·파티·공통 챌린지·푸시·문의·공지·관리자 요구사항 없음 / 화면 목록이 W12까지 / 보류 항목 미반영 / 공복혈당 수집 / 예측 요청 작업 큐 서술 / 4주 비교·내 변화 화면 면책 문구 없음 / 만 14세 미만 법정대리인 동의 요구(서비스는 만 19세 이상으로 제한) / 배지·캘린더·운영 현황 요구사항 없음</t>
+          <t>커뮤니티·파이·파티·공통 챌린지·푸시·문의·공지·관리자 요구사항 없음 / 화면 목록이 W12까지 / 보류 항목 미반영 / 공복혈당 수집 / 예측 요청 작업 큐 서술 / 4주 비교·내 변화 화면 면책 문구 없음 / 만 14세 미만 법정대리인 동의 요구(서비스는 만 19세 이상으로 제한) / 배지·캘린더·운영 현황 요구사항 없음 / 새 12주 시작·모델 버전 표시·양호 오해 안내 요구사항 없음</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
-          <t>신규 요구사항 REQ-COMM-001~014, REQ-PIE-001~004, REQ-CHARA-001~003, REQ-PARTY-001~005, REQ-CCHAL-001~005, REQ-PUSH-001~007, REQ-INQ-001~004, REQ-NOTICE-001~002, REQ-CHAL-012·013, REQ-DASH-012·013, REQ-ADM-001~013 추가, 화면 목록에 W13~W23·A01~A04, ID Naming 접두사 10개 추가 / 보류 3건 반영: 공복혈당 수집 중단(REQ-HEALTH-002·007), 예측 요청은 즉시 계산·201 반환(REQ-PRED-002), W11·W11-2 면책 문구(NFR-SAFE-001), 보류 시트 3건 상태 '반영' / 법정대리인 동의 삭제 → 만 19세 이상 가입(REQ-CONSENT-003, REQ-USER-001, REQ-ELIG-001 수정) / 배지(REQ-BADGE-001·002), 캘린더(REQ-CAL-001~003), 관리자 운영 현황(REQ-ADM-014) 추가, 화면 목록에 W24·W08-2·A05</t>
+          <t>신규 요구사항 REQ-COMM-001~014, REQ-PIE-001~004, REQ-CHARA-001~003, REQ-PARTY-001~005, REQ-CCHAL-001~005, REQ-PUSH-001~007, REQ-INQ-001~004, REQ-NOTICE-001~002, REQ-CHAL-012·013, REQ-DASH-012·013, REQ-ADM-001~013 추가, 화면 목록에 W13~W23·A01~A04, ID Naming 접두사 10개 추가 / 보류 3건 반영: 공복혈당 수집 중단(REQ-HEALTH-002·007), 예측 요청은 즉시 계산·201 반환(REQ-PRED-002), W11·W11-2 면책 문구(NFR-SAFE-001), 보류 시트 3건 상태 '반영' / 법정대리인 동의 삭제 → 만 19세 이상 가입(REQ-CONSENT-003, REQ-USER-001, REQ-ELIG-001 수정) / 배지(REQ-BADGE-001·002), 캘린더(REQ-CAL-001~003), 관리자 운영 현황(REQ-ADM-014) 추가, 화면 목록에 W24·W08-2·A05 / 새 12주 시작(REQ-CHAL-014), 목표 미달 안내(REQ-CHAL-015), 분석 모델 버전 표시(REQ-PRED-010), 양호 안내(REQ-PRED-011), 사람별 모델 버전 고정(NFR-ML-010), 모델 버전 변경 공지(REQ-NOTICE-003) 추가, REQ-CHAL-012의 '12주 한 번만 허용' 수정, 화면 목록에 W08-3</t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
@@ -6807,7 +6807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K170"/>
+  <dimension ref="A1:K176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.00500011" customWidth="1" min="1" max="1"/>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>시작일 기준 4주마다 바뀐 항목만 다시 입력해 처음과 비교하도록 안내한다. 서버는 지금 12주를 한 번만 허용한다(12주를 마친 뒤 새 12주는 팀 결정 필요).</t>
+          <t>시작일 기준 4주마다 바뀐 항목만 다시 입력해 처음과 비교하도록 안내한다. 12주를 마친 뒤 새 12주를 시작하는 방법은 REQ-CHAL-014를 따른다.</t>
         </is>
       </c>
       <c r="J148" s="14" t="inlineStr">
@@ -16509,6 +16509,348 @@
         </is>
       </c>
       <c r="K170" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-014</t>
+        </is>
+      </c>
+      <c r="B171" s="14" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="C171" s="14" t="inlineStr">
+        <is>
+          <t>12주 프로그램</t>
+        </is>
+      </c>
+      <c r="D171" s="14" t="inlineStr">
+        <is>
+          <t>새 12주 시작</t>
+        </is>
+      </c>
+      <c r="E171" s="14" t="inlineStr">
+        <is>
+          <t>12주 완료 후</t>
+        </is>
+      </c>
+      <c r="F171" s="14" t="inlineStr">
+        <is>
+          <t>12주를 모두 마친 이용자는 새 12주(4주씩 3번)를 시작할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G171" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H171" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I171" s="14" t="inlineStr">
+        <is>
+          <t>홈의 '새 12주 시작하기' 버튼은 서버가 시작 가능(can_restart)이라고 할 때만 보인다. 누르면 확인창에서 모델 버전이 바뀌었으면 새 버전·업데이트 날짜·바뀐 점과 '이전 12주 결과는 그때 쓴 모델 그대로 남고 새 결과와는 직접 비교할 수 없다'를 안내한다. 이전 12주의 결과·예측·모델 버전은 덮어쓰지 않고 보존하며 지난 12주 기록에서 12주마다 따로 열어 볼 수 있다. 12주를 마치지 않았으면 서버가 409(PROGRAM_NOT_COMPLETE)로 막는다.</t>
+        </is>
+      </c>
+      <c r="J171" s="14" t="inlineStr">
+        <is>
+          <t>W08-3 12주를 마친 홈 · 새 12주 시작, W23 내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
+        </is>
+      </c>
+      <c r="K171" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-015</t>
+        </is>
+      </c>
+      <c r="B172" s="14" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="C172" s="14" t="inlineStr">
+        <is>
+          <t>4주 종료</t>
+        </is>
+      </c>
+      <c r="D172" s="14" t="inlineStr">
+        <is>
+          <t>목표 미달 안내</t>
+        </is>
+      </c>
+      <c r="E172" s="14" t="inlineStr">
+        <is>
+          <t>다음 단계 문구</t>
+        </is>
+      </c>
+      <c r="F172" s="14" t="inlineStr">
+        <is>
+          <t>4주 목표를 달성하지 못한 이용자에게는 달성한 이용자와 다른 문구로 다음 4주를 안내해야 한다.</t>
+        </is>
+      </c>
+      <c r="G172" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H172" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I172" s="14" t="inlineStr">
+        <is>
+          <t>미달이어도 12주 일정은 그대로 다음 차수로 넘어간다. 홈은 '목표를 다 채우지는 못했지만 괜찮아요. 다음 4주 미션을 골라 이어서 해 봐요', 버튼은 '다음 4주 미션 고르기'로 보인다. 달성한 이용자는 '다음 4주 시작하기'가 그대로 나온다.</t>
+        </is>
+      </c>
+      <c r="J172" s="14" t="inlineStr">
+        <is>
+          <t>W08 대시보드 (홈), W10 챌린지 수행 · 인증</t>
+        </is>
+      </c>
+      <c r="K172" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PRED-010</t>
+        </is>
+      </c>
+      <c r="B173" s="14" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="C173" s="14" t="inlineStr">
+        <is>
+          <t>결과 표시</t>
+        </is>
+      </c>
+      <c r="D173" s="14" t="inlineStr">
+        <is>
+          <t>모델 버전</t>
+        </is>
+      </c>
+      <c r="E173" s="14" t="inlineStr">
+        <is>
+          <t>버전·업데이트 날짜</t>
+        </is>
+      </c>
+      <c r="F173" s="14" t="inlineStr">
+        <is>
+          <t>분석 결과 화면과 12주 결과 화면에는 그 결과를 계산한 분석 모델의 버전과 업데이트 날짜를 표시해야 한다.</t>
+        </is>
+      </c>
+      <c r="G173" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H173" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I173" s="14" t="inlineStr">
+        <is>
+          <t>결과 화면 아래 안내에 '분석 모델: 심장 혈관 건강 신호 v○ (날짜 업데이트) · 생활습관·체형 비교 v○'를 보여 준다. 12주 결과는 '12주를 시작한 모델 그대로 처음부터 끝까지 계산했어요'를 함께 보여 준다. 서버가 버전·날짜를 주지 않으면 표시하지 않는다.</t>
+        </is>
+      </c>
+      <c r="J173" s="14" t="inlineStr">
+        <is>
+          <t>W06 예측 결과 · XAI 설명, W23 내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
+        </is>
+      </c>
+      <c r="K173" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="13" t="inlineStr">
+        <is>
+          <t>REQ-PRED-011</t>
+        </is>
+      </c>
+      <c r="B174" s="14" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="C174" s="14" t="inlineStr">
+        <is>
+          <t>결과 표시</t>
+        </is>
+      </c>
+      <c r="D174" s="14" t="inlineStr">
+        <is>
+          <t>양호 안내</t>
+        </is>
+      </c>
+      <c r="E174" s="14" t="inlineStr">
+        <is>
+          <t>의미 설명</t>
+        </is>
+      </c>
+      <c r="F174" s="14" t="inlineStr">
+        <is>
+          <t>분석 결과의 범주가 '양호'일 때는 그 뜻이 건강에 문제가 없다는 것이 아님을 접지 않고 항상 보여 줘야 한다.</t>
+        </is>
+      </c>
+      <c r="G174" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H174" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I174" s="14" t="inlineStr">
+        <is>
+          <t>결과 화면은 배지 바로 아래에 '입력한 정보로 계산한 10년 심장 혈관 질환 확률이 낮은 구간(2% 미만)이에요. 건강에 전혀 문제가 없다는 뜻은 아니에요.'를 항상 보여 준다. 홈·12주 계획·내 데이터·4주 재입력·내 변화·12주 변화에는 '양호는 건강에 문제가 없다는 뜻은 아니에요.' 한 줄을 보여 준다. '주의'와 '높음'에는 넣지 않는다. 근거: 지인 설문 13명 중 7명(53.8%)이 '건강에 문제없음'으로 오해(2026-10-26).</t>
+        </is>
+      </c>
+      <c r="J174" s="14" t="inlineStr">
+        <is>
+          <t>W06 예측 결과 · XAI 설명, W08 대시보드 (홈), W23 내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
+        </is>
+      </c>
+      <c r="K174" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="13" t="inlineStr">
+        <is>
+          <t>NFR-ML-010</t>
+        </is>
+      </c>
+      <c r="B175" s="14" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="C175" s="14" t="inlineStr">
+        <is>
+          <t>버전 관리</t>
+        </is>
+      </c>
+      <c r="D175" s="14" t="inlineStr">
+        <is>
+          <t>사람별 고정</t>
+        </is>
+      </c>
+      <c r="E175" s="14" t="inlineStr">
+        <is>
+          <t>12주 시작 버전</t>
+        </is>
+      </c>
+      <c r="F175" s="14" t="inlineStr">
+        <is>
+          <t>한 사람의 4주·12주 비교는 그 사람이 12주를 시작한 모델 버전으로 끝까지 계산해야 한다.</t>
+        </is>
+      </c>
+      <c r="G175" s="14" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H175" s="14" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I175" s="14" t="inlineStr">
+        <is>
+          <t>모델 파일을 버전별로 읽고 사람마다 12주 첫 분석의 버전으로 4주·12주 재예측을 계산한다. 다음 12주를 시작하면 새 버전으로 시작하고 사용자에게 안내한다. 과거 결과는 덮어쓰지 않고 버전과 함께 보존한다. 안전 문제나 버그가 있으면 고정과 상관없이 전원을 즉시 새 버전으로 바꾸고 안내한다. (원칙: PR #199, 식약처·FDA·IMDRF 가이드라인 확인)</t>
+        </is>
+      </c>
+      <c r="J175" s="14" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K175" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="13" t="inlineStr">
+        <is>
+          <t>REQ-NOTICE-003</t>
+        </is>
+      </c>
+      <c r="B176" s="14" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="C176" s="14" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D176" s="14" t="inlineStr">
+        <is>
+          <t>모델 버전 변경 공지</t>
+        </is>
+      </c>
+      <c r="E176" s="14" t="inlineStr">
+        <is>
+          <t>배포 전 안내</t>
+        </is>
+      </c>
+      <c r="F176" s="14" t="inlineStr">
+        <is>
+          <t>새 분석 모델 버전을 배포하기 전에 무엇이 바뀌는지와 언제부터 적용되는지를 공지로 알려야 한다.</t>
+        </is>
+      </c>
+      <c r="G176" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H176" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I176" s="14" t="inlineStr">
+        <is>
+          <t>관리자 공지 화면으로 올리고, 안전 문제로 전원을 바로 바꿀 때도 같은 방법으로 알린다. 푸시 공지는 알림 종류에 '공지'를 추가해야 하며 담당을 정해야 한다.</t>
+        </is>
+      </c>
+      <c r="J176" s="14" t="inlineStr">
+        <is>
+          <t>A03 관리자 · 공지 · 신고 · 글 관리, W21 1:1 문의 · 비회원 문의 · 공지사항</t>
+        </is>
+      </c>
+      <c r="K176" s="14" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -18716,7 +19058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.005000109999999" customWidth="1" min="1" max="1"/>
@@ -18932,12 +19274,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>입력 혈압 판정, 심장 혈관 건강 신호(확률·범주·확률 근거), 혈관 나이(같은 성별·연령대 상위 %·계산 근거), 바꿀 수 있는 요인, 생활습관·체형 비교(3단계·비교 기준), 면책 문구</t>
+          <t>입력 혈압 판정, 심장 혈관 건강 신호(확률·범주·확률 근거), 혈관 나이(같은 성별·연령대 상위 %·계산 근거), 바꿀 수 있는 요인, 생활습관·체형 비교(3단계·비교 기준), 면책 문구, 분석 모델 버전, 양호 안내</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>REQ-PRED-001, REQ-PRED-003, REQ-PRED-006,  NFR-SAFE-001, NFR-SAFE-002, NFR-SAFE-003, NFR-SAFE-005, NFR-SAFE-007</t>
+          <t>REQ-PRED-001, REQ-PRED-003, REQ-PRED-006,  NFR-SAFE-001, NFR-SAFE-002, NFR-SAFE-003, NFR-SAFE-005, NFR-SAFE-007, REQ-PRED-010, REQ-PRED-011</t>
         </is>
       </c>
     </row>
@@ -19025,592 +19367,619 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>W09</t>
+          <t>W08-3</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>챌린지 선택</t>
+          <t>12주를 마친 홈 · 새 12주 시작</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>추천 → 선택 → 시작</t>
+          <t>12주 완료 → 새 12주 시작하기 → 모델 버전 안내 → 챌린지 선택</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>예측 근거별 챌린지 후보, 연결된 위험 요인 표시, 목표 횟수 설정, 사이클 시작, 고정 미션 2개, 제외한 챌린지·이유</t>
+          <t>12주 완료 카드, 새 12주 시작하기 버튼, 확인창(모델 버전·바뀐 점·결과 보존 안내)</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>REQ-CHAL-001, REQ-CHAL-002, REQ-CHAL-003, REQ-CHAL-008, REQ-CHAL-009, NFR-DASH-001, REQ-FEED-003, NFR-SAFE-007</t>
+          <t>REQ-CHAL-014, REQ-PRED-010, NFR-ML-010, REQ-NOTICE-003</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W09</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>챌린지 수행 · 인증</t>
+          <t>챌린지 선택</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>목표 → 인증 → 달성률</t>
+          <t>추천 → 선택 → 시작</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>오늘의 목표 목록, 인증하기, 당일 기록 수정, 주간·사이클 달성률, 식단 사진 업로드</t>
+          <t>예측 근거별 챌린지 후보, 연결된 위험 요인 표시, 목표 횟수 설정, 사이클 시작, 고정 미션 2개, 제외한 챌린지·이유</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>REQ-CHAL-004, REQ-CHAL-005, REQ-CHAL-006, REQ-CHAL-007, REQ-CHAL-010, REQ-DASH-008, REQ-DASH-009, NFR-DASH-001, REQ-RECO-002</t>
+          <t>REQ-CHAL-001, REQ-CHAL-002, REQ-CHAL-003, REQ-CHAL-008, REQ-CHAL-009, NFR-DASH-001, REQ-FEED-003, NFR-SAFE-007</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>추이 · 변화 추적</t>
+          <t>챌린지 수행 · 인증</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>이력 → 차트</t>
+          <t>목표 → 인증 → 달성률</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>예측 이력 차트, 최초 대비 증감(색상+기호), 기간 필터, 데이터 1건 이하 빈 상태</t>
+          <t>오늘의 목표 목록, 인증하기, 당일 기록 수정, 주간·사이클 달성률, 식단 사진 업로드</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>REQ-DASH-002, REQ-DASH-003, REQ-DASH-010, REQ-FEED-002, NFR-SAFE-005, NFR-ARCH-004</t>
+          <t>REQ-CHAL-004, REQ-CHAL-005, REQ-CHAL-006, REQ-CHAL-007, REQ-CHAL-010, REQ-DASH-008, REQ-DASH-009, NFR-DASH-001, REQ-RECO-002</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>W11-2</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>4주 전 · 후 비교</t>
+          <t>추이 · 변화 추적</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>재입력 → 같은 모델 → 변화</t>
+          <t>이력 → 차트</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>시작·4주 후 심장 혈관 건강 신호·생활습관·체형 비교, 혈압·몸무게·허리둘레 변화, 미션 달성률·습관 변화, 다음 4주 챌린지 선택 (혈관 나이·요인 순위 변화는 보류 · 결정 필요 시트 참고)</t>
+          <t>예측 이력 차트, 최초 대비 증감(색상+기호), 기간 필터, 데이터 1건 이하 빈 상태</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-008, REQ-PRED-007, REQ-DASH-003, REQ-DASH-011</t>
+          <t>REQ-DASH-002, REQ-DASH-003, REQ-DASH-010, REQ-FEED-002, NFR-SAFE-005, NFR-ARCH-004</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W11-2</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>피드백 · 마이페이지</t>
+          <t>4주 전 · 후 비교</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>의견 → 저장 / 계정 관리</t>
+          <t>재입력 → 같은 모델 → 변화</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>결과·추천 평가와 의견 입력, 알림 수신 설정, 동의 철회, 회원 탈퇴</t>
+          <t>시작·4주 후 심장 혈관 건강 신호·생활습관·체형 비교, 혈압·몸무게·허리둘레 변화, 미션 달성률·습관 변화, 다음 4주 챌린지 선택 (혈관 나이·요인 순위 변화는 보류 · 결정 필요 시트 참고)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>REQ-USER-003, REQ-CONSENT-002, REQ-NOTI-001, REQ-FEED-001</t>
+          <t>REQ-HEALTH-008, REQ-PRED-007, REQ-DASH-003, REQ-DASH-011</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>커뮤니티 피드</t>
+          <t>피드백 · 마이페이지</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>피드 보기 → 글 열기 / 글쓰기 / 사람 프로필</t>
+          <t>의견 → 저장 / 계정 관리</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>탭(피드·챌린지·파티), 분류 칩, 안내 띠, 글 카드, 글쓰기 버튼</t>
+          <t>결과·추천 평가와 의견 입력, 알림 수신 설정, 동의 철회, 회원 탈퇴</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-001, REQ-COMM-002, REQ-COMM-003, REQ-COMM-007, REQ-COMM-010, REQ-PUSH-001</t>
+          <t>REQ-USER-003, REQ-CONSENT-002, REQ-NOTI-001, REQ-FEED-001</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>글쓰기</t>
+          <t>커뮤니티 피드</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>분류 선택 → 제목·본문 → 챌린지 붙이기 → 올리기</t>
+          <t>피드 보기 → 글 열기 / 글쓰기 / 사람 프로필</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>올릴 곳, 분류 칩, 제목·본문, 챌린지 붙이기, 사진 3장, 파이 안내</t>
+          <t>탭(피드·챌린지·파티), 분류 칩, 안내 띠, 글 카드, 글쓰기 버튼</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-004, REQ-COMM-005, REQ-COMM-007, REQ-PIE-001</t>
+          <t>REQ-COMM-001, REQ-COMM-002, REQ-COMM-003, REQ-COMM-007, REQ-COMM-010, REQ-PUSH-001</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>글 상세 · 댓글 · 답글 · 좋아요</t>
+          <t>글쓰기</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>글 읽기 → 좋아요 → 댓글·답글 → 수정·삭제·신고</t>
+          <t>분류 선택 → 제목·본문 → 챌린지 붙이기 → 올리기</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>글 머리, 좋아요, 신고, 댓글·답글(한 단계), 댓글 좋아요, 입력줄</t>
+          <t>올릴 곳, 분류 칩, 제목·본문, 챌린지 붙이기, 사진 3장, 파이 안내</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-003, REQ-COMM-005, REQ-COMM-006, REQ-COMM-008, REQ-COMM-009, REQ-COMM-010, REQ-PUSH-002</t>
+          <t>REQ-COMM-004, REQ-COMM-005, REQ-COMM-007, REQ-PIE-001</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>사람 프로필 · 인기도</t>
+          <t>글 상세 · 댓글 · 답글 · 좋아요</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>닉네임·아바타 → 글·댓글 → 인기도 하트</t>
+          <t>글 읽기 → 좋아요 → 댓글·답글 → 수정·삭제·신고</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·닉네임, 인기도 하트, 글·댓글 탭</t>
+          <t>글 머리, 좋아요, 신고, 댓글·답글(한 단계), 댓글 좋아요, 입력줄</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-011, REQ-COMM-012, REQ-COMM-013, REQ-CHARA-003, REQ-PUSH-005</t>
+          <t>REQ-COMM-003, REQ-COMM-005, REQ-COMM-006, REQ-COMM-008, REQ-COMM-009, REQ-COMM-010, REQ-PUSH-002</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>닉네임 정하기 · 캐릭터 꾸미기</t>
+          <t>사람 프로필 · 인기도</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>닉네임 → 캐릭터 → 파이로 아이템 구매 → 저장</t>
+          <t>닉네임·아바타 → 글·댓글 → 인기도 하트</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>미리보기, 6개 탭(몸체·색·눈 색·표정·얼굴·머리), 가격, 파이 잔액, 저장 버튼</t>
+          <t>캐릭터·닉네임, 인기도 하트, 글·댓글 탭</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>REQ-COMM-014, REQ-CHARA-001, REQ-CHARA-002, REQ-CHARA-003, REQ-PIE-002</t>
+          <t>REQ-COMM-011, REQ-COMM-012, REQ-COMM-013, REQ-CHARA-003, REQ-PUSH-005</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>파이</t>
+          <t>닉네임 정하기 · 캐릭터 꾸미기</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>내 파이 → 모으는 방법 → 최근 내역</t>
+          <t>닉네임 → 캐릭터 → 파이로 아이템 구매 → 저장</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>잔액, 지급표, 최근 내역, 가입 감사 파이 받기</t>
+          <t>미리보기, 6개 탭(몸체·색·눈 색·표정·얼굴·머리), 가격, 파이 잔액, 저장 버튼</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>REQ-PIE-001, REQ-PIE-002, REQ-PIE-003, REQ-PIE-004</t>
+          <t>REQ-COMM-014, REQ-CHARA-001, REQ-CHARA-002, REQ-CHARA-003, REQ-PIE-002</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>챌린지 파티</t>
+          <t>파이</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>만들기 / 초대 코드 참여 → 파티 현황 → 파티 피드</t>
+          <t>내 파이 → 모으는 방법 → 최근 내역</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>파티 시작·만들기·현황·피드(W19-2~4 하위 화면)</t>
+          <t>잔액, 지급표, 최근 내역, 가입 감사 파이 받기</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>REQ-PARTY-001, REQ-PARTY-002, REQ-PARTY-003, REQ-PARTY-004, REQ-PARTY-005, REQ-PUSH-004</t>
+          <t>REQ-PIE-001, REQ-PIE-002, REQ-PIE-003, REQ-PIE-004</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>공통 챌린지</t>
+          <t>챌린지 파티</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>목록 → 참여 → 하루 인증 → 순위·완주 보상</t>
+          <t>만들기 / 초대 코드 참여 → 파티 현황 → 파티 피드</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>목록(진행·예정·종료), 상세(규칙·보상·순위표), 인증 입력</t>
+          <t>파티 시작·만들기·현황·피드(W19-2~4 하위 화면)</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>REQ-CCHAL-001, REQ-CCHAL-002, REQ-CCHAL-003, REQ-CCHAL-004, REQ-CCHAL-005</t>
+          <t>REQ-PARTY-001, REQ-PARTY-002, REQ-PARTY-003, REQ-PARTY-004, REQ-PARTY-005, REQ-PUSH-004</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>1:1 문의 · 비회원 문의 · 공지사항</t>
+          <t>공통 챌린지</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>문의 남기기 → 답변 확인 / 공지 확인</t>
+          <t>목록 → 참여 → 하루 인증 → 순위·완주 보상</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>문의 목록·작성, 비회원 문의(조회 번호), 공지 목록</t>
+          <t>목록(진행·예정·종료), 상세(규칙·보상·순위표), 인증 입력</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>REQ-INQ-001, REQ-INQ-002, REQ-INQ-003, REQ-INQ-004, REQ-NOTICE-002, REQ-PUSH-003</t>
+          <t>REQ-CCHAL-001, REQ-CCHAL-002, REQ-CCHAL-003, REQ-CCHAL-004, REQ-CCHAL-005</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>알림 설정 · 더보기</t>
+          <t>1:1 문의 · 비회원 문의 · 공지사항</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>더보기 → 알림 설정 → 켜기 → 종류별 선택</t>
+          <t>문의 남기기 → 답변 확인 / 공지 확인</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>알림 스위치, 종류별 스위치 5개, 환경 안내(아이폰·안드로이드), 더보기 메뉴</t>
+          <t>문의 목록·작성, 비회원 문의(조회 번호), 공지 목록</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>REQ-PUSH-001, REQ-PUSH-002, REQ-PUSH-003, REQ-PUSH-004, REQ-PUSH-005, REQ-PUSH-006, REQ-PUSH-007, REQ-NOTI-001</t>
+          <t>REQ-INQ-001, REQ-INQ-002, REQ-INQ-003, REQ-INQ-004, REQ-NOTICE-002, REQ-PUSH-003</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
+          <t>알림 설정 · 더보기</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>12주 계획 → 4주마다 재입력 → 12주 결과 → 지난 기록</t>
+          <t>더보기 → 알림 설정 → 켜기 → 종류별 선택</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>12주 일정, 혈압 그래프, 전·후 표, 습관 변화, 4주마다 달성률</t>
+          <t>알림 스위치, 종류별 스위치 5개, 환경 안내(아이폰·안드로이드), 더보기 메뉴</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>REQ-CHAL-012, REQ-CHAL-013, REQ-DASH-012, REQ-DASH-013, NFR-SAFE-001</t>
+          <t>REQ-PUSH-001, REQ-PUSH-002, REQ-PUSH-003, REQ-PUSH-004, REQ-PUSH-005, REQ-PUSH-006, REQ-PUSH-007, REQ-NOTI-001</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>내 배지</t>
+          <t>내 12주 계획 · 12주 결과 · 지난 12주 기록</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>배지 모으기 → 내 배지 확인</t>
+          <t>12주 계획 → 4주마다 재입력 → 12주 결과 → 지난 기록</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>모은 개수 링, 다음 배지, 연속 달성·완주와 기록 배지, 진행률</t>
+          <t>12주 일정, 혈압 그래프, 전·후 표, 습관 변화, 4주마다 달성률</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>REQ-BADGE-001, REQ-BADGE-002</t>
+          <t>REQ-CHAL-012, REQ-CHAL-013, REQ-CHAL-014, REQ-PRED-010, REQ-DASH-012, REQ-DASH-013, NFR-SAFE-001</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 미션 · 가입자 · 통계 · 열람 기록</t>
+          <t>내 배지</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>미션 노출 → 가입자 → 통계 → 열람 기록</t>
+          <t>배지 모으기 → 내 배지 확인</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>왼쪽 메뉴(11개), 표, 필터, 검색</t>
+          <t>모은 개수 링, 다음 배지, 연속 달성·완주와 기록 배지, 진행률</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-001, REQ-ADM-002, REQ-ADM-003, REQ-ADM-004, REQ-ADM-012</t>
+          <t>REQ-BADGE-001, REQ-BADGE-002</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 문의 · 비회원 문의</t>
+          <t>관리자 · 미션 · 가입자 · 통계 · 열람 기록</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>목록 → 열어서 답변</t>
+          <t>미션 노출 → 가입자 → 통계 → 열람 기록</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>상태 필터, 문의 목록, 답변 입력</t>
+          <t>왼쪽 메뉴(11개), 표, 필터, 검색</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-005, REQ-ADM-006, REQ-INQ-002, REQ-INQ-003</t>
+          <t>REQ-ADM-001, REQ-ADM-002, REQ-ADM-003, REQ-ADM-004, REQ-ADM-012</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 공지 · 신고 · 글 관리</t>
+          <t>관리자 · 문의 · 비회원 문의</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>공지 올리기 / 신고 처리 / 글 숨김·삭제</t>
+          <t>목록 → 열어서 답변</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>공지 폼, 신고 표, 글 표, 계정 정지·삭제</t>
+          <t>상태 필터, 문의 목록, 답변 입력</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-007, REQ-ADM-008, REQ-ADM-009, REQ-ADM-013, REQ-NOTICE-001, REQ-COMM-008</t>
+          <t>REQ-ADM-005, REQ-ADM-006, REQ-INQ-002, REQ-INQ-003</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>관리자 · 공통 챌린지 · 테스트 계정 삭제</t>
+          <t>관리자 · 공지 · 신고 · 글 관리</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>공통 챌린지 열기·확정 / 테스트 계정 삭제</t>
+          <t>공지 올리기 / 신고 처리 / 글 숨김·삭제</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>챌린지 폼·카드, 순위 확정, 미리보기·삭제</t>
+          <t>공지 폼, 신고 표, 글 표, 계정 정지·삭제</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-010, REQ-ADM-011, REQ-CCHAL-005</t>
+          <t>REQ-ADM-007, REQ-ADM-008, REQ-ADM-009, REQ-ADM-013, REQ-NOTICE-001, REQ-COMM-008</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>관리자 · 공통 챌린지 · 테스트 계정 삭제</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>공통 챌린지 열기·확정 / 테스트 계정 삭제</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>챌린지 폼·카드, 순위 확정, 미리보기·삭제</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>REQ-ADM-010, REQ-ADM-011, REQ-CCHAL-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>A05</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>관리자 · 운영 현황</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>기간 선택 → 단계별·날짜별 집계 → CSV</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>체험 진행 현황, 날짜별 활동, 동의·삭제 현황, 서비스 상태, CSV</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>REQ-ADM-014</t>
         </is>

--- a/docs/요구사항_정의서_파이온.xlsx
+++ b/docs/요구사항_정의서_파이온.xlsx
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>커뮤니티·파이·파티·공통 챌린지·푸시·문의·공지·관리자 요구사항 없음 / 화면 목록이 W12까지 / 보류 항목 미반영 / 공복혈당 수집 / 예측 요청 작업 큐 서술 / 4주 비교·내 변화 화면 면책 문구 없음 / 만 14세 미만 법정대리인 동의 요구(서비스는 만 19세 이상으로 제한) / 배지·캘린더·운영 현황 요구사항 없음 / 새 12주 시작·모델 버전 표시·양호 오해 안내 요구사항 없음</t>
+          <t>커뮤니티·파이·파티·공통 챌린지·푸시·문의·공지·관리자 요구사항 없음 / 화면 목록이 W12까지 / 보류 항목 미반영 / 공복혈당 수집 / 예측 요청 작업 큐 서술 / 4주 비교·내 변화 화면 면책 문구 없음 / 만 14세 미만 법정대리인 동의 요구(서비스는 만 19세 이상으로 제한) / 배지·캘린더·운영 현황 요구사항 없음 / 새 12주 시작·모델 버전 표시·양호 오해 안내 요구사항 없음 / 10/26 멘토링 이후 구현된 4건 요구사항 없음</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
-          <t>신규 요구사항 REQ-COMM-001~014, REQ-PIE-001~004, REQ-CHARA-001~003, REQ-PARTY-001~005, REQ-CCHAL-001~005, REQ-PUSH-001~007, REQ-INQ-001~004, REQ-NOTICE-001~002, REQ-CHAL-012·013, REQ-DASH-012·013, REQ-ADM-001~013 추가, 화면 목록에 W13~W23·A01~A04, ID Naming 접두사 10개 추가 / 보류 3건 반영: 공복혈당 수집 중단(REQ-HEALTH-002·007), 예측 요청은 즉시 계산·201 반환(REQ-PRED-002), W11·W11-2 면책 문구(NFR-SAFE-001), 보류 시트 3건 상태 '반영' / 법정대리인 동의 삭제 → 만 19세 이상 가입(REQ-CONSENT-003, REQ-USER-001, REQ-ELIG-001 수정) / 배지(REQ-BADGE-001·002), 캘린더(REQ-CAL-001~003), 관리자 운영 현황(REQ-ADM-014) 추가, 화면 목록에 W24·W08-2·A05 / 새 12주 시작(REQ-CHAL-014), 목표 미달 안내(REQ-CHAL-015), 분석 모델 버전 표시(REQ-PRED-010), 양호 안내(REQ-PRED-011), 사람별 모델 버전 고정(NFR-ML-010), 모델 버전 변경 공지(REQ-NOTICE-003) 추가, REQ-CHAL-012의 '12주 한 번만 허용' 수정, 화면 목록에 W08-3</t>
+          <t>신규 요구사항 REQ-COMM-001~014, REQ-PIE-001~004, REQ-CHARA-001~003, REQ-PARTY-001~005, REQ-CCHAL-001~005, REQ-PUSH-001~007, REQ-INQ-001~004, REQ-NOTICE-001~002, REQ-CHAL-012·013, REQ-DASH-012·013, REQ-ADM-001~013 추가, 화면 목록에 W13~W23·A01~A04, ID Naming 접두사 10개 추가 / 보류 3건 반영: 공복혈당 수집 중단(REQ-HEALTH-002·007), 예측 요청은 즉시 계산·201 반환(REQ-PRED-002), W11·W11-2 면책 문구(NFR-SAFE-001), 보류 시트 3건 상태 '반영' / 법정대리인 동의 삭제 → 만 19세 이상 가입(REQ-CONSENT-003, REQ-USER-001, REQ-ELIG-001 수정) / 배지(REQ-BADGE-001·002), 캘린더(REQ-CAL-001~003), 관리자 운영 현황(REQ-ADM-014) 추가, 화면 목록에 W24·W08-2·A05 / 새 12주 시작(REQ-CHAL-014), 목표 미달 안내(REQ-CHAL-015), 분석 모델 버전 표시(REQ-PRED-010), 양호 안내(REQ-PRED-011), 사람별 모델 버전 고정(NFR-ML-010), 모델 버전 변경 공지(REQ-NOTICE-003) 추가, REQ-CHAL-012의 '12주 한 번만 허용' 수정, 화면 목록에 W08-3 / 기간별 이탈 분석(REQ-ADM-015), 분석 필수 챌린지 시작(REQ-CHAL-016), 가입 이메일 도메인 선택(REQ-USER-005), 혈압 쉬운 표기(REQ-HEALTH-009) 추가 (10/28 최신화)</t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
@@ -6807,7 +6807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K176"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.00500011" customWidth="1" min="1" max="1"/>
@@ -16851,6 +16851,234 @@
         </is>
       </c>
       <c r="K176" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="13" t="inlineStr">
+        <is>
+          <t>REQ-ADM-015</t>
+        </is>
+      </c>
+      <c r="B177" s="14" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="C177" s="14" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="D177" s="14" t="inlineStr">
+        <is>
+          <t>기간별 이탈 분석</t>
+        </is>
+      </c>
+      <c r="E177" s="14" t="inlineStr">
+        <is>
+          <t>실제 기록 기준</t>
+        </is>
+      </c>
+      <c r="F177" s="14" t="inlineStr">
+        <is>
+          <t>관리자는 가입 기간을 정해 단계별 이탈과 가장 많이 빠진 단계, 챌린지 시작 후 직접 기록일 분포를 볼 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G177" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H177" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I177" s="14" t="inlineStr">
+        <is>
+          <t>단계(가입·대상 확인·건강정보·설문 제출·분석 결과·챌린지 시작·다음 4주 시작)마다 실제 기록이 있는 인원, 앞 단계에서 안 넘어온 인원, 앞 단계 없이 온 인원을 보여 주고 가장 많이 빠진 단계를 강조한다. 첫 4주 직접 기록일(0·1·2·3일 이상)별 인원은 체험 자동 채움 기록을 빼고 센다. 분석 없이 챌린지를 시작한 계정은 회원 번호 끝 8자리와 가입 시각만 보여 주고 이메일은 보여 주지 않는다. 기본 기간은 지인 체험 기간(10/22~10/25), 관리자 계정 제외 선택.</t>
+        </is>
+      </c>
+      <c r="J177" s="14" t="inlineStr">
+        <is>
+          <t>A05 관리자 · 운영 현황</t>
+        </is>
+      </c>
+      <c r="K177" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="13" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-016</t>
+        </is>
+      </c>
+      <c r="B178" s="14" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="C178" s="14" t="inlineStr">
+        <is>
+          <t>시작 조건</t>
+        </is>
+      </c>
+      <c r="D178" s="14" t="inlineStr">
+        <is>
+          <t>분석 필수</t>
+        </is>
+      </c>
+      <c r="E178" s="14" t="inlineStr">
+        <is>
+          <t>서버 검사</t>
+        </is>
+      </c>
+      <c r="F178" s="14" t="inlineStr">
+        <is>
+          <t>챌린지는 분석(예측)을 마친 이용자만 시작할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G178" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H178" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I178" s="14" t="inlineStr">
+        <is>
+          <t>화면 순서를 건너뛰거나 중간에 멈췄다 돌아와도 분석 결과 없이 챌린지가 만들어지지 않는다. 분석이 없으면 서버가 409(ANALYSIS_REQUIRED)와 "분석을 먼저 마쳐야 챌린지를 시작할 수 있어요."를 돌려 주고 아무것도 만들지 않는다. 설문은 건너뛸 수 있는 단계라 필수로 하지 않는다. 근거: 분석 없이 시작한 계정(bcb65673)이 4주 비교의 기준 결과를 갖지 못함.</t>
+        </is>
+      </c>
+      <c r="J178" s="14" t="inlineStr">
+        <is>
+          <t>W09 챌린지 선택</t>
+        </is>
+      </c>
+      <c r="K178" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="13" t="inlineStr">
+        <is>
+          <t>REQ-USER-005</t>
+        </is>
+      </c>
+      <c r="B179" s="14" t="inlineStr">
+        <is>
+          <t>회원·인증</t>
+        </is>
+      </c>
+      <c r="C179" s="14" t="inlineStr">
+        <is>
+          <t>회원가입</t>
+        </is>
+      </c>
+      <c r="D179" s="14" t="inlineStr">
+        <is>
+          <t>이메일 입력</t>
+        </is>
+      </c>
+      <c r="E179" s="14" t="inlineStr">
+        <is>
+          <t>도메인 선택</t>
+        </is>
+      </c>
+      <c r="F179" s="14" t="inlineStr">
+        <is>
+          <t>가입 화면에서 이메일 주소의 @ 뒷부분은 목록에서 고르게 해 도메인 오타로 인한 중복 가입을 줄여야 한다.</t>
+        </is>
+      </c>
+      <c r="G179" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H179" s="14" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I179" s="14" t="inlineStr">
+        <is>
+          <t>아이디는 직접 입력하고 도메인은 gmail.com·naver.com·daum.net·hanmail.net·kakao.com·nate.com·outlook.com·icloud.com 중에서 고른다(직접 입력 없음). 아이디 칸에 전체 주소를 붙여 넣으면 @ 앞은 아이디에, 뒤는 목록에 있으면 자동 선택한다. 서버에는 하나의 이메일 문자열로 보낸다. 근거: 이메일 오타로 중복 가입된 계정 발견(멘토링 10/26).</t>
+        </is>
+      </c>
+      <c r="J179" s="14" t="inlineStr">
+        <is>
+          <t>W02 회원가입 · 로그인 · 동의</t>
+        </is>
+      </c>
+      <c r="K179" s="14" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="13" t="inlineStr">
+        <is>
+          <t>REQ-HEALTH-009</t>
+        </is>
+      </c>
+      <c r="B180" s="14" t="inlineStr">
+        <is>
+          <t>건강정보</t>
+        </is>
+      </c>
+      <c r="C180" s="14" t="inlineStr">
+        <is>
+          <t>입력 화면</t>
+        </is>
+      </c>
+      <c r="D180" s="14" t="inlineStr">
+        <is>
+          <t>혈압 표기</t>
+        </is>
+      </c>
+      <c r="E180" s="14" t="inlineStr">
+        <is>
+          <t>쉬운 말</t>
+        </is>
+      </c>
+      <c r="F180" s="14" t="inlineStr">
+        <is>
+          <t>혈압 입력칸은 "높은 쪽 혈압(수축기)"와 "낮은 쪽 혈압(이완기)"처럼 쉬운 말과 의학 용어를 함께 보여 줘야 한다.</t>
+        </is>
+      </c>
+      <c r="G180" s="14" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H180" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I180" s="14" t="inlineStr">
+        <is>
+          <t>건강정보 입력, 4주 재입력, 홈·내 변화·12주 변화의 혈압 표기에 같은 이름을 쓴다. 두 칸이 바뀌어 높은 쪽이 낮은 쪽보다 크지 않으면 "높은 쪽 혈압은 낮은 쪽 혈압보다 커야 해요. 두 칸이 바뀌지 않았는지 확인해 주세요."를 보여 준다. 근거: 지인 설문 "수축기·이완기가 헷갈렸다".</t>
+        </is>
+      </c>
+      <c r="J180" s="14" t="inlineStr">
+        <is>
+          <t>W04 건강정보 입력, W11-2 4주 전 · 후 비교</t>
+        </is>
+      </c>
+      <c r="K180" s="14" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -19144,7 +19372,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>REQ-USER-001, REQ-USER-002, REQ-USER-004, REQ-CONSENT-001, REQ-CONSENT-003, NFR-SEC-003, NFR-SEC-006</t>
+          <t>REQ-USER-001, REQ-USER-002, REQ-USER-004, REQ-CONSENT-001, REQ-CONSENT-003, NFR-SEC-003, NFR-SEC-006, REQ-USER-005</t>
         </is>
       </c>
     </row>
@@ -19198,7 +19426,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-001, REQ-HEALTH-002, REQ-HEALTH-003, REQ-HEALTH-004, REQ-HEALTH-006, REQ-HEALTH-008, NFR-SEC-003, NFR-SEC-005, NFR-SEC-006, NFR-SEC-007, NFR-OPS-006</t>
+          <t>REQ-HEALTH-001, REQ-HEALTH-002, REQ-HEALTH-003, REQ-HEALTH-004, REQ-HEALTH-006, REQ-HEALTH-008, NFR-SEC-003, NFR-SEC-005, NFR-SEC-006, NFR-SEC-007, NFR-OPS-006, REQ-HEALTH-009</t>
         </is>
       </c>
     </row>
@@ -19414,7 +19642,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>REQ-CHAL-001, REQ-CHAL-002, REQ-CHAL-003, REQ-CHAL-008, REQ-CHAL-009, NFR-DASH-001, REQ-FEED-003, NFR-SAFE-007</t>
+          <t>REQ-CHAL-001, REQ-CHAL-002, REQ-CHAL-003, REQ-CHAL-008, REQ-CHAL-009, NFR-DASH-001, REQ-FEED-003, NFR-SAFE-007, REQ-CHAL-016</t>
         </is>
       </c>
     </row>
@@ -19976,12 +20204,12 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>체험 진행 현황, 날짜별 활동, 동의·삭제 현황, 서비스 상태, CSV</t>
+          <t>체험 진행 현황, 날짜별 활동, 동의·삭제 현황, 서비스 상태, CSV, 기간별 이탈 분석(단계별 이탈·직접 기록일·분석 없이 시작한 계정)</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>REQ-ADM-014</t>
+          <t>REQ-ADM-014, REQ-ADM-015</t>
         </is>
       </c>
     </row>
